--- a/survey.xlsx
+++ b/survey.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="129">
   <si>
     <t xml:space="preserve">type</t>
   </si>
@@ -93,31 +93,163 @@
     <t xml:space="preserve">Did not answer</t>
   </si>
   <si>
-    <t xml:space="preserve">decision_makers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wife</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wife</t>
-  </si>
-  <si>
-    <t xml:space="preserve">husband</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Husband</t>
-  </si>
-  <si>
-    <t xml:space="preserve">senior_male</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Male</t>
-  </si>
-  <si>
-    <t xml:space="preserve">senior_female</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Female</t>
+    <t xml:space="preserve">yesno</t>
+  </si>
+  <si>
+    <t xml:space="preserve">yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No</t>
+  </si>
+  <si>
+    <t xml:space="preserve">yesnodk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Don’t know</t>
+  </si>
+  <si>
+    <t xml:space="preserve">occupation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">agriculture</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agriculture</t>
+  </si>
+  <si>
+    <t xml:space="preserve">army</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Army</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bank employee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">business</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Business (own business)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">conductor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conductor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">construction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Construction worker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">craft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Craftsmanship (statues, tailor, etc)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">daily_wage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daily wage labourer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">occucpation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">domestic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Domestic work (maid, etc.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">driver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Driver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">factory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Factory worker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gvt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Government employee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hotel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hotel / restaurant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">housework</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Housework (in own house)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ngo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NGO worker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">office</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Office (salaried desk job)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pensioner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">police</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Police</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shopkeeper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shop keeper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">teacher_gvt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teacher (government)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">teacher_pvt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teacher (private)</t>
   </si>
   <si>
     <t xml:space="preserve">other</t>
@@ -126,171 +258,6 @@
     <t xml:space="preserve">Other</t>
   </si>
   <si>
-    <t xml:space="preserve">notapplicable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not applicable/No one</t>
-  </si>
-  <si>
-    <t xml:space="preserve">yesno</t>
-  </si>
-  <si>
-    <t xml:space="preserve">yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No</t>
-  </si>
-  <si>
-    <t xml:space="preserve">yesnodk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Don’t know</t>
-  </si>
-  <si>
-    <t xml:space="preserve">occupation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">agriculture</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agriculture</t>
-  </si>
-  <si>
-    <t xml:space="preserve">army</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Army</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bank employee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">business</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Business (own business)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">conductor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conductor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">construction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Construction worker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">craft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Craftsmanship (statues, tailor, etc)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">daily_wage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily wage labourer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">occucpation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">domestic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Domestic work (maid, etc.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">driver</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Driver</t>
-  </si>
-  <si>
-    <t xml:space="preserve">factory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Factory worker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gvt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Government employee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hotel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hotel / restaurant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">housework</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Housework (in own house)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ngo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NGO worker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">office</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Office (salaried desk job)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pension</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pensioner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">police</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Police</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shopkeeper</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shop keeper</t>
-  </si>
-  <si>
-    <t xml:space="preserve">teacher_gvt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teacher (government)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">teacher_pvt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teacher (private)</t>
-  </si>
-  <si>
     <t xml:space="preserve">relationtorespondent</t>
   </si>
   <si>
@@ -372,105 +339,6 @@
     <t xml:space="preserve">money refused</t>
   </si>
   <si>
-    <t xml:space="preserve">agree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">agree1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strongly disagree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">agree2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Somewhat disagree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">agree3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Neither agree or disagree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">agree4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Somewhat agree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">agree5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strongly agree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">apply</t>
-  </si>
-  <si>
-    <t xml:space="preserve">apply1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">does not apply at all (I)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">apply2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">applies a bit  (II)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">apply3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">applies somewhat (III)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">apply4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">applies mostly (IIII)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">apply5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">applies completely (IIIII)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">risk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">risk1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">not at all willing to take risks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">risk2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">a bit willing to take risks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">risk3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">somewhat willing to take risks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">risk4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mostly willing to take risks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">risk5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">very willing to take risks</t>
-  </si>
-  <si>
     <t xml:space="preserve">edu</t>
   </si>
   <si>
@@ -529,78 +397,6 @@
   </si>
   <si>
     <t xml:space="preserve">Higher than masters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">trustopt1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">everybody can be trusted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">many people can be trusted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">some people can be trusted and sometimes you have to be careful in dealing with most people</t>
-  </si>
-  <si>
-    <t xml:space="preserve">you have to be careful in dealing with many people</t>
-  </si>
-  <si>
-    <t xml:space="preserve">you have to be careful in dealing with everybody</t>
-  </si>
-  <si>
-    <t xml:space="preserve">trustopt2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">everybody will be fair</t>
-  </si>
-  <si>
-    <t xml:space="preserve">many people would be fair</t>
-  </si>
-  <si>
-    <t xml:space="preserve">some people would try to take advantage and some would be fair</t>
-  </si>
-  <si>
-    <t xml:space="preserve">many people would try to take adavantage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">everybody would try to take adavantage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">trustopt3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">everybody tries to be helfpul</t>
-  </si>
-  <si>
-    <t xml:space="preserve">many people try to be helpful</t>
-  </si>
-  <si>
-    <t xml:space="preserve">some people try to be helpful and some people just look out for themselves</t>
-  </si>
-  <si>
-    <t xml:space="preserve">many people just look out for themselves</t>
-  </si>
-  <si>
-    <t xml:space="preserve">everybody just looks out for themselves</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hardworkopt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">It's only a matter of hard work</t>
-  </si>
-  <si>
-    <t xml:space="preserve">It's more a matter of hard work</t>
-  </si>
-  <si>
-    <t xml:space="preserve">It's a matter of both hard work, luck, and connections.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">It's more a matter of luck and connections</t>
-  </si>
-  <si>
-    <t xml:space="preserve">It's only a matter of luck and connections</t>
   </si>
   <si>
     <t xml:space="preserve">style</t>
@@ -619,10 +415,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -656,12 +453,6 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Euphemia UCAS"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -731,15 +522,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -930,7 +721,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AMH999"/>
+  <dimension ref="A1:XFD999"/>
   <sheetFormatPr defaultColWidth="13.37109375" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="37.18"/>
@@ -1999,1046 +1790,7441 @@
       <c r="AMG1" s="3"/>
       <c r="AMH1" s="3"/>
     </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0"/>
+      <c r="B2" s="0"/>
+      <c r="C2" s="0"/>
+      <c r="D2" s="0"/>
+      <c r="E2" s="0"/>
+      <c r="F2" s="0"/>
+      <c r="G2" s="0"/>
+      <c r="H2" s="0"/>
+      <c r="I2" s="0"/>
+      <c r="XFC2" s="0"/>
+      <c r="XFD2" s="0"/>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0"/>
+      <c r="B3" s="0"/>
+      <c r="C3" s="0"/>
+      <c r="D3" s="0"/>
+      <c r="E3" s="0"/>
+      <c r="F3" s="0"/>
+      <c r="G3" s="0"/>
+      <c r="H3" s="0"/>
+      <c r="I3" s="0"/>
+      <c r="XFC3" s="0"/>
+      <c r="XFD3" s="0"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0"/>
+      <c r="B4" s="0"/>
+      <c r="C4" s="0"/>
+      <c r="D4" s="0"/>
+      <c r="E4" s="0"/>
+      <c r="F4" s="0"/>
+      <c r="G4" s="0"/>
+      <c r="H4" s="0"/>
+      <c r="I4" s="0"/>
+      <c r="XFC4" s="0"/>
+      <c r="XFD4" s="0"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0"/>
+      <c r="B5" s="0"/>
+      <c r="C5" s="0"/>
+      <c r="D5" s="0"/>
+      <c r="E5" s="0"/>
+      <c r="F5" s="0"/>
+      <c r="G5" s="0"/>
+      <c r="H5" s="0"/>
+      <c r="I5" s="0"/>
+      <c r="XFC5" s="0"/>
+      <c r="XFD5" s="0"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0"/>
+      <c r="B6" s="0"/>
+      <c r="C6" s="0"/>
+      <c r="D6" s="0"/>
+      <c r="E6" s="0"/>
+      <c r="F6" s="0"/>
+      <c r="G6" s="0"/>
+      <c r="H6" s="0"/>
+      <c r="I6" s="0"/>
+      <c r="XFC6" s="0"/>
+      <c r="XFD6" s="0"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0"/>
+      <c r="B7" s="0"/>
+      <c r="C7" s="0"/>
+      <c r="D7" s="0"/>
+      <c r="E7" s="0"/>
+      <c r="F7" s="0"/>
+      <c r="G7" s="0"/>
+      <c r="H7" s="0"/>
+      <c r="I7" s="0"/>
+      <c r="XFC7" s="0"/>
+      <c r="XFD7" s="0"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0"/>
+      <c r="B8" s="0"/>
+      <c r="C8" s="0"/>
+      <c r="D8" s="0"/>
+      <c r="E8" s="0"/>
+      <c r="F8" s="0"/>
+      <c r="G8" s="0"/>
+      <c r="H8" s="0"/>
+      <c r="I8" s="0"/>
+      <c r="XFC8" s="0"/>
+      <c r="XFD8" s="0"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0"/>
+      <c r="B9" s="0"/>
+      <c r="C9" s="0"/>
+      <c r="D9" s="0"/>
+      <c r="E9" s="0"/>
+      <c r="F9" s="0"/>
+      <c r="G9" s="0"/>
+      <c r="H9" s="0"/>
+      <c r="I9" s="0"/>
+      <c r="XFC9" s="0"/>
+      <c r="XFD9" s="0"/>
+    </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O10" s="1"/>
+      <c r="A10" s="0"/>
+      <c r="B10" s="0"/>
+      <c r="C10" s="0"/>
+      <c r="D10" s="0"/>
+      <c r="E10" s="0"/>
+      <c r="F10" s="0"/>
+      <c r="G10" s="0"/>
+      <c r="H10" s="0"/>
+      <c r="I10" s="0"/>
+      <c r="XFC10" s="0"/>
+      <c r="XFD10" s="0"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0"/>
+      <c r="B11" s="0"/>
+      <c r="C11" s="0"/>
+      <c r="D11" s="0"/>
+      <c r="E11" s="0"/>
+      <c r="F11" s="0"/>
+      <c r="G11" s="0"/>
+      <c r="H11" s="0"/>
+      <c r="I11" s="0"/>
+      <c r="XFC11" s="0"/>
+      <c r="XFD11" s="0"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0"/>
+      <c r="B12" s="0"/>
+      <c r="C12" s="0"/>
+      <c r="D12" s="0"/>
+      <c r="E12" s="0"/>
+      <c r="F12" s="0"/>
+      <c r="G12" s="0"/>
+      <c r="H12" s="0"/>
+      <c r="I12" s="0"/>
+      <c r="XFC12" s="0"/>
+      <c r="XFD12" s="0"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0"/>
+      <c r="B13" s="0"/>
+      <c r="C13" s="0"/>
+      <c r="D13" s="0"/>
+      <c r="E13" s="0"/>
+      <c r="F13" s="0"/>
+      <c r="G13" s="0"/>
+      <c r="H13" s="0"/>
+      <c r="I13" s="0"/>
+      <c r="XFC13" s="0"/>
+      <c r="XFD13" s="0"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0"/>
+      <c r="B14" s="0"/>
+      <c r="C14" s="0"/>
+      <c r="D14" s="0"/>
+      <c r="E14" s="0"/>
+      <c r="F14" s="0"/>
+      <c r="G14" s="0"/>
+      <c r="H14" s="0"/>
+      <c r="I14" s="0"/>
+      <c r="XFC14" s="0"/>
+      <c r="XFD14" s="0"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0"/>
+      <c r="B15" s="0"/>
+      <c r="C15" s="0"/>
+      <c r="D15" s="0"/>
+      <c r="E15" s="0"/>
+      <c r="F15" s="0"/>
+      <c r="G15" s="0"/>
+      <c r="H15" s="0"/>
+      <c r="I15" s="0"/>
+      <c r="XFC15" s="0"/>
+      <c r="XFD15" s="0"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0"/>
+      <c r="B16" s="0"/>
+      <c r="C16" s="0"/>
+      <c r="D16" s="0"/>
+      <c r="E16" s="0"/>
+      <c r="F16" s="0"/>
+      <c r="G16" s="0"/>
+      <c r="H16" s="0"/>
+      <c r="I16" s="0"/>
+      <c r="XFC16" s="0"/>
+      <c r="XFD16" s="0"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0"/>
+      <c r="B17" s="0"/>
+      <c r="C17" s="0"/>
+      <c r="D17" s="0"/>
+      <c r="E17" s="0"/>
+      <c r="F17" s="0"/>
+      <c r="G17" s="0"/>
+      <c r="H17" s="0"/>
+      <c r="I17" s="0"/>
+      <c r="XFC17" s="0"/>
+      <c r="XFD17" s="0"/>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0"/>
+      <c r="B18" s="0"/>
+      <c r="C18" s="0"/>
+      <c r="D18" s="0"/>
+      <c r="E18" s="0"/>
+      <c r="F18" s="0"/>
+      <c r="G18" s="0"/>
+      <c r="H18" s="0"/>
+      <c r="I18" s="0"/>
+      <c r="XFC18" s="0"/>
+      <c r="XFD18" s="0"/>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0"/>
+      <c r="B19" s="0"/>
+      <c r="C19" s="0"/>
+      <c r="D19" s="0"/>
+      <c r="E19" s="0"/>
+      <c r="F19" s="0"/>
+      <c r="G19" s="0"/>
+      <c r="H19" s="0"/>
+      <c r="I19" s="0"/>
+      <c r="XFC19" s="0"/>
+      <c r="XFD19" s="0"/>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0"/>
+      <c r="B20" s="0"/>
+      <c r="C20" s="0"/>
+      <c r="D20" s="0"/>
+      <c r="E20" s="0"/>
+      <c r="F20" s="0"/>
+      <c r="G20" s="0"/>
+      <c r="H20" s="0"/>
+      <c r="I20" s="0"/>
+      <c r="XFC20" s="0"/>
+      <c r="XFD20" s="0"/>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0"/>
+      <c r="B21" s="0"/>
+      <c r="C21" s="0"/>
+      <c r="D21" s="0"/>
+      <c r="E21" s="0"/>
+      <c r="F21" s="0"/>
+      <c r="G21" s="0"/>
+      <c r="H21" s="0"/>
+      <c r="I21" s="0"/>
+      <c r="XFC21" s="0"/>
+      <c r="XFD21" s="0"/>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0"/>
+      <c r="B22" s="0"/>
+      <c r="C22" s="0"/>
+      <c r="D22" s="0"/>
+      <c r="E22" s="0"/>
+      <c r="F22" s="0"/>
+      <c r="G22" s="0"/>
+      <c r="H22" s="0"/>
+      <c r="I22" s="0"/>
+      <c r="XFC22" s="0"/>
+      <c r="XFD22" s="0"/>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0"/>
+      <c r="B23" s="0"/>
+      <c r="C23" s="0"/>
+      <c r="D23" s="0"/>
+      <c r="E23" s="0"/>
+      <c r="F23" s="0"/>
+      <c r="G23" s="0"/>
+      <c r="H23" s="0"/>
+      <c r="I23" s="0"/>
+      <c r="XFC23" s="0"/>
+      <c r="XFD23" s="0"/>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0"/>
+      <c r="B24" s="0"/>
+      <c r="C24" s="0"/>
+      <c r="D24" s="0"/>
+      <c r="E24" s="0"/>
+      <c r="F24" s="0"/>
+      <c r="G24" s="0"/>
+      <c r="H24" s="0"/>
+      <c r="I24" s="0"/>
+      <c r="XFC24" s="0"/>
+      <c r="XFD24" s="0"/>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0"/>
+      <c r="B25" s="0"/>
+      <c r="C25" s="0"/>
+      <c r="D25" s="0"/>
+      <c r="E25" s="0"/>
+      <c r="F25" s="0"/>
+      <c r="G25" s="0"/>
+      <c r="H25" s="0"/>
+      <c r="I25" s="0"/>
+      <c r="XFC25" s="0"/>
+      <c r="XFD25" s="0"/>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0"/>
+      <c r="B26" s="0"/>
+      <c r="C26" s="0"/>
+      <c r="D26" s="0"/>
+      <c r="E26" s="0"/>
+      <c r="F26" s="0"/>
+      <c r="G26" s="0"/>
+      <c r="H26" s="0"/>
+      <c r="I26" s="0"/>
+      <c r="XFC26" s="0"/>
+      <c r="XFD26" s="0"/>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="0"/>
+      <c r="B27" s="0"/>
+      <c r="C27" s="0"/>
+      <c r="D27" s="0"/>
+      <c r="E27" s="0"/>
+      <c r="F27" s="0"/>
+      <c r="G27" s="0"/>
+      <c r="H27" s="0"/>
+      <c r="I27" s="0"/>
+      <c r="XFC27" s="0"/>
+      <c r="XFD27" s="0"/>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="0"/>
+      <c r="B28" s="0"/>
+      <c r="C28" s="0"/>
+      <c r="D28" s="0"/>
+      <c r="E28" s="0"/>
+      <c r="F28" s="0"/>
+      <c r="G28" s="0"/>
+      <c r="H28" s="0"/>
+      <c r="I28" s="0"/>
+      <c r="XFC28" s="0"/>
+      <c r="XFD28" s="0"/>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="0"/>
+      <c r="B29" s="0"/>
+      <c r="C29" s="0"/>
+      <c r="D29" s="0"/>
+      <c r="E29" s="0"/>
+      <c r="F29" s="0"/>
+      <c r="G29" s="0"/>
+      <c r="H29" s="0"/>
+      <c r="I29" s="0"/>
+      <c r="XFC29" s="0"/>
+      <c r="XFD29" s="0"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="0"/>
+      <c r="B30" s="0"/>
+      <c r="C30" s="0"/>
+      <c r="D30" s="0"/>
+      <c r="E30" s="0"/>
+      <c r="F30" s="0"/>
+      <c r="G30" s="0"/>
+      <c r="H30" s="0"/>
+      <c r="I30" s="0"/>
+      <c r="XFC30" s="0"/>
+      <c r="XFD30" s="0"/>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="0"/>
+      <c r="B31" s="0"/>
+      <c r="C31" s="0"/>
+      <c r="D31" s="0"/>
+      <c r="E31" s="0"/>
+      <c r="F31" s="0"/>
+      <c r="G31" s="0"/>
+      <c r="H31" s="0"/>
+      <c r="I31" s="0"/>
+      <c r="XFC31" s="0"/>
+      <c r="XFD31" s="0"/>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="0"/>
+      <c r="B32" s="0"/>
+      <c r="C32" s="0"/>
+      <c r="D32" s="0"/>
+      <c r="E32" s="0"/>
+      <c r="F32" s="0"/>
+      <c r="G32" s="0"/>
+      <c r="H32" s="0"/>
+      <c r="I32" s="0"/>
+      <c r="XFC32" s="0"/>
+      <c r="XFD32" s="0"/>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="0"/>
+      <c r="B33" s="0"/>
+      <c r="C33" s="0"/>
+      <c r="D33" s="0"/>
+      <c r="E33" s="0"/>
+      <c r="F33" s="0"/>
+      <c r="G33" s="0"/>
+      <c r="H33" s="0"/>
+      <c r="I33" s="0"/>
+      <c r="XFC33" s="0"/>
+      <c r="XFD33" s="0"/>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="0"/>
+      <c r="B34" s="0"/>
+      <c r="C34" s="0"/>
+      <c r="D34" s="0"/>
+      <c r="E34" s="0"/>
+      <c r="F34" s="0"/>
+      <c r="G34" s="0"/>
+      <c r="H34" s="0"/>
+      <c r="I34" s="0"/>
+      <c r="XFC34" s="0"/>
+      <c r="XFD34" s="0"/>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="0"/>
+      <c r="B35" s="0"/>
+      <c r="C35" s="0"/>
+      <c r="D35" s="0"/>
+      <c r="E35" s="0"/>
+      <c r="F35" s="0"/>
+      <c r="G35" s="0"/>
+      <c r="H35" s="0"/>
+      <c r="I35" s="0"/>
+      <c r="XFC35" s="0"/>
+      <c r="XFD35" s="0"/>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="0"/>
+      <c r="B36" s="0"/>
+      <c r="C36" s="0"/>
+      <c r="D36" s="0"/>
+      <c r="E36" s="0"/>
+      <c r="F36" s="0"/>
+      <c r="G36" s="0"/>
+      <c r="H36" s="0"/>
+      <c r="I36" s="0"/>
+      <c r="XFC36" s="0"/>
+      <c r="XFD36" s="0"/>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="0"/>
+      <c r="B37" s="0"/>
+      <c r="C37" s="0"/>
+      <c r="D37" s="0"/>
+      <c r="E37" s="0"/>
+      <c r="F37" s="0"/>
+      <c r="G37" s="0"/>
+      <c r="H37" s="0"/>
+      <c r="I37" s="0"/>
+      <c r="XFC37" s="0"/>
+      <c r="XFD37" s="0"/>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="0"/>
+      <c r="B38" s="0"/>
+      <c r="C38" s="0"/>
+      <c r="D38" s="0"/>
+      <c r="E38" s="0"/>
+      <c r="F38" s="0"/>
+      <c r="G38" s="0"/>
+      <c r="H38" s="0"/>
+      <c r="I38" s="0"/>
+      <c r="XFC38" s="0"/>
+      <c r="XFD38" s="0"/>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="0"/>
+      <c r="B39" s="0"/>
+      <c r="C39" s="0"/>
+      <c r="D39" s="0"/>
+      <c r="E39" s="0"/>
+      <c r="F39" s="0"/>
+      <c r="G39" s="0"/>
+      <c r="H39" s="0"/>
+      <c r="I39" s="0"/>
+      <c r="XFC39" s="0"/>
+      <c r="XFD39" s="0"/>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="0"/>
+      <c r="B40" s="0"/>
+      <c r="C40" s="0"/>
+      <c r="D40" s="0"/>
+      <c r="E40" s="0"/>
+      <c r="F40" s="0"/>
+      <c r="G40" s="0"/>
+      <c r="H40" s="0"/>
+      <c r="I40" s="0"/>
+      <c r="XFC40" s="0"/>
+      <c r="XFD40" s="0"/>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="0"/>
+      <c r="B41" s="0"/>
+      <c r="C41" s="0"/>
+      <c r="D41" s="0"/>
+      <c r="E41" s="0"/>
+      <c r="F41" s="0"/>
+      <c r="G41" s="0"/>
+      <c r="H41" s="0"/>
+      <c r="I41" s="0"/>
+      <c r="XFC41" s="0"/>
+      <c r="XFD41" s="0"/>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="0"/>
+      <c r="B42" s="0"/>
+      <c r="C42" s="0"/>
+      <c r="D42" s="0"/>
+      <c r="E42" s="0"/>
+      <c r="F42" s="0"/>
+      <c r="G42" s="0"/>
+      <c r="H42" s="0"/>
+      <c r="I42" s="0"/>
+      <c r="XFC42" s="0"/>
+      <c r="XFD42" s="0"/>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="0"/>
+      <c r="B43" s="0"/>
+      <c r="C43" s="0"/>
+      <c r="D43" s="0"/>
+      <c r="E43" s="0"/>
+      <c r="F43" s="0"/>
+      <c r="G43" s="0"/>
+      <c r="H43" s="0"/>
+      <c r="I43" s="0"/>
+      <c r="XFC43" s="0"/>
+      <c r="XFD43" s="0"/>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="0"/>
+      <c r="B44" s="0"/>
+      <c r="C44" s="0"/>
+      <c r="D44" s="0"/>
+      <c r="E44" s="0"/>
+      <c r="F44" s="0"/>
+      <c r="G44" s="0"/>
+      <c r="H44" s="0"/>
+      <c r="I44" s="0"/>
+      <c r="XFC44" s="0"/>
+      <c r="XFD44" s="0"/>
+    </row>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="0"/>
+      <c r="B45" s="0"/>
+      <c r="C45" s="0"/>
+      <c r="D45" s="0"/>
+      <c r="E45" s="0"/>
+      <c r="F45" s="0"/>
+      <c r="G45" s="0"/>
+      <c r="H45" s="0"/>
+      <c r="I45" s="0"/>
+      <c r="XFC45" s="0"/>
+      <c r="XFD45" s="0"/>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="0"/>
+      <c r="B46" s="0"/>
+      <c r="C46" s="0"/>
+      <c r="D46" s="0"/>
+      <c r="E46" s="0"/>
+      <c r="F46" s="0"/>
+      <c r="G46" s="0"/>
+      <c r="H46" s="0"/>
+      <c r="I46" s="0"/>
+      <c r="XFC46" s="0"/>
+      <c r="XFD46" s="0"/>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="0"/>
+      <c r="B47" s="0"/>
+      <c r="C47" s="0"/>
+      <c r="D47" s="0"/>
+      <c r="E47" s="0"/>
+      <c r="F47" s="0"/>
+      <c r="G47" s="0"/>
+      <c r="H47" s="0"/>
+      <c r="I47" s="0"/>
+      <c r="XFC47" s="0"/>
+      <c r="XFD47" s="0"/>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="0"/>
+      <c r="B48" s="0"/>
+      <c r="C48" s="0"/>
+      <c r="D48" s="0"/>
+      <c r="E48" s="0"/>
+      <c r="F48" s="0"/>
+      <c r="G48" s="0"/>
+      <c r="H48" s="0"/>
+      <c r="I48" s="0"/>
+      <c r="XFC48" s="0"/>
+      <c r="XFD48" s="0"/>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="0"/>
+      <c r="B49" s="0"/>
+      <c r="C49" s="0"/>
+      <c r="D49" s="0"/>
+      <c r="E49" s="0"/>
+      <c r="F49" s="0"/>
+      <c r="G49" s="0"/>
+      <c r="H49" s="0"/>
+      <c r="I49" s="0"/>
+      <c r="XFC49" s="0"/>
+      <c r="XFD49" s="0"/>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="0"/>
+      <c r="B50" s="0"/>
+      <c r="C50" s="0"/>
+      <c r="D50" s="0"/>
+      <c r="E50" s="0"/>
+      <c r="F50" s="0"/>
+      <c r="G50" s="0"/>
+      <c r="H50" s="0"/>
+      <c r="I50" s="0"/>
+      <c r="XFC50" s="0"/>
+      <c r="XFD50" s="0"/>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="0"/>
+      <c r="B51" s="0"/>
+      <c r="C51" s="0"/>
+      <c r="D51" s="0"/>
+      <c r="E51" s="0"/>
+      <c r="F51" s="0"/>
+      <c r="G51" s="0"/>
+      <c r="H51" s="0"/>
+      <c r="I51" s="0"/>
+      <c r="XFC51" s="0"/>
+      <c r="XFD51" s="0"/>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="0"/>
+      <c r="B52" s="0"/>
+      <c r="C52" s="0"/>
+      <c r="D52" s="0"/>
+      <c r="E52" s="0"/>
+      <c r="F52" s="0"/>
+      <c r="G52" s="0"/>
+      <c r="H52" s="0"/>
+      <c r="I52" s="0"/>
+      <c r="XFC52" s="0"/>
+      <c r="XFD52" s="0"/>
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="0"/>
+      <c r="B53" s="0"/>
+      <c r="C53" s="0"/>
+      <c r="D53" s="0"/>
+      <c r="E53" s="0"/>
+      <c r="F53" s="0"/>
+      <c r="G53" s="0"/>
+      <c r="H53" s="0"/>
+      <c r="I53" s="0"/>
+      <c r="XFC53" s="0"/>
+      <c r="XFD53" s="0"/>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="0"/>
+      <c r="B54" s="0"/>
+      <c r="C54" s="0"/>
+      <c r="D54" s="0"/>
+      <c r="E54" s="0"/>
+      <c r="F54" s="0"/>
+      <c r="G54" s="0"/>
+      <c r="H54" s="0"/>
+      <c r="I54" s="0"/>
+      <c r="XFC54" s="0"/>
+      <c r="XFD54" s="0"/>
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="0"/>
+      <c r="B55" s="0"/>
+      <c r="C55" s="0"/>
+      <c r="D55" s="0"/>
+      <c r="E55" s="0"/>
+      <c r="F55" s="0"/>
+      <c r="G55" s="0"/>
+      <c r="H55" s="0"/>
+      <c r="I55" s="0"/>
+      <c r="XFC55" s="0"/>
+      <c r="XFD55" s="0"/>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="0"/>
+      <c r="B56" s="0"/>
+      <c r="C56" s="0"/>
+      <c r="D56" s="0"/>
+      <c r="E56" s="0"/>
+      <c r="F56" s="0"/>
+      <c r="G56" s="0"/>
+      <c r="H56" s="0"/>
+      <c r="I56" s="0"/>
+      <c r="XFC56" s="0"/>
+      <c r="XFD56" s="0"/>
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="0"/>
+      <c r="B57" s="0"/>
+      <c r="C57" s="0"/>
+      <c r="D57" s="0"/>
+      <c r="E57" s="0"/>
+      <c r="F57" s="0"/>
+      <c r="G57" s="0"/>
+      <c r="H57" s="0"/>
+      <c r="I57" s="0"/>
+      <c r="XFC57" s="0"/>
+      <c r="XFD57" s="0"/>
+    </row>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="0"/>
+      <c r="B58" s="0"/>
+      <c r="C58" s="0"/>
+      <c r="D58" s="0"/>
+      <c r="E58" s="0"/>
+      <c r="F58" s="0"/>
+      <c r="G58" s="0"/>
+      <c r="H58" s="0"/>
+      <c r="I58" s="0"/>
+      <c r="XFC58" s="0"/>
+      <c r="XFD58" s="0"/>
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="0"/>
+      <c r="B59" s="0"/>
+      <c r="C59" s="0"/>
+      <c r="D59" s="0"/>
+      <c r="E59" s="0"/>
+      <c r="F59" s="0"/>
+      <c r="G59" s="0"/>
+      <c r="H59" s="0"/>
+      <c r="I59" s="0"/>
+      <c r="XFC59" s="0"/>
+      <c r="XFD59" s="0"/>
+    </row>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="0"/>
+      <c r="B60" s="0"/>
+      <c r="C60" s="0"/>
+      <c r="D60" s="0"/>
+      <c r="E60" s="0"/>
+      <c r="F60" s="0"/>
+      <c r="G60" s="0"/>
+      <c r="H60" s="0"/>
+      <c r="I60" s="0"/>
+      <c r="XFC60" s="0"/>
+      <c r="XFD60" s="0"/>
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="0"/>
+      <c r="B61" s="0"/>
+      <c r="C61" s="0"/>
+      <c r="D61" s="0"/>
+      <c r="E61" s="0"/>
+      <c r="F61" s="0"/>
+      <c r="G61" s="0"/>
+      <c r="H61" s="0"/>
+      <c r="I61" s="0"/>
+      <c r="XFC61" s="0"/>
+      <c r="XFD61" s="0"/>
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="0"/>
+      <c r="B62" s="0"/>
+      <c r="C62" s="0"/>
+      <c r="D62" s="0"/>
+      <c r="E62" s="0"/>
+      <c r="F62" s="0"/>
+      <c r="G62" s="0"/>
+      <c r="H62" s="0"/>
+      <c r="I62" s="0"/>
+      <c r="XFC62" s="0"/>
+      <c r="XFD62" s="0"/>
+    </row>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="0"/>
+      <c r="B63" s="0"/>
+      <c r="C63" s="0"/>
+      <c r="D63" s="0"/>
+      <c r="E63" s="0"/>
+      <c r="F63" s="0"/>
+      <c r="G63" s="0"/>
+      <c r="H63" s="0"/>
+      <c r="I63" s="0"/>
+      <c r="XFC63" s="0"/>
+      <c r="XFD63" s="0"/>
+    </row>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="0"/>
+      <c r="B64" s="0"/>
+      <c r="C64" s="0"/>
+      <c r="D64" s="0"/>
+      <c r="E64" s="0"/>
+      <c r="F64" s="0"/>
+      <c r="G64" s="0"/>
+      <c r="H64" s="0"/>
+      <c r="I64" s="0"/>
+      <c r="XFC64" s="0"/>
+      <c r="XFD64" s="0"/>
+    </row>
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="0"/>
+      <c r="B65" s="0"/>
+      <c r="C65" s="0"/>
+      <c r="D65" s="0"/>
+      <c r="E65" s="0"/>
+      <c r="F65" s="0"/>
+      <c r="G65" s="0"/>
+      <c r="H65" s="0"/>
+      <c r="I65" s="0"/>
+      <c r="XFC65" s="0"/>
+      <c r="XFD65" s="0"/>
+    </row>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="0"/>
+      <c r="B66" s="0"/>
+      <c r="C66" s="0"/>
+      <c r="D66" s="0"/>
+      <c r="E66" s="0"/>
+      <c r="F66" s="0"/>
+      <c r="G66" s="0"/>
+      <c r="H66" s="0"/>
+      <c r="I66" s="0"/>
+      <c r="XFC66" s="0"/>
+      <c r="XFD66" s="0"/>
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="0"/>
+      <c r="B67" s="0"/>
+      <c r="C67" s="0"/>
+      <c r="D67" s="0"/>
+      <c r="E67" s="0"/>
+      <c r="F67" s="0"/>
+      <c r="G67" s="0"/>
+      <c r="H67" s="0"/>
+      <c r="I67" s="0"/>
+      <c r="XFC67" s="0"/>
+      <c r="XFD67" s="0"/>
+    </row>
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="0"/>
+      <c r="B68" s="0"/>
+      <c r="C68" s="0"/>
+      <c r="D68" s="0"/>
+      <c r="E68" s="0"/>
+      <c r="F68" s="0"/>
+      <c r="G68" s="0"/>
+      <c r="H68" s="0"/>
+      <c r="I68" s="0"/>
+      <c r="XFC68" s="0"/>
+      <c r="XFD68" s="0"/>
+    </row>
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="0"/>
+      <c r="B69" s="0"/>
+      <c r="C69" s="0"/>
+      <c r="D69" s="0"/>
+      <c r="E69" s="0"/>
+      <c r="F69" s="0"/>
+      <c r="G69" s="0"/>
+      <c r="H69" s="0"/>
+      <c r="I69" s="0"/>
+      <c r="XFC69" s="0"/>
+      <c r="XFD69" s="0"/>
+    </row>
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="0"/>
+      <c r="B70" s="0"/>
+      <c r="C70" s="0"/>
+      <c r="D70" s="0"/>
+      <c r="E70" s="0"/>
+      <c r="F70" s="0"/>
+      <c r="G70" s="0"/>
+      <c r="H70" s="0"/>
+      <c r="I70" s="0"/>
+      <c r="XFC70" s="0"/>
+      <c r="XFD70" s="0"/>
+    </row>
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="0"/>
+      <c r="B71" s="0"/>
+      <c r="C71" s="0"/>
+      <c r="D71" s="0"/>
+      <c r="E71" s="0"/>
+      <c r="F71" s="0"/>
+      <c r="G71" s="0"/>
+      <c r="H71" s="0"/>
+      <c r="I71" s="0"/>
+      <c r="XFC71" s="0"/>
+      <c r="XFD71" s="0"/>
+    </row>
+    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="0"/>
+      <c r="B72" s="0"/>
+      <c r="C72" s="0"/>
+      <c r="D72" s="0"/>
+      <c r="E72" s="0"/>
+      <c r="F72" s="0"/>
+      <c r="G72" s="0"/>
+      <c r="H72" s="0"/>
+      <c r="I72" s="0"/>
+      <c r="XFC72" s="0"/>
+      <c r="XFD72" s="0"/>
+    </row>
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="0"/>
+      <c r="B73" s="0"/>
+      <c r="C73" s="0"/>
+      <c r="D73" s="0"/>
+      <c r="E73" s="0"/>
+      <c r="F73" s="0"/>
+      <c r="G73" s="0"/>
+      <c r="H73" s="0"/>
+      <c r="I73" s="0"/>
+      <c r="XFC73" s="0"/>
+      <c r="XFD73" s="0"/>
+    </row>
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="0"/>
+      <c r="B74" s="0"/>
+      <c r="C74" s="0"/>
+      <c r="D74" s="0"/>
+      <c r="E74" s="0"/>
+      <c r="F74" s="0"/>
+      <c r="G74" s="0"/>
+      <c r="H74" s="0"/>
+      <c r="I74" s="0"/>
+      <c r="XFC74" s="0"/>
+      <c r="XFD74" s="0"/>
+    </row>
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="0"/>
+      <c r="B75" s="0"/>
+      <c r="C75" s="0"/>
+      <c r="D75" s="0"/>
+      <c r="E75" s="0"/>
+      <c r="F75" s="0"/>
+      <c r="G75" s="0"/>
+      <c r="H75" s="0"/>
+      <c r="I75" s="0"/>
+      <c r="XFC75" s="0"/>
+      <c r="XFD75" s="0"/>
+    </row>
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="0"/>
+      <c r="B76" s="0"/>
+      <c r="C76" s="0"/>
+      <c r="D76" s="0"/>
+      <c r="E76" s="0"/>
+      <c r="F76" s="0"/>
+      <c r="G76" s="4"/>
+      <c r="H76" s="0"/>
+      <c r="I76" s="0"/>
+      <c r="XFC76" s="0"/>
+      <c r="XFD76" s="0"/>
+    </row>
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="0"/>
+      <c r="B77" s="0"/>
+      <c r="C77" s="0"/>
+      <c r="D77" s="0"/>
+      <c r="E77" s="0"/>
+      <c r="F77" s="0"/>
+      <c r="G77" s="0"/>
+      <c r="H77" s="0"/>
+      <c r="I77" s="0"/>
+      <c r="XFC77" s="0"/>
+      <c r="XFD77" s="0"/>
+    </row>
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="0"/>
+      <c r="B78" s="0"/>
+      <c r="C78" s="0"/>
+      <c r="D78" s="0"/>
+      <c r="E78" s="0"/>
+      <c r="F78" s="0"/>
+      <c r="G78" s="0"/>
+      <c r="H78" s="0"/>
+      <c r="I78" s="0"/>
+      <c r="XFC78" s="0"/>
+      <c r="XFD78" s="0"/>
+    </row>
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="0"/>
+      <c r="B79" s="0"/>
+      <c r="C79" s="0"/>
+      <c r="D79" s="0"/>
+      <c r="E79" s="0"/>
+      <c r="F79" s="0"/>
+      <c r="G79" s="0"/>
+      <c r="H79" s="0"/>
+      <c r="I79" s="0"/>
+      <c r="XFC79" s="0"/>
+      <c r="XFD79" s="0"/>
+    </row>
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="0"/>
+      <c r="B80" s="0"/>
+      <c r="C80" s="0"/>
+      <c r="D80" s="0"/>
+      <c r="E80" s="0"/>
+      <c r="F80" s="0"/>
+      <c r="G80" s="0"/>
+      <c r="H80" s="0"/>
+      <c r="I80" s="0"/>
+      <c r="XFC80" s="0"/>
+      <c r="XFD80" s="0"/>
+    </row>
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="0"/>
+      <c r="B81" s="0"/>
+      <c r="C81" s="0"/>
+      <c r="D81" s="0"/>
+      <c r="E81" s="0"/>
+      <c r="F81" s="0"/>
+      <c r="G81" s="0"/>
+      <c r="H81" s="0"/>
+      <c r="I81" s="0"/>
+      <c r="XFC81" s="0"/>
+      <c r="XFD81" s="0"/>
+    </row>
+    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="0"/>
+      <c r="B82" s="0"/>
+      <c r="C82" s="0"/>
+      <c r="D82" s="0"/>
+      <c r="E82" s="0"/>
+      <c r="F82" s="0"/>
+      <c r="G82" s="0"/>
+      <c r="H82" s="0"/>
+      <c r="I82" s="0"/>
+      <c r="XFC82" s="0"/>
+      <c r="XFD82" s="0"/>
+    </row>
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="0"/>
+      <c r="B83" s="0"/>
+      <c r="C83" s="0"/>
+      <c r="D83" s="0"/>
+      <c r="E83" s="0"/>
+      <c r="F83" s="0"/>
+      <c r="G83" s="0"/>
+      <c r="H83" s="0"/>
+      <c r="I83" s="0"/>
+      <c r="XFC83" s="0"/>
+      <c r="XFD83" s="0"/>
+    </row>
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="0"/>
+      <c r="B84" s="0"/>
+      <c r="C84" s="0"/>
+      <c r="D84" s="0"/>
+      <c r="E84" s="0"/>
+      <c r="F84" s="0"/>
+      <c r="G84" s="0"/>
+      <c r="H84" s="0"/>
+      <c r="I84" s="0"/>
+      <c r="XFC84" s="0"/>
+      <c r="XFD84" s="0"/>
+    </row>
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="0"/>
+      <c r="B85" s="0"/>
+      <c r="C85" s="0"/>
+      <c r="D85" s="0"/>
+      <c r="E85" s="0"/>
+      <c r="F85" s="0"/>
+      <c r="G85" s="0"/>
+      <c r="H85" s="0"/>
+      <c r="I85" s="0"/>
+      <c r="XFC85" s="0"/>
+      <c r="XFD85" s="0"/>
+    </row>
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="0"/>
+      <c r="B86" s="0"/>
+      <c r="C86" s="0"/>
+      <c r="D86" s="0"/>
+      <c r="E86" s="0"/>
+      <c r="F86" s="0"/>
+      <c r="G86" s="0"/>
+      <c r="H86" s="0"/>
+      <c r="I86" s="0"/>
+      <c r="XFC86" s="0"/>
+      <c r="XFD86" s="0"/>
+    </row>
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="0"/>
+      <c r="B87" s="0"/>
+      <c r="C87" s="0"/>
+      <c r="D87" s="0"/>
+      <c r="E87" s="0"/>
+      <c r="F87" s="0"/>
+      <c r="G87" s="0"/>
+      <c r="H87" s="0"/>
+      <c r="I87" s="0"/>
+      <c r="XFC87" s="0"/>
+      <c r="XFD87" s="0"/>
+    </row>
+    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="0"/>
+      <c r="B88" s="0"/>
+      <c r="C88" s="0"/>
+      <c r="D88" s="0"/>
+      <c r="E88" s="0"/>
+      <c r="F88" s="0"/>
+      <c r="G88" s="0"/>
+      <c r="H88" s="0"/>
+      <c r="I88" s="0"/>
+      <c r="XFC88" s="0"/>
+      <c r="XFD88" s="0"/>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J89" s="1"/>
-      <c r="M89" s="1"/>
+      <c r="A89" s="0"/>
+      <c r="B89" s="0"/>
+      <c r="C89" s="0"/>
+      <c r="D89" s="0"/>
+      <c r="E89" s="0"/>
+      <c r="F89" s="0"/>
+      <c r="G89" s="0"/>
+      <c r="H89" s="0"/>
+      <c r="I89" s="0"/>
+      <c r="XFC89" s="0"/>
+      <c r="XFD89" s="0"/>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K90" s="1"/>
+      <c r="A90" s="0"/>
+      <c r="B90" s="0"/>
+      <c r="C90" s="0"/>
+      <c r="D90" s="0"/>
+      <c r="E90" s="0"/>
+      <c r="F90" s="0"/>
+      <c r="G90" s="0"/>
+      <c r="H90" s="0"/>
+      <c r="I90" s="0"/>
+      <c r="XFC90" s="0"/>
+      <c r="XFD90" s="0"/>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K91" s="1"/>
+      <c r="A91" s="0"/>
+      <c r="B91" s="0"/>
+      <c r="C91" s="0"/>
+      <c r="D91" s="0"/>
+      <c r="E91" s="0"/>
+      <c r="F91" s="0"/>
+      <c r="G91" s="0"/>
+      <c r="H91" s="0"/>
+      <c r="I91" s="0"/>
+      <c r="XFC91" s="0"/>
+      <c r="XFD91" s="0"/>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K92" s="1"/>
+      <c r="A92" s="0"/>
+      <c r="B92" s="0"/>
+      <c r="C92" s="0"/>
+      <c r="D92" s="0"/>
+      <c r="E92" s="0"/>
+      <c r="F92" s="0"/>
+      <c r="G92" s="0"/>
+      <c r="H92" s="0"/>
+      <c r="I92" s="0"/>
+      <c r="XFC92" s="0"/>
+      <c r="XFD92" s="0"/>
+    </row>
+    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="0"/>
+      <c r="B93" s="0"/>
+      <c r="C93" s="0"/>
+      <c r="D93" s="0"/>
+      <c r="E93" s="0"/>
+      <c r="F93" s="0"/>
+      <c r="G93" s="0"/>
+      <c r="H93" s="0"/>
+      <c r="I93" s="0"/>
+      <c r="XFC93" s="0"/>
+      <c r="XFD93" s="0"/>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K94" s="1"/>
+      <c r="A94" s="0"/>
+      <c r="B94" s="0"/>
+      <c r="C94" s="0"/>
+      <c r="D94" s="0"/>
+      <c r="E94" s="0"/>
+      <c r="F94" s="0"/>
+      <c r="G94" s="0"/>
+      <c r="H94" s="0"/>
+      <c r="I94" s="0"/>
+      <c r="XFC94" s="0"/>
+      <c r="XFD94" s="0"/>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K95" s="1"/>
+      <c r="A95" s="0"/>
+      <c r="B95" s="0"/>
+      <c r="C95" s="0"/>
+      <c r="D95" s="0"/>
+      <c r="E95" s="0"/>
+      <c r="F95" s="0"/>
+      <c r="G95" s="0"/>
+      <c r="H95" s="0"/>
+      <c r="I95" s="0"/>
+      <c r="XFC95" s="0"/>
+      <c r="XFD95" s="0"/>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K96" s="1"/>
+      <c r="A96" s="0"/>
+      <c r="B96" s="0"/>
+      <c r="C96" s="0"/>
+      <c r="D96" s="0"/>
+      <c r="E96" s="0"/>
+      <c r="F96" s="0"/>
+      <c r="G96" s="0"/>
+      <c r="H96" s="0"/>
+      <c r="I96" s="0"/>
+      <c r="XFC96" s="0"/>
+      <c r="XFD96" s="0"/>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K97" s="1"/>
+      <c r="A97" s="0"/>
+      <c r="B97" s="0"/>
+      <c r="C97" s="0"/>
+      <c r="D97" s="0"/>
+      <c r="E97" s="0"/>
+      <c r="F97" s="0"/>
+      <c r="G97" s="0"/>
+      <c r="H97" s="0"/>
+      <c r="I97" s="0"/>
+      <c r="XFC97" s="0"/>
+      <c r="XFD97" s="0"/>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K98" s="1"/>
+      <c r="A98" s="0"/>
+      <c r="B98" s="0"/>
+      <c r="C98" s="0"/>
+      <c r="D98" s="0"/>
+      <c r="E98" s="0"/>
+      <c r="F98" s="0"/>
+      <c r="G98" s="0"/>
+      <c r="H98" s="0"/>
+      <c r="I98" s="0"/>
+      <c r="XFC98" s="0"/>
+      <c r="XFD98" s="0"/>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K99" s="1"/>
+      <c r="A99" s="0"/>
+      <c r="B99" s="0"/>
+      <c r="C99" s="0"/>
+      <c r="D99" s="0"/>
+      <c r="E99" s="0"/>
+      <c r="F99" s="0"/>
+      <c r="G99" s="0"/>
+      <c r="H99" s="0"/>
+      <c r="I99" s="0"/>
+      <c r="XFC99" s="0"/>
+      <c r="XFD99" s="0"/>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K100" s="1"/>
+      <c r="A100" s="0"/>
+      <c r="B100" s="0"/>
+      <c r="C100" s="0"/>
+      <c r="D100" s="0"/>
+      <c r="E100" s="0"/>
+      <c r="F100" s="0"/>
+      <c r="G100" s="0"/>
+      <c r="H100" s="0"/>
+      <c r="I100" s="0"/>
+      <c r="XFC100" s="0"/>
+      <c r="XFD100" s="0"/>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K101" s="1"/>
+      <c r="A101" s="0"/>
+      <c r="B101" s="0"/>
+      <c r="C101" s="0"/>
+      <c r="D101" s="0"/>
+      <c r="E101" s="0"/>
+      <c r="F101" s="0"/>
+      <c r="G101" s="0"/>
+      <c r="H101" s="0"/>
+      <c r="I101" s="0"/>
+      <c r="XFC101" s="0"/>
+      <c r="XFD101" s="0"/>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K102" s="1"/>
+      <c r="A102" s="0"/>
+      <c r="B102" s="0"/>
+      <c r="C102" s="0"/>
+      <c r="D102" s="0"/>
+      <c r="E102" s="0"/>
+      <c r="F102" s="0"/>
+      <c r="G102" s="0"/>
+      <c r="H102" s="0"/>
+      <c r="I102" s="0"/>
+      <c r="XFC102" s="0"/>
+      <c r="XFD102" s="0"/>
+    </row>
+    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="0"/>
+      <c r="B103" s="0"/>
+      <c r="C103" s="0"/>
+      <c r="D103" s="0"/>
+      <c r="E103" s="0"/>
+      <c r="F103" s="0"/>
+      <c r="G103" s="0"/>
+      <c r="H103" s="0"/>
+      <c r="I103" s="0"/>
+      <c r="XFC103" s="0"/>
+      <c r="XFD103" s="0"/>
+    </row>
+    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="0"/>
+      <c r="B104" s="0"/>
+      <c r="C104" s="0"/>
+      <c r="D104" s="0"/>
+      <c r="E104" s="0"/>
+      <c r="F104" s="0"/>
+      <c r="G104" s="0"/>
+      <c r="H104" s="0"/>
+      <c r="I104" s="0"/>
+      <c r="XFC104" s="0"/>
+      <c r="XFD104" s="0"/>
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J105" s="1"/>
+      <c r="A105" s="0"/>
+      <c r="B105" s="0"/>
+      <c r="C105" s="0"/>
+      <c r="D105" s="0"/>
+      <c r="E105" s="0"/>
+      <c r="F105" s="0"/>
+      <c r="G105" s="0"/>
+      <c r="H105" s="0"/>
+      <c r="I105" s="0"/>
+      <c r="XFC105" s="0"/>
+      <c r="XFD105" s="0"/>
+    </row>
+    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="0"/>
+      <c r="B106" s="0"/>
+      <c r="C106" s="0"/>
+      <c r="D106" s="0"/>
+      <c r="E106" s="0"/>
+      <c r="F106" s="0"/>
+      <c r="G106" s="0"/>
+      <c r="H106" s="0"/>
+      <c r="I106" s="0"/>
+      <c r="XFC106" s="0"/>
+      <c r="XFD106" s="0"/>
     </row>
     <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J107" s="1"/>
+      <c r="A107" s="0"/>
+      <c r="B107" s="0"/>
+      <c r="C107" s="0"/>
+      <c r="D107" s="0"/>
+      <c r="E107" s="0"/>
+      <c r="F107" s="0"/>
+      <c r="G107" s="0"/>
+      <c r="H107" s="0"/>
+      <c r="I107" s="0"/>
+      <c r="XFC107" s="0"/>
+      <c r="XFD107" s="0"/>
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J108" s="1"/>
+      <c r="A108" s="0"/>
+      <c r="B108" s="0"/>
+      <c r="C108" s="0"/>
+      <c r="D108" s="0"/>
+      <c r="E108" s="0"/>
+      <c r="F108" s="0"/>
+      <c r="G108" s="0"/>
+      <c r="H108" s="0"/>
+      <c r="I108" s="0"/>
+      <c r="XFC108" s="0"/>
+      <c r="XFD108" s="0"/>
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J109" s="1"/>
+      <c r="A109" s="0"/>
+      <c r="B109" s="0"/>
+      <c r="C109" s="0"/>
+      <c r="D109" s="0"/>
+      <c r="E109" s="0"/>
+      <c r="F109" s="0"/>
+      <c r="G109" s="0"/>
+      <c r="H109" s="0"/>
+      <c r="I109" s="0"/>
+      <c r="XFC109" s="0"/>
+      <c r="XFD109" s="0"/>
     </row>
     <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J110" s="1"/>
+      <c r="A110" s="0"/>
+      <c r="B110" s="0"/>
+      <c r="C110" s="0"/>
+      <c r="D110" s="0"/>
+      <c r="E110" s="0"/>
+      <c r="F110" s="0"/>
+      <c r="G110" s="0"/>
+      <c r="H110" s="0"/>
+      <c r="I110" s="0"/>
+      <c r="XFC110" s="0"/>
+      <c r="XFD110" s="0"/>
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J111" s="1"/>
+      <c r="A111" s="0"/>
+      <c r="B111" s="0"/>
+      <c r="C111" s="0"/>
+      <c r="D111" s="0"/>
+      <c r="E111" s="0"/>
+      <c r="F111" s="0"/>
+      <c r="G111" s="0"/>
+      <c r="H111" s="0"/>
+      <c r="I111" s="0"/>
+      <c r="XFC111" s="0"/>
+      <c r="XFD111" s="0"/>
     </row>
     <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J112" s="1"/>
+      <c r="A112" s="0"/>
+      <c r="B112" s="0"/>
+      <c r="C112" s="0"/>
+      <c r="D112" s="0"/>
+      <c r="E112" s="0"/>
+      <c r="F112" s="0"/>
+      <c r="G112" s="0"/>
+      <c r="H112" s="0"/>
+      <c r="I112" s="0"/>
+      <c r="XFC112" s="0"/>
+      <c r="XFD112" s="0"/>
     </row>
     <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J113" s="1"/>
+      <c r="A113" s="0"/>
+      <c r="B113" s="0"/>
+      <c r="C113" s="0"/>
+      <c r="D113" s="0"/>
+      <c r="E113" s="0"/>
+      <c r="F113" s="0"/>
+      <c r="G113" s="0"/>
+      <c r="H113" s="0"/>
+      <c r="I113" s="0"/>
+      <c r="XFC113" s="0"/>
+      <c r="XFD113" s="0"/>
     </row>
     <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J114" s="1"/>
+      <c r="A114" s="0"/>
+      <c r="B114" s="0"/>
+      <c r="C114" s="0"/>
+      <c r="D114" s="0"/>
+      <c r="E114" s="0"/>
+      <c r="F114" s="0"/>
+      <c r="G114" s="0"/>
+      <c r="H114" s="0"/>
+      <c r="I114" s="0"/>
+      <c r="XFC114" s="0"/>
+      <c r="XFD114" s="0"/>
     </row>
     <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J115" s="1"/>
+      <c r="A115" s="0"/>
+      <c r="B115" s="0"/>
+      <c r="C115" s="0"/>
+      <c r="D115" s="0"/>
+      <c r="E115" s="0"/>
+      <c r="F115" s="0"/>
+      <c r="G115" s="0"/>
+      <c r="H115" s="0"/>
+      <c r="I115" s="0"/>
+      <c r="XFC115" s="0"/>
+      <c r="XFD115" s="0"/>
+    </row>
+    <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="0"/>
+      <c r="B116" s="0"/>
+      <c r="C116" s="0"/>
+      <c r="D116" s="0"/>
+      <c r="E116" s="0"/>
+      <c r="F116" s="0"/>
+      <c r="G116" s="0"/>
+      <c r="H116" s="0"/>
+      <c r="I116" s="0"/>
+      <c r="XFC116" s="0"/>
+      <c r="XFD116" s="0"/>
+    </row>
+    <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="0"/>
+      <c r="B117" s="0"/>
+      <c r="C117" s="0"/>
+      <c r="D117" s="0"/>
+      <c r="E117" s="0"/>
+      <c r="F117" s="0"/>
+      <c r="G117" s="0"/>
+      <c r="H117" s="0"/>
+      <c r="I117" s="0"/>
+      <c r="XFC117" s="0"/>
+      <c r="XFD117" s="0"/>
     </row>
     <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J118" s="1"/>
+      <c r="A118" s="0"/>
+      <c r="B118" s="0"/>
+      <c r="C118" s="0"/>
+      <c r="D118" s="0"/>
+      <c r="E118" s="0"/>
+      <c r="F118" s="0"/>
+      <c r="G118" s="4"/>
+      <c r="H118" s="0"/>
+      <c r="I118" s="0"/>
+      <c r="XFC118" s="0"/>
+      <c r="XFD118" s="0"/>
+    </row>
+    <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="0"/>
+      <c r="B119" s="0"/>
+      <c r="C119" s="0"/>
+      <c r="D119" s="0"/>
+      <c r="E119" s="0"/>
+      <c r="F119" s="0"/>
+      <c r="G119" s="0"/>
+      <c r="H119" s="0"/>
+      <c r="I119" s="0"/>
+      <c r="XFC119" s="0"/>
+      <c r="XFD119" s="0"/>
     </row>
     <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K120" s="1"/>
+      <c r="A120" s="0"/>
+      <c r="B120" s="0"/>
+      <c r="C120" s="0"/>
+      <c r="D120" s="0"/>
+      <c r="E120" s="0"/>
+      <c r="F120" s="0"/>
+      <c r="G120" s="0"/>
+      <c r="H120" s="0"/>
+      <c r="I120" s="0"/>
+      <c r="XFC120" s="0"/>
+      <c r="XFD120" s="0"/>
     </row>
     <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K121" s="1"/>
+      <c r="A121" s="0"/>
+      <c r="B121" s="0"/>
+      <c r="C121" s="0"/>
+      <c r="D121" s="0"/>
+      <c r="E121" s="0"/>
+      <c r="F121" s="0"/>
+      <c r="G121" s="0"/>
+      <c r="H121" s="0"/>
+      <c r="I121" s="0"/>
+      <c r="XFC121" s="0"/>
+      <c r="XFD121" s="0"/>
     </row>
     <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K122" s="1"/>
+      <c r="A122" s="0"/>
+      <c r="B122" s="0"/>
+      <c r="C122" s="0"/>
+      <c r="D122" s="0"/>
+      <c r="E122" s="0"/>
+      <c r="F122" s="0"/>
+      <c r="G122" s="0"/>
+      <c r="H122" s="0"/>
+      <c r="I122" s="0"/>
+      <c r="XFC122" s="0"/>
+      <c r="XFD122" s="0"/>
+    </row>
+    <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="0"/>
+      <c r="B123" s="0"/>
+      <c r="C123" s="0"/>
+      <c r="D123" s="0"/>
+      <c r="E123" s="0"/>
+      <c r="F123" s="0"/>
+      <c r="G123" s="0"/>
+      <c r="H123" s="0"/>
+      <c r="I123" s="0"/>
+      <c r="XFC123" s="0"/>
+      <c r="XFD123" s="0"/>
     </row>
     <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K124" s="1"/>
+      <c r="A124" s="0"/>
+      <c r="B124" s="0"/>
+      <c r="C124" s="0"/>
+      <c r="D124" s="0"/>
+      <c r="E124" s="0"/>
+      <c r="F124" s="0"/>
+      <c r="G124" s="0"/>
+      <c r="H124" s="0"/>
+      <c r="I124" s="0"/>
+      <c r="XFC124" s="0"/>
+      <c r="XFD124" s="0"/>
     </row>
     <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J125" s="1"/>
-      <c r="M125" s="1"/>
+      <c r="A125" s="0"/>
+      <c r="B125" s="0"/>
+      <c r="C125" s="0"/>
+      <c r="D125" s="0"/>
+      <c r="E125" s="0"/>
+      <c r="F125" s="0"/>
+      <c r="G125" s="0"/>
+      <c r="H125" s="0"/>
+      <c r="I125" s="0"/>
+      <c r="XFC125" s="0"/>
+      <c r="XFD125" s="0"/>
     </row>
     <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K126" s="1"/>
+      <c r="A126" s="0"/>
+      <c r="B126" s="0"/>
+      <c r="C126" s="0"/>
+      <c r="D126" s="0"/>
+      <c r="E126" s="0"/>
+      <c r="F126" s="0"/>
+      <c r="G126" s="0"/>
+      <c r="H126" s="0"/>
+      <c r="I126" s="0"/>
+      <c r="XFC126" s="0"/>
+      <c r="XFD126" s="0"/>
+    </row>
+    <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="0"/>
+      <c r="B127" s="0"/>
+      <c r="C127" s="0"/>
+      <c r="D127" s="0"/>
+      <c r="E127" s="0"/>
+      <c r="F127" s="0"/>
+      <c r="G127" s="0"/>
+      <c r="H127" s="0"/>
+      <c r="I127" s="0"/>
+      <c r="XFC127" s="0"/>
+      <c r="XFD127" s="0"/>
     </row>
     <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J128" s="1"/>
+      <c r="A128" s="0"/>
+      <c r="B128" s="0"/>
+      <c r="C128" s="0"/>
+      <c r="D128" s="0"/>
+      <c r="E128" s="0"/>
+      <c r="F128" s="0"/>
+      <c r="G128" s="0"/>
+      <c r="H128" s="0"/>
+      <c r="I128" s="0"/>
+      <c r="XFC128" s="0"/>
+      <c r="XFD128" s="0"/>
+    </row>
+    <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="0"/>
+      <c r="B129" s="0"/>
+      <c r="C129" s="0"/>
+      <c r="D129" s="0"/>
+      <c r="E129" s="0"/>
+      <c r="F129" s="0"/>
+      <c r="G129" s="0"/>
+      <c r="H129" s="0"/>
+      <c r="I129" s="0"/>
+      <c r="XFC129" s="0"/>
+      <c r="XFD129" s="0"/>
+    </row>
+    <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="0"/>
+      <c r="B130" s="0"/>
+      <c r="C130" s="0"/>
+      <c r="D130" s="0"/>
+      <c r="E130" s="0"/>
+      <c r="F130" s="0"/>
+      <c r="G130" s="0"/>
+      <c r="H130" s="0"/>
+      <c r="I130" s="0"/>
+      <c r="XFC130" s="0"/>
+      <c r="XFD130" s="0"/>
+    </row>
+    <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="0"/>
+      <c r="B131" s="0"/>
+      <c r="C131" s="0"/>
+      <c r="D131" s="0"/>
+      <c r="E131" s="0"/>
+      <c r="F131" s="0"/>
+      <c r="G131" s="0"/>
+      <c r="H131" s="0"/>
+      <c r="I131" s="0"/>
+      <c r="XFC131" s="0"/>
+      <c r="XFD131" s="0"/>
     </row>
     <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K132" s="1"/>
+      <c r="A132" s="0"/>
+      <c r="B132" s="0"/>
+      <c r="C132" s="0"/>
+      <c r="D132" s="0"/>
+      <c r="E132" s="0"/>
+      <c r="F132" s="0"/>
+      <c r="G132" s="0"/>
+      <c r="H132" s="0"/>
+      <c r="I132" s="0"/>
+      <c r="XFC132" s="0"/>
+      <c r="XFD132" s="0"/>
     </row>
     <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J133" s="1"/>
+      <c r="A133" s="0"/>
+      <c r="B133" s="0"/>
+      <c r="C133" s="0"/>
+      <c r="D133" s="0"/>
+      <c r="E133" s="0"/>
+      <c r="F133" s="0"/>
+      <c r="G133" s="0"/>
+      <c r="H133" s="0"/>
+      <c r="I133" s="0"/>
+      <c r="XFC133" s="0"/>
+      <c r="XFD133" s="0"/>
     </row>
     <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K134" s="1"/>
+      <c r="A134" s="0"/>
+      <c r="B134" s="0"/>
+      <c r="C134" s="0"/>
+      <c r="D134" s="0"/>
+      <c r="E134" s="0"/>
+      <c r="F134" s="0"/>
+      <c r="G134" s="0"/>
+      <c r="H134" s="0"/>
+      <c r="I134" s="0"/>
+      <c r="XFC134" s="0"/>
+      <c r="XFD134" s="0"/>
+    </row>
+    <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A135" s="0"/>
+      <c r="B135" s="0"/>
+      <c r="C135" s="0"/>
+      <c r="D135" s="0"/>
+      <c r="E135" s="0"/>
+      <c r="F135" s="0"/>
+      <c r="G135" s="0"/>
+      <c r="H135" s="0"/>
+      <c r="I135" s="0"/>
+      <c r="XFC135" s="0"/>
+      <c r="XFD135" s="0"/>
     </row>
     <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K136" s="1"/>
+      <c r="A136" s="0"/>
+      <c r="B136" s="0"/>
+      <c r="C136" s="0"/>
+      <c r="D136" s="0"/>
+      <c r="E136" s="0"/>
+      <c r="F136" s="0"/>
+      <c r="G136" s="0"/>
+      <c r="H136" s="0"/>
+      <c r="I136" s="0"/>
+      <c r="XFC136" s="0"/>
+      <c r="XFD136" s="0"/>
     </row>
     <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K137" s="1"/>
+      <c r="A137" s="0"/>
+      <c r="B137" s="0"/>
+      <c r="C137" s="0"/>
+      <c r="D137" s="0"/>
+      <c r="E137" s="0"/>
+      <c r="F137" s="0"/>
+      <c r="G137" s="0"/>
+      <c r="H137" s="0"/>
+      <c r="I137" s="0"/>
+      <c r="XFC137" s="0"/>
+      <c r="XFD137" s="0"/>
     </row>
     <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K138" s="1"/>
+      <c r="A138" s="0"/>
+      <c r="B138" s="0"/>
+      <c r="C138" s="0"/>
+      <c r="D138" s="0"/>
+      <c r="E138" s="0"/>
+      <c r="F138" s="0"/>
+      <c r="G138" s="0"/>
+      <c r="H138" s="0"/>
+      <c r="I138" s="0"/>
+      <c r="XFC138" s="0"/>
+      <c r="XFD138" s="0"/>
     </row>
     <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K139" s="1"/>
+      <c r="A139" s="0"/>
+      <c r="B139" s="0"/>
+      <c r="C139" s="0"/>
+      <c r="D139" s="0"/>
+      <c r="E139" s="0"/>
+      <c r="F139" s="0"/>
+      <c r="G139" s="0"/>
+      <c r="H139" s="0"/>
+      <c r="I139" s="0"/>
+      <c r="XFC139" s="0"/>
+      <c r="XFD139" s="0"/>
     </row>
     <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K140" s="1"/>
+      <c r="A140" s="0"/>
+      <c r="B140" s="0"/>
+      <c r="C140" s="0"/>
+      <c r="D140" s="0"/>
+      <c r="E140" s="0"/>
+      <c r="F140" s="0"/>
+      <c r="G140" s="0"/>
+      <c r="H140" s="0"/>
+      <c r="I140" s="0"/>
+      <c r="XFC140" s="0"/>
+      <c r="XFD140" s="0"/>
     </row>
     <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K141" s="1"/>
+      <c r="A141" s="0"/>
+      <c r="B141" s="0"/>
+      <c r="C141" s="0"/>
+      <c r="D141" s="0"/>
+      <c r="E141" s="0"/>
+      <c r="F141" s="0"/>
+      <c r="G141" s="0"/>
+      <c r="H141" s="0"/>
+      <c r="I141" s="0"/>
+      <c r="XFC141" s="0"/>
+      <c r="XFD141" s="0"/>
     </row>
     <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K142" s="1"/>
+      <c r="A142" s="0"/>
+      <c r="B142" s="0"/>
+      <c r="C142" s="0"/>
+      <c r="D142" s="0"/>
+      <c r="E142" s="0"/>
+      <c r="F142" s="0"/>
+      <c r="G142" s="0"/>
+      <c r="H142" s="0"/>
+      <c r="I142" s="0"/>
+      <c r="XFC142" s="0"/>
+      <c r="XFD142" s="0"/>
     </row>
     <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K143" s="1"/>
+      <c r="A143" s="0"/>
+      <c r="B143" s="0"/>
+      <c r="C143" s="0"/>
+      <c r="D143" s="0"/>
+      <c r="E143" s="0"/>
+      <c r="F143" s="0"/>
+      <c r="G143" s="0"/>
+      <c r="H143" s="0"/>
+      <c r="I143" s="0"/>
+      <c r="XFC143" s="0"/>
+      <c r="XFD143" s="0"/>
     </row>
     <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K144" s="1"/>
+      <c r="A144" s="0"/>
+      <c r="B144" s="0"/>
+      <c r="C144" s="0"/>
+      <c r="D144" s="0"/>
+      <c r="E144" s="0"/>
+      <c r="F144" s="0"/>
+      <c r="G144" s="0"/>
+      <c r="H144" s="0"/>
+      <c r="I144" s="0"/>
+      <c r="XFC144" s="0"/>
+      <c r="XFD144" s="0"/>
+    </row>
+    <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A145" s="0"/>
+      <c r="B145" s="0"/>
+      <c r="C145" s="0"/>
+      <c r="D145" s="0"/>
+      <c r="E145" s="0"/>
+      <c r="F145" s="0"/>
+      <c r="G145" s="0"/>
+      <c r="H145" s="0"/>
+      <c r="I145" s="0"/>
+      <c r="XFC145" s="0"/>
+      <c r="XFD145" s="0"/>
+    </row>
+    <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A146" s="0"/>
+      <c r="B146" s="0"/>
+      <c r="C146" s="0"/>
+      <c r="D146" s="0"/>
+      <c r="E146" s="0"/>
+      <c r="F146" s="0"/>
+      <c r="G146" s="0"/>
+      <c r="H146" s="0"/>
+      <c r="I146" s="0"/>
+      <c r="XFC146" s="0"/>
+      <c r="XFD146" s="0"/>
     </row>
     <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J147" s="1"/>
+      <c r="A147" s="0"/>
+      <c r="B147" s="0"/>
+      <c r="C147" s="0"/>
+      <c r="D147" s="0"/>
+      <c r="E147" s="0"/>
+      <c r="F147" s="0"/>
+      <c r="G147" s="0"/>
+      <c r="H147" s="0"/>
+      <c r="I147" s="0"/>
+      <c r="XFC147" s="0"/>
+      <c r="XFD147" s="0"/>
+    </row>
+    <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A148" s="0"/>
+      <c r="B148" s="0"/>
+      <c r="C148" s="0"/>
+      <c r="D148" s="0"/>
+      <c r="E148" s="0"/>
+      <c r="F148" s="0"/>
+      <c r="G148" s="0"/>
+      <c r="H148" s="0"/>
+      <c r="I148" s="0"/>
+      <c r="XFC148" s="0"/>
+      <c r="XFD148" s="0"/>
     </row>
     <row r="149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J149" s="1"/>
+      <c r="A149" s="0"/>
+      <c r="B149" s="0"/>
+      <c r="C149" s="0"/>
+      <c r="D149" s="0"/>
+      <c r="E149" s="0"/>
+      <c r="F149" s="0"/>
+      <c r="G149" s="0"/>
+      <c r="H149" s="0"/>
+      <c r="I149" s="0"/>
+      <c r="XFC149" s="0"/>
+      <c r="XFD149" s="0"/>
     </row>
     <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J150" s="1"/>
+      <c r="A150" s="0"/>
+      <c r="B150" s="0"/>
+      <c r="C150" s="0"/>
+      <c r="D150" s="0"/>
+      <c r="E150" s="0"/>
+      <c r="F150" s="0"/>
+      <c r="G150" s="0"/>
+      <c r="H150" s="0"/>
+      <c r="I150" s="0"/>
+      <c r="XFC150" s="0"/>
+      <c r="XFD150" s="0"/>
     </row>
     <row r="151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J151" s="1"/>
+      <c r="A151" s="0"/>
+      <c r="B151" s="0"/>
+      <c r="C151" s="0"/>
+      <c r="D151" s="0"/>
+      <c r="E151" s="0"/>
+      <c r="F151" s="0"/>
+      <c r="G151" s="0"/>
+      <c r="H151" s="0"/>
+      <c r="I151" s="0"/>
+      <c r="XFC151" s="0"/>
+      <c r="XFD151" s="0"/>
     </row>
     <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J152" s="1"/>
+      <c r="A152" s="0"/>
+      <c r="B152" s="0"/>
+      <c r="C152" s="0"/>
+      <c r="D152" s="0"/>
+      <c r="E152" s="0"/>
+      <c r="F152" s="0"/>
+      <c r="G152" s="0"/>
+      <c r="H152" s="0"/>
+      <c r="I152" s="0"/>
+      <c r="XFC152" s="0"/>
+      <c r="XFD152" s="0"/>
     </row>
     <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J153" s="1"/>
+      <c r="A153" s="0"/>
+      <c r="B153" s="0"/>
+      <c r="C153" s="0"/>
+      <c r="D153" s="0"/>
+      <c r="E153" s="0"/>
+      <c r="F153" s="0"/>
+      <c r="G153" s="0"/>
+      <c r="H153" s="0"/>
+      <c r="I153" s="0"/>
+      <c r="XFC153" s="0"/>
+      <c r="XFD153" s="0"/>
     </row>
     <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J154" s="1"/>
+      <c r="A154" s="0"/>
+      <c r="B154" s="0"/>
+      <c r="C154" s="0"/>
+      <c r="D154" s="0"/>
+      <c r="E154" s="0"/>
+      <c r="F154" s="0"/>
+      <c r="G154" s="0"/>
+      <c r="H154" s="0"/>
+      <c r="I154" s="0"/>
+      <c r="XFC154" s="0"/>
+      <c r="XFD154" s="0"/>
     </row>
     <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J155" s="1"/>
+      <c r="A155" s="0"/>
+      <c r="B155" s="0"/>
+      <c r="C155" s="0"/>
+      <c r="D155" s="0"/>
+      <c r="E155" s="0"/>
+      <c r="F155" s="0"/>
+      <c r="G155" s="0"/>
+      <c r="H155" s="0"/>
+      <c r="I155" s="0"/>
+      <c r="XFC155" s="0"/>
+      <c r="XFD155" s="0"/>
     </row>
     <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J156" s="1"/>
+      <c r="A156" s="0"/>
+      <c r="B156" s="0"/>
+      <c r="C156" s="0"/>
+      <c r="D156" s="0"/>
+      <c r="E156" s="0"/>
+      <c r="F156" s="0"/>
+      <c r="G156" s="0"/>
+      <c r="H156" s="0"/>
+      <c r="I156" s="0"/>
+      <c r="XFC156" s="0"/>
+      <c r="XFD156" s="0"/>
     </row>
     <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J157" s="1"/>
+      <c r="A157" s="0"/>
+      <c r="B157" s="0"/>
+      <c r="C157" s="0"/>
+      <c r="D157" s="0"/>
+      <c r="E157" s="0"/>
+      <c r="F157" s="0"/>
+      <c r="G157" s="0"/>
+      <c r="H157" s="0"/>
+      <c r="I157" s="0"/>
+      <c r="XFC157" s="0"/>
+      <c r="XFD157" s="0"/>
+    </row>
+    <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A158" s="0"/>
+      <c r="B158" s="0"/>
+      <c r="C158" s="0"/>
+      <c r="D158" s="0"/>
+      <c r="E158" s="0"/>
+      <c r="F158" s="0"/>
+      <c r="G158" s="0"/>
+      <c r="H158" s="0"/>
+      <c r="I158" s="0"/>
+      <c r="XFC158" s="0"/>
+      <c r="XFD158" s="0"/>
+    </row>
+    <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A159" s="0"/>
+      <c r="B159" s="0"/>
+      <c r="C159" s="0"/>
+      <c r="D159" s="0"/>
+      <c r="E159" s="0"/>
+      <c r="F159" s="0"/>
+      <c r="G159" s="0"/>
+      <c r="H159" s="0"/>
+      <c r="I159" s="0"/>
+      <c r="XFC159" s="0"/>
+      <c r="XFD159" s="0"/>
     </row>
     <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J160" s="1"/>
+      <c r="A160" s="0"/>
+      <c r="B160" s="0"/>
+      <c r="C160" s="0"/>
+      <c r="D160" s="0"/>
+      <c r="E160" s="0"/>
+      <c r="F160" s="0"/>
+      <c r="G160" s="0"/>
+      <c r="H160" s="0"/>
+      <c r="I160" s="0"/>
+      <c r="XFC160" s="0"/>
+      <c r="XFD160" s="0"/>
+    </row>
+    <row r="161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="0"/>
+      <c r="B161" s="0"/>
+      <c r="C161" s="0"/>
+      <c r="D161" s="0"/>
+      <c r="E161" s="0"/>
+      <c r="F161" s="0"/>
+      <c r="G161" s="4"/>
+      <c r="H161" s="0"/>
+      <c r="I161" s="0"/>
+      <c r="XFC161" s="0"/>
+      <c r="XFD161" s="0"/>
     </row>
     <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K162" s="1"/>
+      <c r="A162" s="0"/>
+      <c r="B162" s="0"/>
+      <c r="C162" s="0"/>
+      <c r="D162" s="0"/>
+      <c r="E162" s="0"/>
+      <c r="F162" s="0"/>
+      <c r="G162" s="0"/>
+      <c r="H162" s="0"/>
+      <c r="I162" s="0"/>
+      <c r="XFC162" s="0"/>
+      <c r="XFD162" s="0"/>
     </row>
     <row r="163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K163" s="1"/>
+      <c r="A163" s="0"/>
+      <c r="B163" s="0"/>
+      <c r="C163" s="0"/>
+      <c r="D163" s="0"/>
+      <c r="E163" s="0"/>
+      <c r="F163" s="0"/>
+      <c r="G163" s="0"/>
+      <c r="H163" s="0"/>
+      <c r="I163" s="0"/>
+      <c r="XFC163" s="0"/>
+      <c r="XFD163" s="0"/>
     </row>
     <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K164" s="1"/>
+      <c r="A164" s="0"/>
+      <c r="B164" s="0"/>
+      <c r="C164" s="0"/>
+      <c r="D164" s="0"/>
+      <c r="E164" s="0"/>
+      <c r="F164" s="0"/>
+      <c r="G164" s="0"/>
+      <c r="H164" s="0"/>
+      <c r="I164" s="0"/>
+      <c r="XFC164" s="0"/>
+      <c r="XFD164" s="0"/>
+    </row>
+    <row r="165" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A165" s="0"/>
+      <c r="B165" s="0"/>
+      <c r="C165" s="0"/>
+      <c r="D165" s="0"/>
+      <c r="E165" s="0"/>
+      <c r="F165" s="0"/>
+      <c r="G165" s="0"/>
+      <c r="H165" s="0"/>
+      <c r="I165" s="0"/>
+      <c r="XFC165" s="0"/>
+      <c r="XFD165" s="0"/>
+    </row>
+    <row r="166" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A166" s="0"/>
+      <c r="B166" s="0"/>
+      <c r="C166" s="0"/>
+      <c r="D166" s="0"/>
+      <c r="E166" s="0"/>
+      <c r="F166" s="0"/>
+      <c r="G166" s="0"/>
+      <c r="H166" s="0"/>
+      <c r="I166" s="0"/>
+      <c r="XFC166" s="0"/>
+      <c r="XFD166" s="0"/>
     </row>
     <row r="167" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K167" s="1"/>
+      <c r="A167" s="0"/>
+      <c r="B167" s="0"/>
+      <c r="C167" s="0"/>
+      <c r="D167" s="0"/>
+      <c r="E167" s="0"/>
+      <c r="F167" s="0"/>
+      <c r="G167" s="0"/>
+      <c r="H167" s="0"/>
+      <c r="I167" s="0"/>
+      <c r="XFC167" s="0"/>
+      <c r="XFD167" s="0"/>
     </row>
     <row r="168" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J168" s="1"/>
-      <c r="M168" s="1"/>
+      <c r="A168" s="0"/>
+      <c r="B168" s="0"/>
+      <c r="C168" s="0"/>
+      <c r="D168" s="0"/>
+      <c r="E168" s="0"/>
+      <c r="F168" s="0"/>
+      <c r="G168" s="0"/>
+      <c r="H168" s="0"/>
+      <c r="I168" s="0"/>
+      <c r="XFC168" s="0"/>
+      <c r="XFD168" s="0"/>
     </row>
     <row r="169" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K169" s="1"/>
+      <c r="A169" s="0"/>
+      <c r="B169" s="0"/>
+      <c r="C169" s="0"/>
+      <c r="D169" s="0"/>
+      <c r="E169" s="0"/>
+      <c r="F169" s="0"/>
+      <c r="G169" s="0"/>
+      <c r="H169" s="0"/>
+      <c r="I169" s="0"/>
+      <c r="XFC169" s="0"/>
+      <c r="XFD169" s="0"/>
+    </row>
+    <row r="170" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A170" s="0"/>
+      <c r="B170" s="0"/>
+      <c r="C170" s="0"/>
+      <c r="D170" s="0"/>
+      <c r="E170" s="0"/>
+      <c r="F170" s="0"/>
+      <c r="G170" s="0"/>
+      <c r="H170" s="0"/>
+      <c r="I170" s="0"/>
+      <c r="XFC170" s="0"/>
+      <c r="XFD170" s="0"/>
     </row>
     <row r="171" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J171" s="1"/>
+      <c r="A171" s="0"/>
+      <c r="B171" s="0"/>
+      <c r="C171" s="0"/>
+      <c r="D171" s="0"/>
+      <c r="E171" s="0"/>
+      <c r="F171" s="0"/>
+      <c r="G171" s="0"/>
+      <c r="H171" s="0"/>
+      <c r="I171" s="0"/>
+      <c r="XFC171" s="0"/>
+      <c r="XFD171" s="0"/>
+    </row>
+    <row r="172" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A172" s="0"/>
+      <c r="B172" s="0"/>
+      <c r="C172" s="0"/>
+      <c r="D172" s="0"/>
+      <c r="E172" s="0"/>
+      <c r="F172" s="0"/>
+      <c r="G172" s="0"/>
+      <c r="H172" s="0"/>
+      <c r="I172" s="0"/>
+      <c r="XFC172" s="0"/>
+      <c r="XFD172" s="0"/>
+    </row>
+    <row r="173" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A173" s="0"/>
+      <c r="B173" s="0"/>
+      <c r="C173" s="0"/>
+      <c r="D173" s="0"/>
+      <c r="E173" s="0"/>
+      <c r="F173" s="0"/>
+      <c r="G173" s="0"/>
+      <c r="H173" s="0"/>
+      <c r="I173" s="0"/>
+      <c r="XFC173" s="0"/>
+      <c r="XFD173" s="0"/>
+    </row>
+    <row r="174" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A174" s="0"/>
+      <c r="B174" s="0"/>
+      <c r="C174" s="0"/>
+      <c r="D174" s="0"/>
+      <c r="E174" s="0"/>
+      <c r="F174" s="0"/>
+      <c r="G174" s="0"/>
+      <c r="H174" s="0"/>
+      <c r="I174" s="0"/>
+      <c r="XFC174" s="0"/>
+      <c r="XFD174" s="0"/>
     </row>
     <row r="175" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K175" s="1"/>
+      <c r="A175" s="0"/>
+      <c r="B175" s="0"/>
+      <c r="C175" s="0"/>
+      <c r="D175" s="0"/>
+      <c r="E175" s="0"/>
+      <c r="F175" s="0"/>
+      <c r="G175" s="0"/>
+      <c r="H175" s="0"/>
+      <c r="I175" s="0"/>
+      <c r="XFC175" s="0"/>
+      <c r="XFD175" s="0"/>
     </row>
     <row r="176" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J176" s="1"/>
+      <c r="A176" s="0"/>
+      <c r="B176" s="0"/>
+      <c r="C176" s="0"/>
+      <c r="D176" s="0"/>
+      <c r="E176" s="0"/>
+      <c r="F176" s="0"/>
+      <c r="G176" s="0"/>
+      <c r="H176" s="0"/>
+      <c r="I176" s="0"/>
+      <c r="XFC176" s="0"/>
+      <c r="XFD176" s="0"/>
     </row>
     <row r="177" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K177" s="1"/>
+      <c r="A177" s="0"/>
+      <c r="B177" s="0"/>
+      <c r="C177" s="0"/>
+      <c r="D177" s="0"/>
+      <c r="E177" s="0"/>
+      <c r="F177" s="0"/>
+      <c r="G177" s="0"/>
+      <c r="H177" s="0"/>
+      <c r="I177" s="0"/>
+      <c r="XFC177" s="0"/>
+      <c r="XFD177" s="0"/>
+    </row>
+    <row r="178" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A178" s="0"/>
+      <c r="B178" s="0"/>
+      <c r="C178" s="0"/>
+      <c r="D178" s="0"/>
+      <c r="E178" s="0"/>
+      <c r="F178" s="0"/>
+      <c r="G178" s="0"/>
+      <c r="H178" s="0"/>
+      <c r="I178" s="0"/>
+      <c r="XFC178" s="0"/>
+      <c r="XFD178" s="0"/>
     </row>
     <row r="179" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K179" s="1"/>
+      <c r="A179" s="0"/>
+      <c r="B179" s="0"/>
+      <c r="C179" s="0"/>
+      <c r="D179" s="0"/>
+      <c r="E179" s="0"/>
+      <c r="F179" s="0"/>
+      <c r="G179" s="0"/>
+      <c r="H179" s="0"/>
+      <c r="I179" s="0"/>
+      <c r="XFC179" s="0"/>
+      <c r="XFD179" s="0"/>
     </row>
     <row r="180" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K180" s="1"/>
+      <c r="A180" s="0"/>
+      <c r="B180" s="0"/>
+      <c r="C180" s="0"/>
+      <c r="D180" s="0"/>
+      <c r="E180" s="0"/>
+      <c r="F180" s="0"/>
+      <c r="G180" s="0"/>
+      <c r="H180" s="0"/>
+      <c r="I180" s="0"/>
+      <c r="XFC180" s="0"/>
+      <c r="XFD180" s="0"/>
     </row>
     <row r="181" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K181" s="1"/>
+      <c r="A181" s="0"/>
+      <c r="B181" s="0"/>
+      <c r="C181" s="0"/>
+      <c r="D181" s="0"/>
+      <c r="E181" s="0"/>
+      <c r="F181" s="0"/>
+      <c r="G181" s="0"/>
+      <c r="H181" s="0"/>
+      <c r="I181" s="0"/>
+      <c r="XFC181" s="0"/>
+      <c r="XFD181" s="0"/>
     </row>
     <row r="182" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K182" s="1"/>
+      <c r="A182" s="0"/>
+      <c r="B182" s="0"/>
+      <c r="C182" s="0"/>
+      <c r="D182" s="0"/>
+      <c r="E182" s="0"/>
+      <c r="F182" s="0"/>
+      <c r="G182" s="0"/>
+      <c r="H182" s="0"/>
+      <c r="I182" s="0"/>
+      <c r="XFC182" s="0"/>
+      <c r="XFD182" s="0"/>
     </row>
     <row r="183" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K183" s="1"/>
+      <c r="A183" s="0"/>
+      <c r="B183" s="0"/>
+      <c r="C183" s="0"/>
+      <c r="D183" s="0"/>
+      <c r="E183" s="0"/>
+      <c r="F183" s="0"/>
+      <c r="G183" s="0"/>
+      <c r="H183" s="0"/>
+      <c r="I183" s="0"/>
+      <c r="XFC183" s="0"/>
+      <c r="XFD183" s="0"/>
     </row>
     <row r="184" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K184" s="1"/>
+      <c r="A184" s="0"/>
+      <c r="B184" s="0"/>
+      <c r="C184" s="0"/>
+      <c r="D184" s="0"/>
+      <c r="E184" s="0"/>
+      <c r="F184" s="0"/>
+      <c r="G184" s="0"/>
+      <c r="H184" s="0"/>
+      <c r="I184" s="0"/>
+      <c r="XFC184" s="0"/>
+      <c r="XFD184" s="0"/>
     </row>
     <row r="185" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K185" s="1"/>
+      <c r="A185" s="0"/>
+      <c r="B185" s="0"/>
+      <c r="C185" s="0"/>
+      <c r="D185" s="0"/>
+      <c r="E185" s="0"/>
+      <c r="F185" s="0"/>
+      <c r="G185" s="0"/>
+      <c r="H185" s="0"/>
+      <c r="I185" s="0"/>
+      <c r="XFC185" s="0"/>
+      <c r="XFD185" s="0"/>
     </row>
     <row r="186" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K186" s="1"/>
+      <c r="A186" s="0"/>
+      <c r="B186" s="0"/>
+      <c r="C186" s="0"/>
+      <c r="D186" s="0"/>
+      <c r="E186" s="0"/>
+      <c r="F186" s="0"/>
+      <c r="G186" s="0"/>
+      <c r="H186" s="0"/>
+      <c r="I186" s="0"/>
+      <c r="XFC186" s="0"/>
+      <c r="XFD186" s="0"/>
     </row>
     <row r="187" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K187" s="1"/>
+      <c r="A187" s="0"/>
+      <c r="B187" s="0"/>
+      <c r="C187" s="0"/>
+      <c r="D187" s="0"/>
+      <c r="E187" s="0"/>
+      <c r="F187" s="0"/>
+      <c r="G187" s="0"/>
+      <c r="H187" s="0"/>
+      <c r="I187" s="0"/>
+      <c r="XFC187" s="0"/>
+      <c r="XFD187" s="0"/>
+    </row>
+    <row r="188" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A188" s="0"/>
+      <c r="B188" s="0"/>
+      <c r="C188" s="0"/>
+      <c r="D188" s="0"/>
+      <c r="E188" s="0"/>
+      <c r="F188" s="0"/>
+      <c r="G188" s="0"/>
+      <c r="H188" s="0"/>
+      <c r="I188" s="0"/>
+      <c r="XFC188" s="0"/>
+      <c r="XFD188" s="0"/>
+    </row>
+    <row r="189" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A189" s="0"/>
+      <c r="B189" s="0"/>
+      <c r="C189" s="0"/>
+      <c r="D189" s="0"/>
+      <c r="E189" s="0"/>
+      <c r="F189" s="0"/>
+      <c r="G189" s="0"/>
+      <c r="H189" s="0"/>
+      <c r="I189" s="0"/>
+      <c r="XFC189" s="0"/>
+      <c r="XFD189" s="0"/>
     </row>
     <row r="190" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J190" s="1"/>
+      <c r="A190" s="0"/>
+      <c r="B190" s="0"/>
+      <c r="C190" s="0"/>
+      <c r="D190" s="0"/>
+      <c r="E190" s="0"/>
+      <c r="F190" s="0"/>
+      <c r="G190" s="0"/>
+      <c r="H190" s="0"/>
+      <c r="I190" s="0"/>
+      <c r="XFC190" s="0"/>
+      <c r="XFD190" s="0"/>
+    </row>
+    <row r="191" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A191" s="0"/>
+      <c r="B191" s="0"/>
+      <c r="C191" s="0"/>
+      <c r="D191" s="0"/>
+      <c r="E191" s="0"/>
+      <c r="F191" s="0"/>
+      <c r="G191" s="0"/>
+      <c r="H191" s="0"/>
+      <c r="I191" s="0"/>
+      <c r="XFC191" s="0"/>
+      <c r="XFD191" s="0"/>
     </row>
     <row r="192" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J192" s="1"/>
+      <c r="A192" s="0"/>
+      <c r="B192" s="0"/>
+      <c r="C192" s="0"/>
+      <c r="D192" s="0"/>
+      <c r="E192" s="0"/>
+      <c r="F192" s="0"/>
+      <c r="G192" s="0"/>
+      <c r="H192" s="0"/>
+      <c r="I192" s="0"/>
+      <c r="XFC192" s="0"/>
+      <c r="XFD192" s="0"/>
     </row>
     <row r="193" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J193" s="1"/>
+      <c r="A193" s="0"/>
+      <c r="B193" s="0"/>
+      <c r="C193" s="0"/>
+      <c r="D193" s="0"/>
+      <c r="E193" s="0"/>
+      <c r="F193" s="0"/>
+      <c r="G193" s="0"/>
+      <c r="H193" s="0"/>
+      <c r="I193" s="0"/>
+      <c r="XFC193" s="0"/>
+      <c r="XFD193" s="0"/>
     </row>
     <row r="194" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J194" s="1"/>
+      <c r="A194" s="0"/>
+      <c r="B194" s="0"/>
+      <c r="C194" s="0"/>
+      <c r="D194" s="0"/>
+      <c r="E194" s="0"/>
+      <c r="F194" s="0"/>
+      <c r="G194" s="0"/>
+      <c r="H194" s="0"/>
+      <c r="I194" s="0"/>
+      <c r="XFC194" s="0"/>
+      <c r="XFD194" s="0"/>
     </row>
     <row r="195" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J195" s="1"/>
+      <c r="A195" s="0"/>
+      <c r="B195" s="0"/>
+      <c r="C195" s="0"/>
+      <c r="D195" s="0"/>
+      <c r="E195" s="0"/>
+      <c r="F195" s="0"/>
+      <c r="G195" s="0"/>
+      <c r="H195" s="0"/>
+      <c r="I195" s="0"/>
+      <c r="XFC195" s="0"/>
+      <c r="XFD195" s="0"/>
     </row>
     <row r="196" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J196" s="1"/>
+      <c r="A196" s="0"/>
+      <c r="B196" s="0"/>
+      <c r="C196" s="0"/>
+      <c r="D196" s="0"/>
+      <c r="E196" s="0"/>
+      <c r="F196" s="0"/>
+      <c r="G196" s="0"/>
+      <c r="H196" s="0"/>
+      <c r="I196" s="0"/>
+      <c r="XFC196" s="0"/>
+      <c r="XFD196" s="0"/>
     </row>
     <row r="197" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J197" s="1"/>
+      <c r="A197" s="0"/>
+      <c r="B197" s="0"/>
+      <c r="C197" s="0"/>
+      <c r="D197" s="0"/>
+      <c r="E197" s="0"/>
+      <c r="F197" s="0"/>
+      <c r="G197" s="0"/>
+      <c r="H197" s="0"/>
+      <c r="I197" s="0"/>
+      <c r="XFC197" s="0"/>
+      <c r="XFD197" s="0"/>
     </row>
     <row r="198" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J198" s="1"/>
+      <c r="A198" s="0"/>
+      <c r="B198" s="0"/>
+      <c r="C198" s="0"/>
+      <c r="D198" s="0"/>
+      <c r="E198" s="0"/>
+      <c r="F198" s="0"/>
+      <c r="G198" s="0"/>
+      <c r="H198" s="0"/>
+      <c r="I198" s="0"/>
+      <c r="XFC198" s="0"/>
+      <c r="XFD198" s="0"/>
     </row>
     <row r="199" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J199" s="1"/>
+      <c r="A199" s="0"/>
+      <c r="B199" s="0"/>
+      <c r="C199" s="0"/>
+      <c r="D199" s="0"/>
+      <c r="E199" s="0"/>
+      <c r="F199" s="0"/>
+      <c r="G199" s="0"/>
+      <c r="H199" s="0"/>
+      <c r="I199" s="0"/>
+      <c r="XFC199" s="0"/>
+      <c r="XFD199" s="0"/>
     </row>
     <row r="200" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J200" s="1"/>
+      <c r="A200" s="0"/>
+      <c r="B200" s="0"/>
+      <c r="C200" s="0"/>
+      <c r="D200" s="0"/>
+      <c r="E200" s="0"/>
+      <c r="F200" s="0"/>
+      <c r="G200" s="0"/>
+      <c r="H200" s="0"/>
+      <c r="I200" s="0"/>
+      <c r="XFC200" s="0"/>
+      <c r="XFD200" s="0"/>
+    </row>
+    <row r="201" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A201" s="0"/>
+      <c r="B201" s="0"/>
+      <c r="C201" s="0"/>
+      <c r="D201" s="0"/>
+      <c r="E201" s="0"/>
+      <c r="F201" s="0"/>
+      <c r="G201" s="0"/>
+      <c r="H201" s="0"/>
+      <c r="I201" s="0"/>
+      <c r="XFC201" s="0"/>
+      <c r="XFD201" s="0"/>
+    </row>
+    <row r="202" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A202" s="0"/>
+      <c r="B202" s="0"/>
+      <c r="C202" s="0"/>
+      <c r="D202" s="0"/>
+      <c r="E202" s="0"/>
+      <c r="F202" s="0"/>
+      <c r="G202" s="0"/>
+      <c r="H202" s="0"/>
+      <c r="I202" s="0"/>
+      <c r="XFC202" s="0"/>
+      <c r="XFD202" s="0"/>
     </row>
     <row r="203" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J203" s="1"/>
+      <c r="A203" s="0"/>
+      <c r="B203" s="0"/>
+      <c r="C203" s="0"/>
+      <c r="D203" s="0"/>
+      <c r="E203" s="0"/>
+      <c r="F203" s="0"/>
+      <c r="G203" s="0"/>
+      <c r="H203" s="0"/>
+      <c r="I203" s="0"/>
+      <c r="XFC203" s="0"/>
+      <c r="XFD203" s="0"/>
+    </row>
+    <row r="204" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A204" s="0"/>
+      <c r="B204" s="0"/>
+      <c r="C204" s="0"/>
+      <c r="D204" s="0"/>
+      <c r="E204" s="0"/>
+      <c r="F204" s="0"/>
+      <c r="G204" s="4"/>
+      <c r="H204" s="0"/>
+      <c r="I204" s="0"/>
+      <c r="XFC204" s="0"/>
+      <c r="XFD204" s="0"/>
     </row>
     <row r="205" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K205" s="1"/>
+      <c r="A205" s="0"/>
+      <c r="B205" s="0"/>
+      <c r="C205" s="0"/>
+      <c r="D205" s="0"/>
+      <c r="E205" s="0"/>
+      <c r="F205" s="0"/>
+      <c r="G205" s="0"/>
+      <c r="H205" s="0"/>
+      <c r="I205" s="0"/>
+      <c r="XFC205" s="0"/>
+      <c r="XFD205" s="0"/>
     </row>
     <row r="206" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K206" s="1"/>
+      <c r="A206" s="0"/>
+      <c r="B206" s="0"/>
+      <c r="C206" s="0"/>
+      <c r="D206" s="0"/>
+      <c r="E206" s="0"/>
+      <c r="F206" s="0"/>
+      <c r="G206" s="0"/>
+      <c r="H206" s="0"/>
+      <c r="I206" s="0"/>
+      <c r="XFC206" s="0"/>
+      <c r="XFD206" s="0"/>
     </row>
     <row r="207" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K207" s="1"/>
+      <c r="A207" s="0"/>
+      <c r="B207" s="0"/>
+      <c r="C207" s="0"/>
+      <c r="D207" s="0"/>
+      <c r="E207" s="0"/>
+      <c r="F207" s="0"/>
+      <c r="G207" s="0"/>
+      <c r="H207" s="0"/>
+      <c r="I207" s="0"/>
+      <c r="XFC207" s="0"/>
+      <c r="XFD207" s="0"/>
+    </row>
+    <row r="208" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A208" s="0"/>
+      <c r="B208" s="0"/>
+      <c r="C208" s="0"/>
+      <c r="D208" s="0"/>
+      <c r="E208" s="0"/>
+      <c r="F208" s="0"/>
+      <c r="G208" s="0"/>
+      <c r="H208" s="0"/>
+      <c r="I208" s="0"/>
+      <c r="XFC208" s="0"/>
+      <c r="XFD208" s="0"/>
+    </row>
+    <row r="209" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A209" s="0"/>
+      <c r="B209" s="0"/>
+      <c r="C209" s="0"/>
+      <c r="D209" s="0"/>
+      <c r="E209" s="0"/>
+      <c r="F209" s="0"/>
+      <c r="G209" s="0"/>
+      <c r="H209" s="0"/>
+      <c r="I209" s="0"/>
+      <c r="XFC209" s="0"/>
+      <c r="XFD209" s="0"/>
     </row>
     <row r="210" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K210" s="1"/>
+      <c r="A210" s="0"/>
+      <c r="B210" s="0"/>
+      <c r="C210" s="0"/>
+      <c r="D210" s="0"/>
+      <c r="E210" s="0"/>
+      <c r="F210" s="0"/>
+      <c r="G210" s="0"/>
+      <c r="H210" s="0"/>
+      <c r="I210" s="0"/>
+      <c r="XFC210" s="0"/>
+      <c r="XFD210" s="0"/>
     </row>
     <row r="211" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J211" s="1"/>
-      <c r="M211" s="1"/>
+      <c r="A211" s="0"/>
+      <c r="B211" s="0"/>
+      <c r="C211" s="0"/>
+      <c r="D211" s="0"/>
+      <c r="E211" s="0"/>
+      <c r="F211" s="0"/>
+      <c r="G211" s="0"/>
+      <c r="H211" s="0"/>
+      <c r="I211" s="0"/>
+      <c r="XFC211" s="0"/>
+      <c r="XFD211" s="0"/>
     </row>
     <row r="212" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K212" s="1"/>
+      <c r="A212" s="0"/>
+      <c r="B212" s="0"/>
+      <c r="C212" s="0"/>
+      <c r="D212" s="0"/>
+      <c r="E212" s="0"/>
+      <c r="F212" s="0"/>
+      <c r="G212" s="0"/>
+      <c r="H212" s="0"/>
+      <c r="I212" s="0"/>
+      <c r="XFC212" s="0"/>
+      <c r="XFD212" s="0"/>
+    </row>
+    <row r="213" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A213" s="0"/>
+      <c r="B213" s="0"/>
+      <c r="C213" s="0"/>
+      <c r="D213" s="0"/>
+      <c r="E213" s="0"/>
+      <c r="F213" s="0"/>
+      <c r="G213" s="0"/>
+      <c r="H213" s="0"/>
+      <c r="I213" s="0"/>
+      <c r="XFC213" s="0"/>
+      <c r="XFD213" s="0"/>
     </row>
     <row r="214" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J214" s="1"/>
+      <c r="A214" s="0"/>
+      <c r="B214" s="0"/>
+      <c r="C214" s="0"/>
+      <c r="D214" s="0"/>
+      <c r="E214" s="0"/>
+      <c r="F214" s="0"/>
+      <c r="G214" s="0"/>
+      <c r="H214" s="0"/>
+      <c r="I214" s="0"/>
+      <c r="XFC214" s="0"/>
+      <c r="XFD214" s="0"/>
+    </row>
+    <row r="215" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A215" s="0"/>
+      <c r="B215" s="0"/>
+      <c r="C215" s="0"/>
+      <c r="D215" s="0"/>
+      <c r="E215" s="0"/>
+      <c r="F215" s="0"/>
+      <c r="G215" s="0"/>
+      <c r="H215" s="0"/>
+      <c r="I215" s="0"/>
+      <c r="XFC215" s="0"/>
+      <c r="XFD215" s="0"/>
+    </row>
+    <row r="216" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A216" s="0"/>
+      <c r="B216" s="0"/>
+      <c r="C216" s="0"/>
+      <c r="D216" s="0"/>
+      <c r="E216" s="0"/>
+      <c r="F216" s="0"/>
+      <c r="G216" s="0"/>
+      <c r="H216" s="0"/>
+      <c r="I216" s="0"/>
+      <c r="XFC216" s="0"/>
+      <c r="XFD216" s="0"/>
+    </row>
+    <row r="217" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A217" s="0"/>
+      <c r="B217" s="0"/>
+      <c r="C217" s="0"/>
+      <c r="D217" s="0"/>
+      <c r="E217" s="0"/>
+      <c r="F217" s="0"/>
+      <c r="G217" s="0"/>
+      <c r="H217" s="0"/>
+      <c r="I217" s="0"/>
+      <c r="XFC217" s="0"/>
+      <c r="XFD217" s="0"/>
     </row>
     <row r="218" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K218" s="1"/>
+      <c r="A218" s="0"/>
+      <c r="B218" s="0"/>
+      <c r="C218" s="0"/>
+      <c r="D218" s="0"/>
+      <c r="E218" s="0"/>
+      <c r="F218" s="0"/>
+      <c r="G218" s="0"/>
+      <c r="H218" s="0"/>
+      <c r="I218" s="0"/>
+      <c r="XFC218" s="0"/>
+      <c r="XFD218" s="0"/>
     </row>
     <row r="219" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J219" s="1"/>
+      <c r="A219" s="0"/>
+      <c r="B219" s="0"/>
+      <c r="C219" s="0"/>
+      <c r="D219" s="0"/>
+      <c r="E219" s="0"/>
+      <c r="F219" s="0"/>
+      <c r="G219" s="0"/>
+      <c r="H219" s="0"/>
+      <c r="I219" s="0"/>
+      <c r="XFC219" s="0"/>
+      <c r="XFD219" s="0"/>
     </row>
     <row r="220" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K220" s="1"/>
+      <c r="A220" s="0"/>
+      <c r="B220" s="0"/>
+      <c r="C220" s="0"/>
+      <c r="D220" s="0"/>
+      <c r="E220" s="0"/>
+      <c r="F220" s="0"/>
+      <c r="G220" s="0"/>
+      <c r="H220" s="0"/>
+      <c r="I220" s="0"/>
+      <c r="XFC220" s="0"/>
+      <c r="XFD220" s="0"/>
+    </row>
+    <row r="221" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A221" s="0"/>
+      <c r="B221" s="0"/>
+      <c r="C221" s="0"/>
+      <c r="D221" s="0"/>
+      <c r="E221" s="0"/>
+      <c r="F221" s="0"/>
+      <c r="G221" s="0"/>
+      <c r="H221" s="0"/>
+      <c r="I221" s="0"/>
+      <c r="XFC221" s="0"/>
+      <c r="XFD221" s="0"/>
     </row>
     <row r="222" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K222" s="1"/>
+      <c r="A222" s="0"/>
+      <c r="B222" s="0"/>
+      <c r="C222" s="0"/>
+      <c r="D222" s="0"/>
+      <c r="E222" s="0"/>
+      <c r="F222" s="0"/>
+      <c r="G222" s="0"/>
+      <c r="H222" s="0"/>
+      <c r="I222" s="0"/>
+      <c r="XFC222" s="0"/>
+      <c r="XFD222" s="0"/>
     </row>
     <row r="223" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K223" s="1"/>
+      <c r="A223" s="0"/>
+      <c r="B223" s="0"/>
+      <c r="C223" s="0"/>
+      <c r="D223" s="0"/>
+      <c r="E223" s="0"/>
+      <c r="F223" s="0"/>
+      <c r="G223" s="0"/>
+      <c r="H223" s="0"/>
+      <c r="I223" s="0"/>
+      <c r="XFC223" s="0"/>
+      <c r="XFD223" s="0"/>
     </row>
     <row r="224" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K224" s="1"/>
+      <c r="A224" s="0"/>
+      <c r="B224" s="0"/>
+      <c r="C224" s="0"/>
+      <c r="D224" s="0"/>
+      <c r="E224" s="0"/>
+      <c r="F224" s="0"/>
+      <c r="G224" s="0"/>
+      <c r="H224" s="0"/>
+      <c r="I224" s="0"/>
+      <c r="XFC224" s="0"/>
+      <c r="XFD224" s="0"/>
     </row>
     <row r="225" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K225" s="1"/>
+      <c r="A225" s="0"/>
+      <c r="B225" s="0"/>
+      <c r="C225" s="0"/>
+      <c r="D225" s="0"/>
+      <c r="E225" s="0"/>
+      <c r="F225" s="0"/>
+      <c r="G225" s="0"/>
+      <c r="H225" s="0"/>
+      <c r="I225" s="0"/>
+      <c r="XFC225" s="0"/>
+      <c r="XFD225" s="0"/>
     </row>
     <row r="226" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K226" s="1"/>
+      <c r="A226" s="0"/>
+      <c r="B226" s="0"/>
+      <c r="C226" s="0"/>
+      <c r="D226" s="0"/>
+      <c r="E226" s="0"/>
+      <c r="F226" s="0"/>
+      <c r="G226" s="0"/>
+      <c r="H226" s="0"/>
+      <c r="I226" s="0"/>
+      <c r="XFC226" s="0"/>
+      <c r="XFD226" s="0"/>
     </row>
     <row r="227" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K227" s="1"/>
+      <c r="A227" s="0"/>
+      <c r="B227" s="0"/>
+      <c r="C227" s="0"/>
+      <c r="D227" s="0"/>
+      <c r="E227" s="0"/>
+      <c r="F227" s="0"/>
+      <c r="G227" s="0"/>
+      <c r="H227" s="0"/>
+      <c r="I227" s="0"/>
+      <c r="XFC227" s="0"/>
+      <c r="XFD227" s="0"/>
     </row>
     <row r="228" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K228" s="1"/>
+      <c r="A228" s="0"/>
+      <c r="B228" s="0"/>
+      <c r="C228" s="0"/>
+      <c r="D228" s="0"/>
+      <c r="E228" s="0"/>
+      <c r="F228" s="0"/>
+      <c r="G228" s="0"/>
+      <c r="H228" s="0"/>
+      <c r="I228" s="0"/>
+      <c r="XFC228" s="0"/>
+      <c r="XFD228" s="0"/>
     </row>
     <row r="229" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K229" s="1"/>
+      <c r="A229" s="0"/>
+      <c r="B229" s="0"/>
+      <c r="C229" s="0"/>
+      <c r="D229" s="0"/>
+      <c r="E229" s="0"/>
+      <c r="F229" s="0"/>
+      <c r="G229" s="0"/>
+      <c r="H229" s="0"/>
+      <c r="I229" s="0"/>
+      <c r="XFC229" s="0"/>
+      <c r="XFD229" s="0"/>
     </row>
     <row r="230" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K230" s="1"/>
+      <c r="A230" s="0"/>
+      <c r="B230" s="0"/>
+      <c r="C230" s="0"/>
+      <c r="D230" s="0"/>
+      <c r="E230" s="0"/>
+      <c r="F230" s="0"/>
+      <c r="G230" s="0"/>
+      <c r="H230" s="0"/>
+      <c r="I230" s="0"/>
+      <c r="XFC230" s="0"/>
+      <c r="XFD230" s="0"/>
+    </row>
+    <row r="231" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A231" s="0"/>
+      <c r="B231" s="0"/>
+      <c r="C231" s="0"/>
+      <c r="D231" s="0"/>
+      <c r="E231" s="0"/>
+      <c r="F231" s="0"/>
+      <c r="G231" s="0"/>
+      <c r="H231" s="0"/>
+      <c r="I231" s="0"/>
+      <c r="XFC231" s="0"/>
+      <c r="XFD231" s="0"/>
+    </row>
+    <row r="232" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A232" s="0"/>
+      <c r="B232" s="0"/>
+      <c r="C232" s="0"/>
+      <c r="D232" s="0"/>
+      <c r="E232" s="0"/>
+      <c r="F232" s="0"/>
+      <c r="G232" s="0"/>
+      <c r="H232" s="0"/>
+      <c r="I232" s="0"/>
+      <c r="XFC232" s="0"/>
+      <c r="XFD232" s="0"/>
     </row>
     <row r="233" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J233" s="1"/>
+      <c r="A233" s="0"/>
+      <c r="B233" s="0"/>
+      <c r="C233" s="0"/>
+      <c r="D233" s="0"/>
+      <c r="E233" s="0"/>
+      <c r="F233" s="0"/>
+      <c r="G233" s="0"/>
+      <c r="H233" s="0"/>
+      <c r="I233" s="0"/>
+      <c r="XFC233" s="0"/>
+      <c r="XFD233" s="0"/>
+    </row>
+    <row r="234" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A234" s="0"/>
+      <c r="B234" s="0"/>
+      <c r="C234" s="0"/>
+      <c r="D234" s="0"/>
+      <c r="E234" s="0"/>
+      <c r="F234" s="0"/>
+      <c r="G234" s="0"/>
+      <c r="H234" s="0"/>
+      <c r="I234" s="0"/>
+      <c r="XFC234" s="0"/>
+      <c r="XFD234" s="0"/>
     </row>
     <row r="235" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J235" s="1"/>
+      <c r="A235" s="0"/>
+      <c r="B235" s="0"/>
+      <c r="C235" s="0"/>
+      <c r="D235" s="0"/>
+      <c r="E235" s="0"/>
+      <c r="F235" s="0"/>
+      <c r="G235" s="0"/>
+      <c r="H235" s="0"/>
+      <c r="I235" s="0"/>
+      <c r="XFC235" s="0"/>
+      <c r="XFD235" s="0"/>
     </row>
     <row r="236" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J236" s="1"/>
+      <c r="A236" s="0"/>
+      <c r="B236" s="0"/>
+      <c r="C236" s="0"/>
+      <c r="D236" s="0"/>
+      <c r="E236" s="0"/>
+      <c r="F236" s="0"/>
+      <c r="G236" s="0"/>
+      <c r="H236" s="0"/>
+      <c r="I236" s="0"/>
+      <c r="XFC236" s="0"/>
+      <c r="XFD236" s="0"/>
     </row>
     <row r="237" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J237" s="1"/>
+      <c r="A237" s="0"/>
+      <c r="B237" s="0"/>
+      <c r="C237" s="0"/>
+      <c r="D237" s="0"/>
+      <c r="E237" s="0"/>
+      <c r="F237" s="0"/>
+      <c r="G237" s="0"/>
+      <c r="H237" s="0"/>
+      <c r="I237" s="0"/>
+      <c r="XFC237" s="0"/>
+      <c r="XFD237" s="0"/>
     </row>
     <row r="238" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J238" s="1"/>
+      <c r="A238" s="0"/>
+      <c r="B238" s="0"/>
+      <c r="C238" s="0"/>
+      <c r="D238" s="0"/>
+      <c r="E238" s="0"/>
+      <c r="F238" s="0"/>
+      <c r="G238" s="0"/>
+      <c r="H238" s="0"/>
+      <c r="I238" s="0"/>
+      <c r="XFC238" s="0"/>
+      <c r="XFD238" s="0"/>
     </row>
     <row r="239" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J239" s="1"/>
+      <c r="A239" s="0"/>
+      <c r="B239" s="0"/>
+      <c r="C239" s="0"/>
+      <c r="D239" s="0"/>
+      <c r="E239" s="0"/>
+      <c r="F239" s="0"/>
+      <c r="G239" s="0"/>
+      <c r="H239" s="0"/>
+      <c r="I239" s="0"/>
+      <c r="XFC239" s="0"/>
+      <c r="XFD239" s="0"/>
     </row>
     <row r="240" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J240" s="1"/>
+      <c r="A240" s="0"/>
+      <c r="B240" s="0"/>
+      <c r="C240" s="0"/>
+      <c r="D240" s="0"/>
+      <c r="E240" s="0"/>
+      <c r="F240" s="0"/>
+      <c r="G240" s="0"/>
+      <c r="H240" s="0"/>
+      <c r="I240" s="0"/>
+      <c r="XFC240" s="0"/>
+      <c r="XFD240" s="0"/>
     </row>
     <row r="241" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J241" s="1"/>
+      <c r="A241" s="0"/>
+      <c r="B241" s="0"/>
+      <c r="C241" s="0"/>
+      <c r="D241" s="0"/>
+      <c r="E241" s="0"/>
+      <c r="F241" s="0"/>
+      <c r="G241" s="0"/>
+      <c r="H241" s="0"/>
+      <c r="I241" s="0"/>
+      <c r="XFC241" s="0"/>
+      <c r="XFD241" s="0"/>
     </row>
     <row r="242" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J242" s="1"/>
+      <c r="A242" s="0"/>
+      <c r="B242" s="0"/>
+      <c r="C242" s="0"/>
+      <c r="D242" s="0"/>
+      <c r="E242" s="0"/>
+      <c r="F242" s="0"/>
+      <c r="G242" s="0"/>
+      <c r="H242" s="0"/>
+      <c r="I242" s="0"/>
+      <c r="XFC242" s="0"/>
+      <c r="XFD242" s="0"/>
     </row>
     <row r="243" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J243" s="1"/>
+      <c r="A243" s="0"/>
+      <c r="B243" s="0"/>
+      <c r="C243" s="0"/>
+      <c r="D243" s="0"/>
+      <c r="E243" s="0"/>
+      <c r="F243" s="0"/>
+      <c r="G243" s="0"/>
+      <c r="H243" s="0"/>
+      <c r="I243" s="0"/>
+      <c r="XFC243" s="0"/>
+      <c r="XFD243" s="0"/>
+    </row>
+    <row r="244" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A244" s="0"/>
+      <c r="B244" s="0"/>
+      <c r="C244" s="0"/>
+      <c r="D244" s="0"/>
+      <c r="E244" s="0"/>
+      <c r="F244" s="0"/>
+      <c r="G244" s="0"/>
+      <c r="H244" s="0"/>
+      <c r="I244" s="0"/>
+      <c r="XFC244" s="0"/>
+      <c r="XFD244" s="0"/>
+    </row>
+    <row r="245" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A245" s="0"/>
+      <c r="B245" s="0"/>
+      <c r="C245" s="0"/>
+      <c r="D245" s="0"/>
+      <c r="E245" s="0"/>
+      <c r="F245" s="0"/>
+      <c r="G245" s="0"/>
+      <c r="H245" s="0"/>
+      <c r="I245" s="0"/>
+      <c r="XFC245" s="0"/>
+      <c r="XFD245" s="0"/>
     </row>
     <row r="246" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J246" s="1"/>
+      <c r="A246" s="0"/>
+      <c r="B246" s="0"/>
+      <c r="C246" s="0"/>
+      <c r="D246" s="0"/>
+      <c r="E246" s="0"/>
+      <c r="F246" s="0"/>
+      <c r="G246" s="0"/>
+      <c r="H246" s="0"/>
+      <c r="I246" s="0"/>
+      <c r="XFC246" s="0"/>
+      <c r="XFD246" s="0"/>
+    </row>
+    <row r="247" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A247" s="0"/>
+      <c r="B247" s="0"/>
+      <c r="C247" s="0"/>
+      <c r="D247" s="0"/>
+      <c r="E247" s="0"/>
+      <c r="F247" s="0"/>
+      <c r="G247" s="4"/>
+      <c r="H247" s="0"/>
+      <c r="I247" s="0"/>
+      <c r="XFC247" s="0"/>
+      <c r="XFD247" s="0"/>
     </row>
     <row r="248" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K248" s="1"/>
+      <c r="A248" s="0"/>
+      <c r="B248" s="0"/>
+      <c r="C248" s="0"/>
+      <c r="D248" s="0"/>
+      <c r="E248" s="0"/>
+      <c r="F248" s="0"/>
+      <c r="G248" s="0"/>
+      <c r="H248" s="0"/>
+      <c r="I248" s="0"/>
+      <c r="XFC248" s="0"/>
+      <c r="XFD248" s="0"/>
     </row>
     <row r="249" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K249" s="1"/>
+      <c r="A249" s="0"/>
+      <c r="B249" s="0"/>
+      <c r="C249" s="0"/>
+      <c r="D249" s="0"/>
+      <c r="E249" s="0"/>
+      <c r="F249" s="0"/>
+      <c r="G249" s="0"/>
+      <c r="H249" s="0"/>
+      <c r="I249" s="0"/>
+      <c r="XFC249" s="0"/>
+      <c r="XFD249" s="0"/>
     </row>
     <row r="250" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K250" s="1"/>
+      <c r="A250" s="0"/>
+      <c r="B250" s="0"/>
+      <c r="C250" s="0"/>
+      <c r="D250" s="0"/>
+      <c r="E250" s="0"/>
+      <c r="F250" s="0"/>
+      <c r="G250" s="0"/>
+      <c r="H250" s="0"/>
+      <c r="I250" s="0"/>
+      <c r="XFC250" s="0"/>
+      <c r="XFD250" s="0"/>
+    </row>
+    <row r="251" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A251" s="0"/>
+      <c r="B251" s="0"/>
+      <c r="C251" s="0"/>
+      <c r="D251" s="0"/>
+      <c r="E251" s="0"/>
+      <c r="F251" s="0"/>
+      <c r="G251" s="0"/>
+      <c r="H251" s="0"/>
+      <c r="I251" s="0"/>
+      <c r="XFC251" s="0"/>
+      <c r="XFD251" s="0"/>
+    </row>
+    <row r="252" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A252" s="0"/>
+      <c r="B252" s="0"/>
+      <c r="C252" s="0"/>
+      <c r="D252" s="0"/>
+      <c r="E252" s="0"/>
+      <c r="F252" s="0"/>
+      <c r="G252" s="0"/>
+      <c r="H252" s="0"/>
+      <c r="I252" s="0"/>
+      <c r="XFC252" s="0"/>
+      <c r="XFD252" s="0"/>
     </row>
     <row r="253" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K253" s="1"/>
+      <c r="A253" s="0"/>
+      <c r="B253" s="0"/>
+      <c r="C253" s="0"/>
+      <c r="D253" s="0"/>
+      <c r="E253" s="0"/>
+      <c r="F253" s="0"/>
+      <c r="G253" s="0"/>
+      <c r="H253" s="0"/>
+      <c r="I253" s="0"/>
+      <c r="XFC253" s="0"/>
+      <c r="XFD253" s="0"/>
     </row>
     <row r="254" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J254" s="1"/>
-      <c r="M254" s="1"/>
+      <c r="A254" s="0"/>
+      <c r="B254" s="0"/>
+      <c r="C254" s="0"/>
+      <c r="D254" s="0"/>
+      <c r="E254" s="0"/>
+      <c r="F254" s="0"/>
+      <c r="G254" s="0"/>
+      <c r="H254" s="0"/>
+      <c r="I254" s="0"/>
+      <c r="XFC254" s="0"/>
+      <c r="XFD254" s="0"/>
     </row>
     <row r="255" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K255" s="1"/>
+      <c r="A255" s="0"/>
+      <c r="B255" s="0"/>
+      <c r="C255" s="0"/>
+      <c r="D255" s="0"/>
+      <c r="E255" s="0"/>
+      <c r="F255" s="0"/>
+      <c r="G255" s="0"/>
+      <c r="H255" s="0"/>
+      <c r="I255" s="0"/>
+      <c r="XFC255" s="0"/>
+      <c r="XFD255" s="0"/>
+    </row>
+    <row r="256" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A256" s="0"/>
+      <c r="B256" s="0"/>
+      <c r="C256" s="0"/>
+      <c r="D256" s="0"/>
+      <c r="E256" s="0"/>
+      <c r="F256" s="0"/>
+      <c r="G256" s="0"/>
+      <c r="H256" s="0"/>
+      <c r="I256" s="0"/>
+      <c r="XFC256" s="0"/>
+      <c r="XFD256" s="0"/>
     </row>
     <row r="257" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J257" s="1"/>
+      <c r="A257" s="0"/>
+      <c r="B257" s="0"/>
+      <c r="C257" s="0"/>
+      <c r="D257" s="0"/>
+      <c r="E257" s="0"/>
+      <c r="F257" s="0"/>
+      <c r="G257" s="0"/>
+      <c r="H257" s="0"/>
+      <c r="I257" s="0"/>
+      <c r="XFC257" s="0"/>
+      <c r="XFD257" s="0"/>
+    </row>
+    <row r="258" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A258" s="0"/>
+      <c r="B258" s="0"/>
+      <c r="C258" s="0"/>
+      <c r="D258" s="0"/>
+      <c r="E258" s="0"/>
+      <c r="F258" s="0"/>
+      <c r="G258" s="0"/>
+      <c r="H258" s="0"/>
+      <c r="I258" s="0"/>
+      <c r="XFC258" s="0"/>
+      <c r="XFD258" s="0"/>
+    </row>
+    <row r="259" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A259" s="0"/>
+      <c r="B259" s="0"/>
+      <c r="C259" s="0"/>
+      <c r="D259" s="0"/>
+      <c r="E259" s="0"/>
+      <c r="F259" s="0"/>
+      <c r="G259" s="0"/>
+      <c r="H259" s="0"/>
+      <c r="I259" s="0"/>
+      <c r="XFC259" s="0"/>
+      <c r="XFD259" s="0"/>
+    </row>
+    <row r="260" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A260" s="0"/>
+      <c r="B260" s="0"/>
+      <c r="C260" s="0"/>
+      <c r="D260" s="0"/>
+      <c r="E260" s="0"/>
+      <c r="F260" s="0"/>
+      <c r="G260" s="0"/>
+      <c r="H260" s="0"/>
+      <c r="I260" s="0"/>
+      <c r="XFC260" s="0"/>
+      <c r="XFD260" s="0"/>
     </row>
     <row r="261" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K261" s="1"/>
+      <c r="A261" s="0"/>
+      <c r="B261" s="0"/>
+      <c r="C261" s="0"/>
+      <c r="D261" s="0"/>
+      <c r="E261" s="0"/>
+      <c r="F261" s="0"/>
+      <c r="G261" s="0"/>
+      <c r="H261" s="0"/>
+      <c r="I261" s="0"/>
+      <c r="XFC261" s="0"/>
+      <c r="XFD261" s="0"/>
     </row>
     <row r="262" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J262" s="1"/>
+      <c r="A262" s="0"/>
+      <c r="B262" s="0"/>
+      <c r="C262" s="0"/>
+      <c r="D262" s="0"/>
+      <c r="E262" s="0"/>
+      <c r="F262" s="0"/>
+      <c r="G262" s="0"/>
+      <c r="H262" s="0"/>
+      <c r="I262" s="0"/>
+      <c r="XFC262" s="0"/>
+      <c r="XFD262" s="0"/>
     </row>
     <row r="263" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K263" s="1"/>
+      <c r="A263" s="0"/>
+      <c r="B263" s="0"/>
+      <c r="C263" s="0"/>
+      <c r="D263" s="0"/>
+      <c r="E263" s="0"/>
+      <c r="F263" s="0"/>
+      <c r="G263" s="0"/>
+      <c r="H263" s="0"/>
+      <c r="I263" s="0"/>
+      <c r="XFC263" s="0"/>
+      <c r="XFD263" s="0"/>
+    </row>
+    <row r="264" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A264" s="0"/>
+      <c r="B264" s="0"/>
+      <c r="C264" s="0"/>
+      <c r="D264" s="0"/>
+      <c r="E264" s="0"/>
+      <c r="F264" s="0"/>
+      <c r="G264" s="0"/>
+      <c r="H264" s="0"/>
+      <c r="I264" s="0"/>
+      <c r="XFC264" s="0"/>
+      <c r="XFD264" s="0"/>
     </row>
     <row r="265" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K265" s="1"/>
+      <c r="A265" s="0"/>
+      <c r="B265" s="0"/>
+      <c r="C265" s="0"/>
+      <c r="D265" s="0"/>
+      <c r="E265" s="0"/>
+      <c r="F265" s="0"/>
+      <c r="G265" s="0"/>
+      <c r="H265" s="0"/>
+      <c r="I265" s="0"/>
+      <c r="XFC265" s="0"/>
+      <c r="XFD265" s="0"/>
     </row>
     <row r="266" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K266" s="1"/>
+      <c r="A266" s="0"/>
+      <c r="B266" s="0"/>
+      <c r="C266" s="0"/>
+      <c r="D266" s="0"/>
+      <c r="E266" s="0"/>
+      <c r="F266" s="0"/>
+      <c r="G266" s="0"/>
+      <c r="H266" s="0"/>
+      <c r="I266" s="0"/>
+      <c r="XFC266" s="0"/>
+      <c r="XFD266" s="0"/>
     </row>
     <row r="267" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K267" s="1"/>
+      <c r="A267" s="0"/>
+      <c r="B267" s="0"/>
+      <c r="C267" s="0"/>
+      <c r="D267" s="0"/>
+      <c r="E267" s="0"/>
+      <c r="F267" s="0"/>
+      <c r="G267" s="0"/>
+      <c r="H267" s="0"/>
+      <c r="I267" s="0"/>
+      <c r="XFC267" s="0"/>
+      <c r="XFD267" s="0"/>
     </row>
     <row r="268" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K268" s="1"/>
+      <c r="A268" s="0"/>
+      <c r="B268" s="0"/>
+      <c r="C268" s="0"/>
+      <c r="D268" s="0"/>
+      <c r="E268" s="0"/>
+      <c r="F268" s="0"/>
+      <c r="G268" s="0"/>
+      <c r="H268" s="0"/>
+      <c r="I268" s="0"/>
+      <c r="XFC268" s="0"/>
+      <c r="XFD268" s="0"/>
     </row>
     <row r="269" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K269" s="1"/>
+      <c r="A269" s="0"/>
+      <c r="B269" s="0"/>
+      <c r="C269" s="0"/>
+      <c r="D269" s="0"/>
+      <c r="E269" s="0"/>
+      <c r="F269" s="0"/>
+      <c r="G269" s="0"/>
+      <c r="H269" s="0"/>
+      <c r="I269" s="0"/>
+      <c r="XFC269" s="0"/>
+      <c r="XFD269" s="0"/>
     </row>
     <row r="270" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K270" s="1"/>
+      <c r="A270" s="0"/>
+      <c r="B270" s="0"/>
+      <c r="C270" s="0"/>
+      <c r="D270" s="0"/>
+      <c r="E270" s="0"/>
+      <c r="F270" s="0"/>
+      <c r="G270" s="0"/>
+      <c r="H270" s="0"/>
+      <c r="I270" s="0"/>
+      <c r="XFC270" s="0"/>
+      <c r="XFD270" s="0"/>
     </row>
     <row r="271" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K271" s="1"/>
+      <c r="A271" s="0"/>
+      <c r="B271" s="0"/>
+      <c r="C271" s="0"/>
+      <c r="D271" s="0"/>
+      <c r="E271" s="0"/>
+      <c r="F271" s="0"/>
+      <c r="G271" s="0"/>
+      <c r="H271" s="0"/>
+      <c r="I271" s="0"/>
+      <c r="XFC271" s="0"/>
+      <c r="XFD271" s="0"/>
     </row>
     <row r="272" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K272" s="1"/>
+      <c r="A272" s="0"/>
+      <c r="B272" s="0"/>
+      <c r="C272" s="0"/>
+      <c r="D272" s="0"/>
+      <c r="E272" s="0"/>
+      <c r="F272" s="0"/>
+      <c r="G272" s="0"/>
+      <c r="H272" s="0"/>
+      <c r="I272" s="0"/>
+      <c r="XFC272" s="0"/>
+      <c r="XFD272" s="0"/>
     </row>
     <row r="273" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K273" s="1"/>
+      <c r="A273" s="0"/>
+      <c r="B273" s="0"/>
+      <c r="C273" s="0"/>
+      <c r="D273" s="0"/>
+      <c r="E273" s="0"/>
+      <c r="F273" s="0"/>
+      <c r="G273" s="0"/>
+      <c r="H273" s="0"/>
+      <c r="I273" s="0"/>
+      <c r="XFC273" s="0"/>
+      <c r="XFD273" s="0"/>
+    </row>
+    <row r="274" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A274" s="0"/>
+      <c r="B274" s="0"/>
+      <c r="C274" s="0"/>
+      <c r="D274" s="0"/>
+      <c r="E274" s="0"/>
+      <c r="F274" s="0"/>
+      <c r="G274" s="0"/>
+      <c r="H274" s="0"/>
+      <c r="I274" s="0"/>
+      <c r="XFC274" s="0"/>
+      <c r="XFD274" s="0"/>
+    </row>
+    <row r="275" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A275" s="0"/>
+      <c r="B275" s="0"/>
+      <c r="C275" s="0"/>
+      <c r="D275" s="0"/>
+      <c r="E275" s="0"/>
+      <c r="F275" s="0"/>
+      <c r="G275" s="0"/>
+      <c r="H275" s="0"/>
+      <c r="I275" s="0"/>
+      <c r="XFC275" s="0"/>
+      <c r="XFD275" s="0"/>
     </row>
     <row r="276" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J276" s="1"/>
+      <c r="A276" s="0"/>
+      <c r="B276" s="0"/>
+      <c r="C276" s="0"/>
+      <c r="D276" s="0"/>
+      <c r="E276" s="0"/>
+      <c r="F276" s="0"/>
+      <c r="G276" s="0"/>
+      <c r="H276" s="0"/>
+      <c r="I276" s="0"/>
+      <c r="XFC276" s="0"/>
+      <c r="XFD276" s="0"/>
+    </row>
+    <row r="277" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A277" s="0"/>
+      <c r="B277" s="0"/>
+      <c r="C277" s="0"/>
+      <c r="D277" s="0"/>
+      <c r="E277" s="0"/>
+      <c r="F277" s="0"/>
+      <c r="G277" s="0"/>
+      <c r="H277" s="0"/>
+      <c r="I277" s="0"/>
+      <c r="XFC277" s="0"/>
+      <c r="XFD277" s="0"/>
     </row>
     <row r="278" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J278" s="1"/>
+      <c r="A278" s="0"/>
+      <c r="B278" s="0"/>
+      <c r="C278" s="0"/>
+      <c r="D278" s="0"/>
+      <c r="E278" s="0"/>
+      <c r="F278" s="0"/>
+      <c r="G278" s="0"/>
+      <c r="H278" s="0"/>
+      <c r="I278" s="0"/>
+      <c r="XFC278" s="0"/>
+      <c r="XFD278" s="0"/>
     </row>
     <row r="279" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J279" s="1"/>
+      <c r="A279" s="0"/>
+      <c r="B279" s="0"/>
+      <c r="C279" s="0"/>
+      <c r="D279" s="0"/>
+      <c r="E279" s="0"/>
+      <c r="F279" s="0"/>
+      <c r="G279" s="0"/>
+      <c r="H279" s="0"/>
+      <c r="I279" s="0"/>
+      <c r="XFC279" s="0"/>
+      <c r="XFD279" s="0"/>
     </row>
     <row r="280" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J280" s="1"/>
+      <c r="A280" s="0"/>
+      <c r="B280" s="0"/>
+      <c r="C280" s="0"/>
+      <c r="D280" s="0"/>
+      <c r="E280" s="0"/>
+      <c r="F280" s="0"/>
+      <c r="G280" s="0"/>
+      <c r="H280" s="0"/>
+      <c r="I280" s="0"/>
+      <c r="XFC280" s="0"/>
+      <c r="XFD280" s="0"/>
     </row>
     <row r="281" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J281" s="1"/>
+      <c r="A281" s="0"/>
+      <c r="B281" s="0"/>
+      <c r="C281" s="0"/>
+      <c r="D281" s="0"/>
+      <c r="E281" s="0"/>
+      <c r="F281" s="0"/>
+      <c r="G281" s="0"/>
+      <c r="H281" s="0"/>
+      <c r="I281" s="0"/>
+      <c r="XFC281" s="0"/>
+      <c r="XFD281" s="0"/>
     </row>
     <row r="282" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J282" s="1"/>
+      <c r="A282" s="0"/>
+      <c r="B282" s="0"/>
+      <c r="C282" s="0"/>
+      <c r="D282" s="0"/>
+      <c r="E282" s="0"/>
+      <c r="F282" s="0"/>
+      <c r="G282" s="0"/>
+      <c r="H282" s="0"/>
+      <c r="I282" s="0"/>
+      <c r="XFC282" s="0"/>
+      <c r="XFD282" s="0"/>
     </row>
     <row r="283" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J283" s="1"/>
+      <c r="A283" s="0"/>
+      <c r="B283" s="0"/>
+      <c r="C283" s="0"/>
+      <c r="D283" s="0"/>
+      <c r="E283" s="0"/>
+      <c r="F283" s="0"/>
+      <c r="G283" s="0"/>
+      <c r="H283" s="0"/>
+      <c r="I283" s="0"/>
+      <c r="XFC283" s="0"/>
+      <c r="XFD283" s="0"/>
     </row>
     <row r="284" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J284" s="1"/>
+      <c r="A284" s="0"/>
+      <c r="B284" s="0"/>
+      <c r="C284" s="0"/>
+      <c r="D284" s="0"/>
+      <c r="E284" s="0"/>
+      <c r="F284" s="0"/>
+      <c r="G284" s="0"/>
+      <c r="H284" s="0"/>
+      <c r="I284" s="0"/>
+      <c r="XFC284" s="0"/>
+      <c r="XFD284" s="0"/>
     </row>
     <row r="285" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J285" s="1"/>
+      <c r="A285" s="0"/>
+      <c r="B285" s="0"/>
+      <c r="C285" s="0"/>
+      <c r="D285" s="0"/>
+      <c r="E285" s="0"/>
+      <c r="F285" s="0"/>
+      <c r="G285" s="0"/>
+      <c r="H285" s="0"/>
+      <c r="I285" s="0"/>
+      <c r="XFC285" s="0"/>
+      <c r="XFD285" s="0"/>
     </row>
     <row r="286" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J286" s="1"/>
+      <c r="A286" s="0"/>
+      <c r="B286" s="0"/>
+      <c r="C286" s="0"/>
+      <c r="D286" s="0"/>
+      <c r="E286" s="0"/>
+      <c r="F286" s="0"/>
+      <c r="G286" s="0"/>
+      <c r="H286" s="0"/>
+      <c r="I286" s="0"/>
+      <c r="XFC286" s="0"/>
+      <c r="XFD286" s="0"/>
+    </row>
+    <row r="287" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A287" s="0"/>
+      <c r="B287" s="0"/>
+      <c r="C287" s="0"/>
+      <c r="D287" s="0"/>
+      <c r="E287" s="0"/>
+      <c r="F287" s="0"/>
+      <c r="G287" s="0"/>
+      <c r="H287" s="0"/>
+      <c r="I287" s="0"/>
+      <c r="XFC287" s="0"/>
+      <c r="XFD287" s="0"/>
+    </row>
+    <row r="288" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A288" s="0"/>
+      <c r="B288" s="0"/>
+      <c r="C288" s="0"/>
+      <c r="D288" s="0"/>
+      <c r="E288" s="0"/>
+      <c r="F288" s="0"/>
+      <c r="G288" s="0"/>
+      <c r="H288" s="0"/>
+      <c r="I288" s="0"/>
+      <c r="XFC288" s="0"/>
+      <c r="XFD288" s="0"/>
     </row>
     <row r="289" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J289" s="1"/>
+      <c r="A289" s="0"/>
+      <c r="B289" s="0"/>
+      <c r="C289" s="0"/>
+      <c r="D289" s="0"/>
+      <c r="E289" s="0"/>
+      <c r="F289" s="0"/>
+      <c r="G289" s="0"/>
+      <c r="H289" s="0"/>
+      <c r="I289" s="0"/>
+      <c r="XFC289" s="0"/>
+      <c r="XFD289" s="0"/>
+    </row>
+    <row r="290" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A290" s="0"/>
+      <c r="B290" s="0"/>
+      <c r="C290" s="0"/>
+      <c r="D290" s="0"/>
+      <c r="E290" s="0"/>
+      <c r="F290" s="0"/>
+      <c r="G290" s="4"/>
+      <c r="H290" s="0"/>
+      <c r="I290" s="0"/>
+      <c r="XFC290" s="0"/>
+      <c r="XFD290" s="0"/>
     </row>
     <row r="291" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K291" s="1"/>
+      <c r="A291" s="0"/>
+      <c r="B291" s="0"/>
+      <c r="C291" s="0"/>
+      <c r="D291" s="0"/>
+      <c r="E291" s="0"/>
+      <c r="F291" s="0"/>
+      <c r="G291" s="0"/>
+      <c r="H291" s="0"/>
+      <c r="I291" s="0"/>
+      <c r="XFC291" s="0"/>
+      <c r="XFD291" s="0"/>
     </row>
     <row r="292" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K292" s="1"/>
+      <c r="A292" s="0"/>
+      <c r="B292" s="0"/>
+      <c r="C292" s="0"/>
+      <c r="D292" s="0"/>
+      <c r="E292" s="0"/>
+      <c r="F292" s="0"/>
+      <c r="G292" s="0"/>
+      <c r="H292" s="0"/>
+      <c r="I292" s="0"/>
+      <c r="XFC292" s="0"/>
+      <c r="XFD292" s="0"/>
     </row>
     <row r="293" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K293" s="1"/>
+      <c r="A293" s="0"/>
+      <c r="B293" s="0"/>
+      <c r="C293" s="0"/>
+      <c r="D293" s="0"/>
+      <c r="E293" s="0"/>
+      <c r="F293" s="0"/>
+      <c r="G293" s="0"/>
+      <c r="H293" s="0"/>
+      <c r="I293" s="0"/>
+      <c r="XFC293" s="0"/>
+      <c r="XFD293" s="0"/>
+    </row>
+    <row r="294" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A294" s="0"/>
+      <c r="B294" s="0"/>
+      <c r="C294" s="0"/>
+      <c r="D294" s="0"/>
+      <c r="E294" s="0"/>
+      <c r="F294" s="0"/>
+      <c r="G294" s="0"/>
+      <c r="H294" s="0"/>
+      <c r="I294" s="0"/>
+      <c r="XFC294" s="0"/>
+      <c r="XFD294" s="0"/>
+    </row>
+    <row r="295" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A295" s="0"/>
+      <c r="B295" s="0"/>
+      <c r="C295" s="0"/>
+      <c r="D295" s="0"/>
+      <c r="E295" s="0"/>
+      <c r="F295" s="0"/>
+      <c r="G295" s="0"/>
+      <c r="H295" s="0"/>
+      <c r="I295" s="0"/>
+      <c r="XFC295" s="0"/>
+      <c r="XFD295" s="0"/>
     </row>
     <row r="296" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K296" s="1"/>
+      <c r="A296" s="0"/>
+      <c r="B296" s="0"/>
+      <c r="C296" s="0"/>
+      <c r="D296" s="0"/>
+      <c r="E296" s="0"/>
+      <c r="F296" s="0"/>
+      <c r="G296" s="0"/>
+      <c r="H296" s="0"/>
+      <c r="I296" s="0"/>
+      <c r="XFC296" s="0"/>
+      <c r="XFD296" s="0"/>
     </row>
     <row r="297" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J297" s="1"/>
-      <c r="M297" s="1"/>
+      <c r="A297" s="0"/>
+      <c r="B297" s="0"/>
+      <c r="C297" s="0"/>
+      <c r="D297" s="0"/>
+      <c r="E297" s="0"/>
+      <c r="F297" s="0"/>
+      <c r="G297" s="0"/>
+      <c r="H297" s="0"/>
+      <c r="I297" s="0"/>
+      <c r="XFC297" s="0"/>
+      <c r="XFD297" s="0"/>
     </row>
     <row r="298" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K298" s="1"/>
+      <c r="A298" s="0"/>
+      <c r="B298" s="0"/>
+      <c r="C298" s="0"/>
+      <c r="D298" s="0"/>
+      <c r="E298" s="0"/>
+      <c r="F298" s="0"/>
+      <c r="G298" s="0"/>
+      <c r="H298" s="0"/>
+      <c r="I298" s="0"/>
+      <c r="XFC298" s="0"/>
+      <c r="XFD298" s="0"/>
+    </row>
+    <row r="299" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A299" s="0"/>
+      <c r="B299" s="0"/>
+      <c r="C299" s="0"/>
+      <c r="D299" s="0"/>
+      <c r="E299" s="0"/>
+      <c r="F299" s="0"/>
+      <c r="G299" s="0"/>
+      <c r="H299" s="0"/>
+      <c r="I299" s="0"/>
+      <c r="XFC299" s="0"/>
+      <c r="XFD299" s="0"/>
     </row>
     <row r="300" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J300" s="1"/>
+      <c r="A300" s="0"/>
+      <c r="B300" s="0"/>
+      <c r="C300" s="0"/>
+      <c r="D300" s="0"/>
+      <c r="E300" s="0"/>
+      <c r="F300" s="0"/>
+      <c r="G300" s="0"/>
+      <c r="H300" s="0"/>
+      <c r="I300" s="0"/>
+      <c r="XFC300" s="0"/>
+      <c r="XFD300" s="0"/>
+    </row>
+    <row r="301" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A301" s="0"/>
+      <c r="B301" s="0"/>
+      <c r="C301" s="0"/>
+      <c r="D301" s="0"/>
+      <c r="E301" s="0"/>
+      <c r="F301" s="0"/>
+      <c r="G301" s="0"/>
+      <c r="H301" s="0"/>
+      <c r="I301" s="0"/>
+      <c r="XFC301" s="0"/>
+      <c r="XFD301" s="0"/>
+    </row>
+    <row r="302" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A302" s="0"/>
+      <c r="B302" s="0"/>
+      <c r="C302" s="0"/>
+      <c r="D302" s="0"/>
+      <c r="E302" s="0"/>
+      <c r="F302" s="0"/>
+      <c r="G302" s="0"/>
+      <c r="H302" s="0"/>
+      <c r="I302" s="0"/>
+      <c r="XFC302" s="0"/>
+      <c r="XFD302" s="0"/>
+    </row>
+    <row r="303" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A303" s="0"/>
+      <c r="B303" s="0"/>
+      <c r="C303" s="0"/>
+      <c r="D303" s="0"/>
+      <c r="E303" s="0"/>
+      <c r="F303" s="0"/>
+      <c r="G303" s="0"/>
+      <c r="H303" s="0"/>
+      <c r="I303" s="0"/>
+      <c r="XFC303" s="0"/>
+      <c r="XFD303" s="0"/>
     </row>
     <row r="304" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K304" s="1"/>
+      <c r="A304" s="0"/>
+      <c r="B304" s="0"/>
+      <c r="C304" s="0"/>
+      <c r="D304" s="0"/>
+      <c r="E304" s="0"/>
+      <c r="F304" s="0"/>
+      <c r="G304" s="0"/>
+      <c r="H304" s="0"/>
+      <c r="I304" s="0"/>
+      <c r="XFC304" s="0"/>
+      <c r="XFD304" s="0"/>
     </row>
     <row r="305" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J305" s="1"/>
+      <c r="A305" s="0"/>
+      <c r="B305" s="0"/>
+      <c r="C305" s="0"/>
+      <c r="D305" s="0"/>
+      <c r="E305" s="0"/>
+      <c r="F305" s="0"/>
+      <c r="G305" s="0"/>
+      <c r="H305" s="0"/>
+      <c r="I305" s="0"/>
+      <c r="XFC305" s="0"/>
+      <c r="XFD305" s="0"/>
     </row>
     <row r="306" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K306" s="1"/>
+      <c r="A306" s="0"/>
+      <c r="B306" s="0"/>
+      <c r="C306" s="0"/>
+      <c r="D306" s="0"/>
+      <c r="E306" s="0"/>
+      <c r="F306" s="0"/>
+      <c r="G306" s="0"/>
+      <c r="H306" s="0"/>
+      <c r="I306" s="0"/>
+      <c r="XFC306" s="0"/>
+      <c r="XFD306" s="0"/>
+    </row>
+    <row r="307" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A307" s="0"/>
+      <c r="B307" s="0"/>
+      <c r="C307" s="0"/>
+      <c r="D307" s="0"/>
+      <c r="E307" s="0"/>
+      <c r="F307" s="0"/>
+      <c r="G307" s="0"/>
+      <c r="H307" s="0"/>
+      <c r="I307" s="0"/>
+      <c r="XFC307" s="0"/>
+      <c r="XFD307" s="0"/>
     </row>
     <row r="308" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K308" s="1"/>
+      <c r="A308" s="0"/>
+      <c r="B308" s="0"/>
+      <c r="C308" s="0"/>
+      <c r="D308" s="0"/>
+      <c r="E308" s="0"/>
+      <c r="F308" s="0"/>
+      <c r="G308" s="0"/>
+      <c r="H308" s="0"/>
+      <c r="I308" s="0"/>
+      <c r="XFC308" s="0"/>
+      <c r="XFD308" s="0"/>
     </row>
     <row r="309" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K309" s="1"/>
+      <c r="A309" s="0"/>
+      <c r="B309" s="0"/>
+      <c r="C309" s="0"/>
+      <c r="D309" s="0"/>
+      <c r="E309" s="0"/>
+      <c r="F309" s="0"/>
+      <c r="G309" s="0"/>
+      <c r="H309" s="0"/>
+      <c r="I309" s="0"/>
+      <c r="XFC309" s="0"/>
+      <c r="XFD309" s="0"/>
     </row>
     <row r="310" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K310" s="1"/>
+      <c r="A310" s="0"/>
+      <c r="B310" s="0"/>
+      <c r="C310" s="0"/>
+      <c r="D310" s="0"/>
+      <c r="E310" s="0"/>
+      <c r="F310" s="0"/>
+      <c r="G310" s="0"/>
+      <c r="H310" s="0"/>
+      <c r="I310" s="0"/>
+      <c r="XFC310" s="0"/>
+      <c r="XFD310" s="0"/>
     </row>
     <row r="311" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K311" s="1"/>
+      <c r="A311" s="0"/>
+      <c r="B311" s="0"/>
+      <c r="C311" s="0"/>
+      <c r="D311" s="0"/>
+      <c r="E311" s="0"/>
+      <c r="F311" s="0"/>
+      <c r="G311" s="0"/>
+      <c r="H311" s="0"/>
+      <c r="I311" s="0"/>
+      <c r="XFC311" s="0"/>
+      <c r="XFD311" s="0"/>
     </row>
     <row r="312" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K312" s="1"/>
+      <c r="A312" s="0"/>
+      <c r="B312" s="0"/>
+      <c r="C312" s="0"/>
+      <c r="D312" s="0"/>
+      <c r="E312" s="0"/>
+      <c r="F312" s="0"/>
+      <c r="G312" s="0"/>
+      <c r="H312" s="0"/>
+      <c r="I312" s="0"/>
+      <c r="XFC312" s="0"/>
+      <c r="XFD312" s="0"/>
     </row>
     <row r="313" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K313" s="1"/>
+      <c r="A313" s="0"/>
+      <c r="B313" s="0"/>
+      <c r="C313" s="0"/>
+      <c r="D313" s="0"/>
+      <c r="E313" s="0"/>
+      <c r="F313" s="0"/>
+      <c r="G313" s="0"/>
+      <c r="H313" s="0"/>
+      <c r="I313" s="0"/>
+      <c r="XFC313" s="0"/>
+      <c r="XFD313" s="0"/>
     </row>
     <row r="314" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K314" s="1"/>
+      <c r="A314" s="0"/>
+      <c r="B314" s="0"/>
+      <c r="C314" s="0"/>
+      <c r="D314" s="0"/>
+      <c r="E314" s="0"/>
+      <c r="F314" s="0"/>
+      <c r="G314" s="0"/>
+      <c r="H314" s="0"/>
+      <c r="I314" s="0"/>
+      <c r="XFC314" s="0"/>
+      <c r="XFD314" s="0"/>
     </row>
     <row r="315" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K315" s="1"/>
+      <c r="A315" s="0"/>
+      <c r="B315" s="0"/>
+      <c r="C315" s="0"/>
+      <c r="D315" s="0"/>
+      <c r="E315" s="0"/>
+      <c r="F315" s="0"/>
+      <c r="G315" s="0"/>
+      <c r="H315" s="0"/>
+      <c r="I315" s="0"/>
+      <c r="XFC315" s="0"/>
+      <c r="XFD315" s="0"/>
     </row>
     <row r="316" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K316" s="1"/>
+      <c r="A316" s="0"/>
+      <c r="B316" s="0"/>
+      <c r="C316" s="0"/>
+      <c r="D316" s="0"/>
+      <c r="E316" s="0"/>
+      <c r="F316" s="0"/>
+      <c r="G316" s="0"/>
+      <c r="H316" s="0"/>
+      <c r="I316" s="0"/>
+      <c r="XFC316" s="0"/>
+      <c r="XFD316" s="0"/>
+    </row>
+    <row r="317" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A317" s="0"/>
+      <c r="B317" s="0"/>
+      <c r="C317" s="0"/>
+      <c r="D317" s="0"/>
+      <c r="E317" s="0"/>
+      <c r="F317" s="0"/>
+      <c r="G317" s="0"/>
+      <c r="H317" s="0"/>
+      <c r="I317" s="0"/>
+      <c r="XFC317" s="0"/>
+      <c r="XFD317" s="0"/>
+    </row>
+    <row r="318" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A318" s="0"/>
+      <c r="B318" s="0"/>
+      <c r="C318" s="0"/>
+      <c r="D318" s="0"/>
+      <c r="E318" s="0"/>
+      <c r="F318" s="0"/>
+      <c r="G318" s="0"/>
+      <c r="H318" s="0"/>
+      <c r="I318" s="0"/>
+      <c r="XFC318" s="0"/>
+      <c r="XFD318" s="0"/>
     </row>
     <row r="319" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J319" s="1"/>
+      <c r="A319" s="0"/>
+      <c r="B319" s="0"/>
+      <c r="C319" s="0"/>
+      <c r="D319" s="0"/>
+      <c r="E319" s="0"/>
+      <c r="F319" s="0"/>
+      <c r="G319" s="0"/>
+      <c r="H319" s="0"/>
+      <c r="I319" s="0"/>
+      <c r="XFC319" s="0"/>
+      <c r="XFD319" s="0"/>
+    </row>
+    <row r="320" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A320" s="0"/>
+      <c r="B320" s="0"/>
+      <c r="C320" s="0"/>
+      <c r="D320" s="0"/>
+      <c r="E320" s="0"/>
+      <c r="F320" s="0"/>
+      <c r="G320" s="0"/>
+      <c r="H320" s="0"/>
+      <c r="I320" s="0"/>
+      <c r="XFC320" s="0"/>
+      <c r="XFD320" s="0"/>
     </row>
     <row r="321" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J321" s="1"/>
+      <c r="A321" s="0"/>
+      <c r="B321" s="0"/>
+      <c r="C321" s="0"/>
+      <c r="D321" s="0"/>
+      <c r="E321" s="0"/>
+      <c r="F321" s="0"/>
+      <c r="G321" s="0"/>
+      <c r="H321" s="0"/>
+      <c r="I321" s="0"/>
+      <c r="XFC321" s="0"/>
+      <c r="XFD321" s="0"/>
     </row>
     <row r="322" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J322" s="1"/>
+      <c r="A322" s="0"/>
+      <c r="B322" s="0"/>
+      <c r="C322" s="0"/>
+      <c r="D322" s="0"/>
+      <c r="E322" s="0"/>
+      <c r="F322" s="0"/>
+      <c r="G322" s="0"/>
+      <c r="H322" s="0"/>
+      <c r="I322" s="0"/>
+      <c r="XFC322" s="0"/>
+      <c r="XFD322" s="0"/>
     </row>
     <row r="323" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J323" s="1"/>
+      <c r="A323" s="0"/>
+      <c r="B323" s="0"/>
+      <c r="C323" s="0"/>
+      <c r="D323" s="0"/>
+      <c r="E323" s="0"/>
+      <c r="F323" s="0"/>
+      <c r="G323" s="0"/>
+      <c r="H323" s="0"/>
+      <c r="I323" s="0"/>
+      <c r="XFC323" s="0"/>
+      <c r="XFD323" s="0"/>
     </row>
     <row r="324" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J324" s="1"/>
+      <c r="A324" s="0"/>
+      <c r="B324" s="0"/>
+      <c r="C324" s="0"/>
+      <c r="D324" s="0"/>
+      <c r="E324" s="0"/>
+      <c r="F324" s="0"/>
+      <c r="G324" s="0"/>
+      <c r="H324" s="0"/>
+      <c r="I324" s="0"/>
+      <c r="XFC324" s="0"/>
+      <c r="XFD324" s="0"/>
     </row>
     <row r="325" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J325" s="1"/>
+      <c r="A325" s="0"/>
+      <c r="B325" s="0"/>
+      <c r="C325" s="0"/>
+      <c r="D325" s="0"/>
+      <c r="E325" s="0"/>
+      <c r="F325" s="0"/>
+      <c r="G325" s="0"/>
+      <c r="H325" s="0"/>
+      <c r="I325" s="0"/>
+      <c r="XFC325" s="0"/>
+      <c r="XFD325" s="0"/>
     </row>
     <row r="326" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J326" s="1"/>
+      <c r="A326" s="0"/>
+      <c r="B326" s="0"/>
+      <c r="C326" s="0"/>
+      <c r="D326" s="0"/>
+      <c r="E326" s="0"/>
+      <c r="F326" s="0"/>
+      <c r="G326" s="0"/>
+      <c r="H326" s="0"/>
+      <c r="I326" s="0"/>
+      <c r="XFC326" s="0"/>
+      <c r="XFD326" s="0"/>
     </row>
     <row r="327" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J327" s="1"/>
+      <c r="A327" s="0"/>
+      <c r="B327" s="0"/>
+      <c r="C327" s="0"/>
+      <c r="D327" s="0"/>
+      <c r="E327" s="0"/>
+      <c r="F327" s="0"/>
+      <c r="G327" s="0"/>
+      <c r="H327" s="0"/>
+      <c r="I327" s="0"/>
+      <c r="XFC327" s="0"/>
+      <c r="XFD327" s="0"/>
     </row>
     <row r="328" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J328" s="1"/>
+      <c r="A328" s="0"/>
+      <c r="B328" s="0"/>
+      <c r="C328" s="0"/>
+      <c r="D328" s="0"/>
+      <c r="E328" s="0"/>
+      <c r="F328" s="0"/>
+      <c r="G328" s="0"/>
+      <c r="H328" s="0"/>
+      <c r="I328" s="0"/>
+      <c r="XFC328" s="0"/>
+      <c r="XFD328" s="0"/>
     </row>
     <row r="329" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J329" s="1"/>
+      <c r="A329" s="0"/>
+      <c r="B329" s="0"/>
+      <c r="C329" s="0"/>
+      <c r="D329" s="0"/>
+      <c r="E329" s="0"/>
+      <c r="F329" s="0"/>
+      <c r="G329" s="0"/>
+      <c r="H329" s="0"/>
+      <c r="I329" s="0"/>
+      <c r="XFC329" s="0"/>
+      <c r="XFD329" s="0"/>
+    </row>
+    <row r="330" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A330" s="0"/>
+      <c r="B330" s="0"/>
+      <c r="C330" s="0"/>
+      <c r="D330" s="0"/>
+      <c r="E330" s="0"/>
+      <c r="F330" s="0"/>
+      <c r="G330" s="0"/>
+      <c r="H330" s="0"/>
+      <c r="I330" s="0"/>
+      <c r="XFC330" s="0"/>
+      <c r="XFD330" s="0"/>
+    </row>
+    <row r="331" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A331" s="0"/>
+      <c r="B331" s="0"/>
+      <c r="C331" s="0"/>
+      <c r="D331" s="0"/>
+      <c r="E331" s="0"/>
+      <c r="F331" s="0"/>
+      <c r="G331" s="0"/>
+      <c r="H331" s="0"/>
+      <c r="I331" s="0"/>
+      <c r="XFC331" s="0"/>
+      <c r="XFD331" s="0"/>
     </row>
     <row r="332" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J332" s="1"/>
+      <c r="A332" s="0"/>
+      <c r="B332" s="0"/>
+      <c r="C332" s="0"/>
+      <c r="D332" s="0"/>
+      <c r="E332" s="0"/>
+      <c r="F332" s="0"/>
+      <c r="G332" s="0"/>
+      <c r="H332" s="0"/>
+      <c r="I332" s="0"/>
+      <c r="XFC332" s="0"/>
+      <c r="XFD332" s="0"/>
+    </row>
+    <row r="333" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A333" s="0"/>
+      <c r="B333" s="0"/>
+      <c r="C333" s="0"/>
+      <c r="D333" s="0"/>
+      <c r="E333" s="0"/>
+      <c r="F333" s="0"/>
+      <c r="G333" s="4"/>
+      <c r="H333" s="0"/>
+      <c r="I333" s="0"/>
+      <c r="XFC333" s="0"/>
+      <c r="XFD333" s="0"/>
     </row>
     <row r="334" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K334" s="1"/>
+      <c r="A334" s="0"/>
+      <c r="B334" s="0"/>
+      <c r="C334" s="0"/>
+      <c r="D334" s="0"/>
+      <c r="E334" s="0"/>
+      <c r="F334" s="0"/>
+      <c r="G334" s="0"/>
+      <c r="H334" s="0"/>
+      <c r="I334" s="0"/>
+      <c r="XFC334" s="0"/>
+      <c r="XFD334" s="0"/>
     </row>
     <row r="335" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K335" s="1"/>
+      <c r="A335" s="0"/>
+      <c r="B335" s="0"/>
+      <c r="C335" s="0"/>
+      <c r="D335" s="0"/>
+      <c r="E335" s="0"/>
+      <c r="F335" s="0"/>
+      <c r="G335" s="0"/>
+      <c r="H335" s="0"/>
+      <c r="I335" s="0"/>
+      <c r="XFC335" s="0"/>
+      <c r="XFD335" s="0"/>
     </row>
     <row r="336" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K336" s="1"/>
+      <c r="A336" s="0"/>
+      <c r="B336" s="0"/>
+      <c r="C336" s="0"/>
+      <c r="D336" s="0"/>
+      <c r="E336" s="0"/>
+      <c r="F336" s="0"/>
+      <c r="G336" s="0"/>
+      <c r="H336" s="0"/>
+      <c r="I336" s="0"/>
+      <c r="XFC336" s="0"/>
+      <c r="XFD336" s="0"/>
+    </row>
+    <row r="337" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A337" s="0"/>
+      <c r="B337" s="0"/>
+      <c r="C337" s="0"/>
+      <c r="D337" s="0"/>
+      <c r="E337" s="0"/>
+      <c r="F337" s="0"/>
+      <c r="G337" s="0"/>
+      <c r="H337" s="0"/>
+      <c r="I337" s="0"/>
+      <c r="XFC337" s="0"/>
+      <c r="XFD337" s="0"/>
+    </row>
+    <row r="338" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A338" s="0"/>
+      <c r="B338" s="0"/>
+      <c r="C338" s="0"/>
+      <c r="D338" s="0"/>
+      <c r="E338" s="0"/>
+      <c r="F338" s="0"/>
+      <c r="G338" s="0"/>
+      <c r="H338" s="0"/>
+      <c r="I338" s="0"/>
+      <c r="XFC338" s="0"/>
+      <c r="XFD338" s="0"/>
     </row>
     <row r="339" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K339" s="1"/>
+      <c r="A339" s="0"/>
+      <c r="B339" s="0"/>
+      <c r="C339" s="0"/>
+      <c r="D339" s="0"/>
+      <c r="E339" s="0"/>
+      <c r="F339" s="0"/>
+      <c r="G339" s="0"/>
+      <c r="H339" s="0"/>
+      <c r="I339" s="0"/>
+      <c r="XFC339" s="0"/>
+      <c r="XFD339" s="0"/>
     </row>
     <row r="340" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J340" s="1"/>
-      <c r="M340" s="1"/>
+      <c r="A340" s="0"/>
+      <c r="B340" s="0"/>
+      <c r="C340" s="0"/>
+      <c r="D340" s="0"/>
+      <c r="E340" s="0"/>
+      <c r="F340" s="0"/>
+      <c r="G340" s="0"/>
+      <c r="H340" s="0"/>
+      <c r="I340" s="0"/>
+      <c r="XFC340" s="0"/>
+      <c r="XFD340" s="0"/>
     </row>
     <row r="341" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K341" s="1"/>
+      <c r="A341" s="0"/>
+      <c r="B341" s="0"/>
+      <c r="C341" s="0"/>
+      <c r="D341" s="0"/>
+      <c r="E341" s="0"/>
+      <c r="F341" s="0"/>
+      <c r="G341" s="0"/>
+      <c r="H341" s="0"/>
+      <c r="I341" s="0"/>
+      <c r="XFC341" s="0"/>
+      <c r="XFD341" s="0"/>
+    </row>
+    <row r="342" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A342" s="0"/>
+      <c r="B342" s="0"/>
+      <c r="C342" s="0"/>
+      <c r="D342" s="0"/>
+      <c r="E342" s="0"/>
+      <c r="F342" s="0"/>
+      <c r="G342" s="0"/>
+      <c r="H342" s="0"/>
+      <c r="I342" s="0"/>
+      <c r="XFC342" s="0"/>
+      <c r="XFD342" s="0"/>
     </row>
     <row r="343" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J343" s="1"/>
+      <c r="A343" s="0"/>
+      <c r="B343" s="0"/>
+      <c r="C343" s="0"/>
+      <c r="D343" s="0"/>
+      <c r="E343" s="0"/>
+      <c r="F343" s="0"/>
+      <c r="G343" s="0"/>
+      <c r="H343" s="0"/>
+      <c r="I343" s="0"/>
+      <c r="XFC343" s="0"/>
+      <c r="XFD343" s="0"/>
+    </row>
+    <row r="344" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A344" s="0"/>
+      <c r="B344" s="0"/>
+      <c r="C344" s="0"/>
+      <c r="D344" s="0"/>
+      <c r="E344" s="0"/>
+      <c r="F344" s="0"/>
+      <c r="G344" s="0"/>
+      <c r="H344" s="0"/>
+      <c r="I344" s="0"/>
+      <c r="XFC344" s="0"/>
+      <c r="XFD344" s="0"/>
+    </row>
+    <row r="345" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A345" s="0"/>
+      <c r="B345" s="0"/>
+      <c r="C345" s="0"/>
+      <c r="D345" s="0"/>
+      <c r="E345" s="0"/>
+      <c r="F345" s="0"/>
+      <c r="G345" s="0"/>
+      <c r="H345" s="0"/>
+      <c r="I345" s="0"/>
+      <c r="XFC345" s="0"/>
+      <c r="XFD345" s="0"/>
+    </row>
+    <row r="346" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A346" s="0"/>
+      <c r="B346" s="0"/>
+      <c r="C346" s="0"/>
+      <c r="D346" s="0"/>
+      <c r="E346" s="0"/>
+      <c r="F346" s="0"/>
+      <c r="G346" s="0"/>
+      <c r="H346" s="0"/>
+      <c r="I346" s="0"/>
+      <c r="XFC346" s="0"/>
+      <c r="XFD346" s="0"/>
     </row>
     <row r="347" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K347" s="1"/>
+      <c r="A347" s="0"/>
+      <c r="B347" s="0"/>
+      <c r="C347" s="0"/>
+      <c r="D347" s="0"/>
+      <c r="E347" s="0"/>
+      <c r="F347" s="0"/>
+      <c r="G347" s="0"/>
+      <c r="H347" s="0"/>
+      <c r="I347" s="0"/>
+      <c r="XFC347" s="0"/>
+      <c r="XFD347" s="0"/>
     </row>
     <row r="348" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J348" s="1"/>
+      <c r="A348" s="0"/>
+      <c r="B348" s="0"/>
+      <c r="C348" s="0"/>
+      <c r="D348" s="0"/>
+      <c r="E348" s="0"/>
+      <c r="F348" s="0"/>
+      <c r="G348" s="0"/>
+      <c r="H348" s="0"/>
+      <c r="I348" s="0"/>
+      <c r="XFC348" s="0"/>
+      <c r="XFD348" s="0"/>
     </row>
     <row r="349" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K349" s="1"/>
+      <c r="A349" s="0"/>
+      <c r="B349" s="0"/>
+      <c r="C349" s="0"/>
+      <c r="D349" s="0"/>
+      <c r="E349" s="0"/>
+      <c r="F349" s="0"/>
+      <c r="G349" s="0"/>
+      <c r="H349" s="0"/>
+      <c r="I349" s="0"/>
+      <c r="XFC349" s="0"/>
+      <c r="XFD349" s="0"/>
+    </row>
+    <row r="350" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A350" s="0"/>
+      <c r="B350" s="0"/>
+      <c r="C350" s="0"/>
+      <c r="D350" s="0"/>
+      <c r="E350" s="0"/>
+      <c r="F350" s="0"/>
+      <c r="G350" s="0"/>
+      <c r="H350" s="0"/>
+      <c r="I350" s="0"/>
+      <c r="XFC350" s="0"/>
+      <c r="XFD350" s="0"/>
     </row>
     <row r="351" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K351" s="1"/>
+      <c r="A351" s="0"/>
+      <c r="B351" s="0"/>
+      <c r="C351" s="0"/>
+      <c r="D351" s="0"/>
+      <c r="E351" s="0"/>
+      <c r="F351" s="0"/>
+      <c r="G351" s="0"/>
+      <c r="H351" s="0"/>
+      <c r="I351" s="0"/>
+      <c r="XFC351" s="0"/>
+      <c r="XFD351" s="0"/>
     </row>
     <row r="352" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K352" s="1"/>
+      <c r="A352" s="0"/>
+      <c r="B352" s="0"/>
+      <c r="C352" s="0"/>
+      <c r="D352" s="0"/>
+      <c r="E352" s="0"/>
+      <c r="F352" s="0"/>
+      <c r="G352" s="0"/>
+      <c r="H352" s="0"/>
+      <c r="I352" s="0"/>
+      <c r="XFC352" s="0"/>
+      <c r="XFD352" s="0"/>
     </row>
     <row r="353" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K353" s="1"/>
+      <c r="A353" s="0"/>
+      <c r="B353" s="0"/>
+      <c r="C353" s="0"/>
+      <c r="D353" s="0"/>
+      <c r="E353" s="0"/>
+      <c r="F353" s="0"/>
+      <c r="G353" s="0"/>
+      <c r="H353" s="0"/>
+      <c r="I353" s="0"/>
+      <c r="XFC353" s="0"/>
+      <c r="XFD353" s="0"/>
     </row>
     <row r="354" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K354" s="1"/>
+      <c r="A354" s="0"/>
+      <c r="B354" s="0"/>
+      <c r="C354" s="0"/>
+      <c r="D354" s="0"/>
+      <c r="E354" s="0"/>
+      <c r="F354" s="0"/>
+      <c r="G354" s="0"/>
+      <c r="H354" s="0"/>
+      <c r="I354" s="0"/>
+      <c r="XFC354" s="0"/>
+      <c r="XFD354" s="0"/>
     </row>
     <row r="355" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K355" s="1"/>
+      <c r="A355" s="0"/>
+      <c r="B355" s="0"/>
+      <c r="C355" s="0"/>
+      <c r="D355" s="0"/>
+      <c r="E355" s="0"/>
+      <c r="F355" s="0"/>
+      <c r="G355" s="0"/>
+      <c r="H355" s="0"/>
+      <c r="I355" s="0"/>
+      <c r="XFC355" s="0"/>
+      <c r="XFD355" s="0"/>
     </row>
     <row r="356" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K356" s="1"/>
+      <c r="A356" s="0"/>
+      <c r="B356" s="0"/>
+      <c r="C356" s="0"/>
+      <c r="D356" s="0"/>
+      <c r="E356" s="0"/>
+      <c r="F356" s="0"/>
+      <c r="G356" s="0"/>
+      <c r="H356" s="0"/>
+      <c r="I356" s="0"/>
+      <c r="XFC356" s="0"/>
+      <c r="XFD356" s="0"/>
     </row>
     <row r="357" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K357" s="1"/>
+      <c r="A357" s="0"/>
+      <c r="B357" s="0"/>
+      <c r="C357" s="0"/>
+      <c r="D357" s="0"/>
+      <c r="E357" s="0"/>
+      <c r="F357" s="0"/>
+      <c r="G357" s="0"/>
+      <c r="H357" s="0"/>
+      <c r="I357" s="0"/>
+      <c r="XFC357" s="0"/>
+      <c r="XFD357" s="0"/>
     </row>
     <row r="358" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K358" s="1"/>
+      <c r="A358" s="0"/>
+      <c r="B358" s="0"/>
+      <c r="C358" s="0"/>
+      <c r="D358" s="0"/>
+      <c r="E358" s="0"/>
+      <c r="F358" s="0"/>
+      <c r="G358" s="0"/>
+      <c r="H358" s="0"/>
+      <c r="I358" s="0"/>
+      <c r="XFC358" s="0"/>
+      <c r="XFD358" s="0"/>
     </row>
     <row r="359" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K359" s="1"/>
+      <c r="A359" s="0"/>
+      <c r="B359" s="0"/>
+      <c r="C359" s="0"/>
+      <c r="D359" s="0"/>
+      <c r="E359" s="0"/>
+      <c r="F359" s="0"/>
+      <c r="G359" s="0"/>
+      <c r="H359" s="0"/>
+      <c r="I359" s="0"/>
+      <c r="XFC359" s="0"/>
+      <c r="XFD359" s="0"/>
+    </row>
+    <row r="360" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A360" s="0"/>
+      <c r="B360" s="0"/>
+      <c r="C360" s="0"/>
+      <c r="D360" s="0"/>
+      <c r="E360" s="0"/>
+      <c r="F360" s="0"/>
+      <c r="G360" s="0"/>
+      <c r="H360" s="0"/>
+      <c r="I360" s="0"/>
+      <c r="XFC360" s="0"/>
+      <c r="XFD360" s="0"/>
+    </row>
+    <row r="361" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A361" s="0"/>
+      <c r="B361" s="0"/>
+      <c r="C361" s="0"/>
+      <c r="D361" s="0"/>
+      <c r="E361" s="0"/>
+      <c r="F361" s="0"/>
+      <c r="G361" s="0"/>
+      <c r="H361" s="0"/>
+      <c r="I361" s="0"/>
+      <c r="XFC361" s="0"/>
+      <c r="XFD361" s="0"/>
     </row>
     <row r="362" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J362" s="1"/>
+      <c r="A362" s="0"/>
+      <c r="B362" s="0"/>
+      <c r="C362" s="0"/>
+      <c r="D362" s="0"/>
+      <c r="E362" s="0"/>
+      <c r="F362" s="0"/>
+      <c r="G362" s="0"/>
+      <c r="H362" s="0"/>
+      <c r="I362" s="0"/>
+      <c r="XFC362" s="0"/>
+      <c r="XFD362" s="0"/>
+    </row>
+    <row r="363" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A363" s="0"/>
+      <c r="B363" s="0"/>
+      <c r="C363" s="0"/>
+      <c r="D363" s="0"/>
+      <c r="E363" s="0"/>
+      <c r="F363" s="0"/>
+      <c r="G363" s="0"/>
+      <c r="H363" s="0"/>
+      <c r="I363" s="0"/>
+      <c r="XFC363" s="0"/>
+      <c r="XFD363" s="0"/>
     </row>
     <row r="364" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J364" s="1"/>
+      <c r="A364" s="0"/>
+      <c r="B364" s="0"/>
+      <c r="C364" s="0"/>
+      <c r="D364" s="0"/>
+      <c r="E364" s="0"/>
+      <c r="F364" s="0"/>
+      <c r="G364" s="0"/>
+      <c r="H364" s="0"/>
+      <c r="I364" s="0"/>
+      <c r="XFC364" s="0"/>
+      <c r="XFD364" s="0"/>
     </row>
     <row r="365" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J365" s="1"/>
+      <c r="A365" s="0"/>
+      <c r="B365" s="0"/>
+      <c r="C365" s="0"/>
+      <c r="D365" s="0"/>
+      <c r="E365" s="0"/>
+      <c r="F365" s="0"/>
+      <c r="G365" s="0"/>
+      <c r="H365" s="0"/>
+      <c r="I365" s="0"/>
+      <c r="XFC365" s="0"/>
+      <c r="XFD365" s="0"/>
     </row>
     <row r="366" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J366" s="1"/>
+      <c r="A366" s="0"/>
+      <c r="B366" s="0"/>
+      <c r="C366" s="0"/>
+      <c r="D366" s="0"/>
+      <c r="E366" s="0"/>
+      <c r="F366" s="0"/>
+      <c r="G366" s="0"/>
+      <c r="H366" s="0"/>
+      <c r="I366" s="0"/>
+      <c r="XFC366" s="0"/>
+      <c r="XFD366" s="0"/>
     </row>
     <row r="367" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J367" s="1"/>
+      <c r="A367" s="0"/>
+      <c r="B367" s="0"/>
+      <c r="C367" s="0"/>
+      <c r="D367" s="0"/>
+      <c r="E367" s="0"/>
+      <c r="F367" s="0"/>
+      <c r="G367" s="0"/>
+      <c r="H367" s="0"/>
+      <c r="I367" s="0"/>
+      <c r="XFC367" s="0"/>
+      <c r="XFD367" s="0"/>
     </row>
     <row r="368" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J368" s="1"/>
+      <c r="A368" s="0"/>
+      <c r="B368" s="0"/>
+      <c r="C368" s="0"/>
+      <c r="D368" s="0"/>
+      <c r="E368" s="0"/>
+      <c r="F368" s="0"/>
+      <c r="G368" s="0"/>
+      <c r="H368" s="0"/>
+      <c r="I368" s="0"/>
+      <c r="XFC368" s="0"/>
+      <c r="XFD368" s="0"/>
     </row>
     <row r="369" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J369" s="1"/>
+      <c r="A369" s="0"/>
+      <c r="B369" s="0"/>
+      <c r="C369" s="0"/>
+      <c r="D369" s="0"/>
+      <c r="E369" s="0"/>
+      <c r="F369" s="0"/>
+      <c r="G369" s="0"/>
+      <c r="H369" s="0"/>
+      <c r="I369" s="0"/>
+      <c r="XFC369" s="0"/>
+      <c r="XFD369" s="0"/>
     </row>
     <row r="370" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J370" s="1"/>
+      <c r="A370" s="0"/>
+      <c r="B370" s="0"/>
+      <c r="C370" s="0"/>
+      <c r="D370" s="0"/>
+      <c r="E370" s="0"/>
+      <c r="F370" s="0"/>
+      <c r="G370" s="0"/>
+      <c r="H370" s="0"/>
+      <c r="I370" s="0"/>
+      <c r="XFC370" s="0"/>
+      <c r="XFD370" s="0"/>
     </row>
     <row r="371" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J371" s="1"/>
+      <c r="A371" s="0"/>
+      <c r="B371" s="0"/>
+      <c r="C371" s="0"/>
+      <c r="D371" s="0"/>
+      <c r="E371" s="0"/>
+      <c r="F371" s="0"/>
+      <c r="G371" s="0"/>
+      <c r="H371" s="0"/>
+      <c r="I371" s="0"/>
+      <c r="XFC371" s="0"/>
+      <c r="XFD371" s="0"/>
     </row>
     <row r="372" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J372" s="1"/>
+      <c r="A372" s="0"/>
+      <c r="B372" s="0"/>
+      <c r="C372" s="0"/>
+      <c r="D372" s="0"/>
+      <c r="E372" s="0"/>
+      <c r="F372" s="0"/>
+      <c r="G372" s="0"/>
+      <c r="H372" s="0"/>
+      <c r="I372" s="0"/>
+      <c r="XFC372" s="0"/>
+      <c r="XFD372" s="0"/>
+    </row>
+    <row r="373" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A373" s="0"/>
+      <c r="B373" s="0"/>
+      <c r="C373" s="0"/>
+      <c r="D373" s="0"/>
+      <c r="E373" s="0"/>
+      <c r="F373" s="0"/>
+      <c r="G373" s="0"/>
+      <c r="H373" s="0"/>
+      <c r="I373" s="0"/>
+      <c r="XFC373" s="0"/>
+      <c r="XFD373" s="0"/>
+    </row>
+    <row r="374" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A374" s="0"/>
+      <c r="B374" s="0"/>
+      <c r="C374" s="0"/>
+      <c r="D374" s="0"/>
+      <c r="E374" s="0"/>
+      <c r="F374" s="0"/>
+      <c r="G374" s="0"/>
+      <c r="H374" s="0"/>
+      <c r="I374" s="0"/>
+      <c r="XFC374" s="0"/>
+      <c r="XFD374" s="0"/>
     </row>
     <row r="375" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J375" s="1"/>
+      <c r="A375" s="0"/>
+      <c r="B375" s="0"/>
+      <c r="C375" s="0"/>
+      <c r="D375" s="0"/>
+      <c r="E375" s="0"/>
+      <c r="F375" s="0"/>
+      <c r="G375" s="0"/>
+      <c r="H375" s="0"/>
+      <c r="I375" s="0"/>
+      <c r="XFC375" s="0"/>
+      <c r="XFD375" s="0"/>
+    </row>
+    <row r="376" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A376" s="0"/>
+      <c r="B376" s="0"/>
+      <c r="C376" s="0"/>
+      <c r="D376" s="0"/>
+      <c r="E376" s="0"/>
+      <c r="F376" s="0"/>
+      <c r="G376" s="4"/>
+      <c r="H376" s="0"/>
+      <c r="I376" s="0"/>
+      <c r="XFC376" s="0"/>
+      <c r="XFD376" s="0"/>
     </row>
     <row r="377" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K377" s="1"/>
+      <c r="A377" s="0"/>
+      <c r="B377" s="0"/>
+      <c r="C377" s="0"/>
+      <c r="D377" s="0"/>
+      <c r="E377" s="0"/>
+      <c r="F377" s="0"/>
+      <c r="G377" s="0"/>
+      <c r="H377" s="0"/>
+      <c r="I377" s="0"/>
+      <c r="XFC377" s="0"/>
+      <c r="XFD377" s="0"/>
     </row>
     <row r="378" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K378" s="1"/>
+      <c r="A378" s="0"/>
+      <c r="B378" s="0"/>
+      <c r="C378" s="0"/>
+      <c r="D378" s="0"/>
+      <c r="E378" s="0"/>
+      <c r="F378" s="0"/>
+      <c r="G378" s="0"/>
+      <c r="H378" s="0"/>
+      <c r="I378" s="0"/>
+      <c r="XFC378" s="0"/>
+      <c r="XFD378" s="0"/>
     </row>
     <row r="379" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K379" s="1"/>
+      <c r="A379" s="0"/>
+      <c r="B379" s="0"/>
+      <c r="C379" s="0"/>
+      <c r="D379" s="0"/>
+      <c r="E379" s="0"/>
+      <c r="F379" s="0"/>
+      <c r="G379" s="0"/>
+      <c r="H379" s="0"/>
+      <c r="I379" s="0"/>
+      <c r="XFC379" s="0"/>
+      <c r="XFD379" s="0"/>
+    </row>
+    <row r="380" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A380" s="0"/>
+      <c r="B380" s="0"/>
+      <c r="C380" s="0"/>
+      <c r="D380" s="0"/>
+      <c r="E380" s="0"/>
+      <c r="F380" s="0"/>
+      <c r="G380" s="0"/>
+      <c r="H380" s="0"/>
+      <c r="I380" s="0"/>
+      <c r="XFC380" s="0"/>
+      <c r="XFD380" s="0"/>
+    </row>
+    <row r="381" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A381" s="0"/>
+      <c r="B381" s="0"/>
+      <c r="C381" s="0"/>
+      <c r="D381" s="0"/>
+      <c r="E381" s="0"/>
+      <c r="F381" s="0"/>
+      <c r="G381" s="0"/>
+      <c r="H381" s="0"/>
+      <c r="I381" s="0"/>
+      <c r="XFC381" s="0"/>
+      <c r="XFD381" s="0"/>
     </row>
     <row r="382" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K382" s="1"/>
+      <c r="A382" s="0"/>
+      <c r="B382" s="0"/>
+      <c r="C382" s="0"/>
+      <c r="D382" s="0"/>
+      <c r="E382" s="0"/>
+      <c r="F382" s="0"/>
+      <c r="G382" s="0"/>
+      <c r="H382" s="0"/>
+      <c r="I382" s="0"/>
+      <c r="XFC382" s="0"/>
+      <c r="XFD382" s="0"/>
     </row>
     <row r="383" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J383" s="1"/>
-      <c r="M383" s="1"/>
+      <c r="A383" s="0"/>
+      <c r="B383" s="0"/>
+      <c r="C383" s="0"/>
+      <c r="D383" s="0"/>
+      <c r="E383" s="0"/>
+      <c r="F383" s="0"/>
+      <c r="G383" s="0"/>
+      <c r="H383" s="0"/>
+      <c r="I383" s="0"/>
+      <c r="XFC383" s="0"/>
+      <c r="XFD383" s="0"/>
     </row>
     <row r="384" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K384" s="1"/>
+      <c r="A384" s="0"/>
+      <c r="B384" s="0"/>
+      <c r="C384" s="0"/>
+      <c r="D384" s="0"/>
+      <c r="E384" s="0"/>
+      <c r="F384" s="0"/>
+      <c r="G384" s="0"/>
+      <c r="H384" s="0"/>
+      <c r="I384" s="0"/>
+      <c r="XFC384" s="0"/>
+      <c r="XFD384" s="0"/>
+    </row>
+    <row r="385" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A385" s="0"/>
+      <c r="B385" s="0"/>
+      <c r="C385" s="0"/>
+      <c r="D385" s="0"/>
+      <c r="E385" s="0"/>
+      <c r="F385" s="0"/>
+      <c r="G385" s="0"/>
+      <c r="H385" s="0"/>
+      <c r="I385" s="0"/>
+      <c r="XFC385" s="0"/>
+      <c r="XFD385" s="0"/>
     </row>
     <row r="386" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J386" s="1"/>
+      <c r="A386" s="0"/>
+      <c r="B386" s="0"/>
+      <c r="C386" s="0"/>
+      <c r="D386" s="0"/>
+      <c r="E386" s="0"/>
+      <c r="F386" s="0"/>
+      <c r="G386" s="0"/>
+      <c r="H386" s="0"/>
+      <c r="I386" s="0"/>
+      <c r="XFC386" s="0"/>
+      <c r="XFD386" s="0"/>
+    </row>
+    <row r="387" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A387" s="0"/>
+      <c r="B387" s="0"/>
+      <c r="C387" s="0"/>
+      <c r="D387" s="0"/>
+      <c r="E387" s="0"/>
+      <c r="F387" s="0"/>
+      <c r="G387" s="0"/>
+      <c r="H387" s="0"/>
+      <c r="I387" s="0"/>
+      <c r="XFC387" s="0"/>
+      <c r="XFD387" s="0"/>
+    </row>
+    <row r="388" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A388" s="0"/>
+      <c r="B388" s="0"/>
+      <c r="C388" s="0"/>
+      <c r="D388" s="0"/>
+      <c r="E388" s="0"/>
+      <c r="F388" s="0"/>
+      <c r="G388" s="0"/>
+      <c r="H388" s="0"/>
+      <c r="I388" s="0"/>
+      <c r="XFC388" s="0"/>
+      <c r="XFD388" s="0"/>
+    </row>
+    <row r="389" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A389" s="0"/>
+      <c r="B389" s="0"/>
+      <c r="C389" s="0"/>
+      <c r="D389" s="0"/>
+      <c r="E389" s="0"/>
+      <c r="F389" s="0"/>
+      <c r="G389" s="0"/>
+      <c r="H389" s="0"/>
+      <c r="I389" s="0"/>
+      <c r="XFC389" s="0"/>
+      <c r="XFD389" s="0"/>
     </row>
     <row r="390" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K390" s="1"/>
+      <c r="A390" s="0"/>
+      <c r="B390" s="0"/>
+      <c r="C390" s="0"/>
+      <c r="D390" s="0"/>
+      <c r="E390" s="0"/>
+      <c r="F390" s="0"/>
+      <c r="G390" s="0"/>
+      <c r="H390" s="0"/>
+      <c r="I390" s="0"/>
+      <c r="XFC390" s="0"/>
+      <c r="XFD390" s="0"/>
     </row>
     <row r="391" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J391" s="1"/>
+      <c r="A391" s="0"/>
+      <c r="B391" s="0"/>
+      <c r="C391" s="0"/>
+      <c r="D391" s="0"/>
+      <c r="E391" s="0"/>
+      <c r="F391" s="0"/>
+      <c r="G391" s="0"/>
+      <c r="H391" s="0"/>
+      <c r="I391" s="0"/>
+      <c r="XFC391" s="0"/>
+      <c r="XFD391" s="0"/>
     </row>
     <row r="392" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K392" s="1"/>
+      <c r="A392" s="0"/>
+      <c r="B392" s="0"/>
+      <c r="C392" s="0"/>
+      <c r="D392" s="0"/>
+      <c r="E392" s="0"/>
+      <c r="F392" s="0"/>
+      <c r="G392" s="0"/>
+      <c r="H392" s="0"/>
+      <c r="I392" s="0"/>
+      <c r="XFC392" s="0"/>
+      <c r="XFD392" s="0"/>
+    </row>
+    <row r="393" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A393" s="0"/>
+      <c r="B393" s="0"/>
+      <c r="C393" s="0"/>
+      <c r="D393" s="0"/>
+      <c r="E393" s="0"/>
+      <c r="F393" s="0"/>
+      <c r="G393" s="0"/>
+      <c r="H393" s="0"/>
+      <c r="I393" s="0"/>
+      <c r="XFC393" s="0"/>
+      <c r="XFD393" s="0"/>
     </row>
     <row r="394" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K394" s="1"/>
+      <c r="A394" s="0"/>
+      <c r="B394" s="0"/>
+      <c r="C394" s="0"/>
+      <c r="D394" s="0"/>
+      <c r="E394" s="0"/>
+      <c r="F394" s="0"/>
+      <c r="G394" s="0"/>
+      <c r="H394" s="0"/>
+      <c r="I394" s="0"/>
+      <c r="XFC394" s="0"/>
+      <c r="XFD394" s="0"/>
     </row>
     <row r="395" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K395" s="1"/>
+      <c r="A395" s="0"/>
+      <c r="B395" s="0"/>
+      <c r="C395" s="0"/>
+      <c r="D395" s="0"/>
+      <c r="E395" s="0"/>
+      <c r="F395" s="0"/>
+      <c r="G395" s="0"/>
+      <c r="H395" s="0"/>
+      <c r="I395" s="0"/>
+      <c r="XFC395" s="0"/>
+      <c r="XFD395" s="0"/>
     </row>
     <row r="396" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K396" s="1"/>
+      <c r="A396" s="0"/>
+      <c r="B396" s="0"/>
+      <c r="C396" s="0"/>
+      <c r="D396" s="0"/>
+      <c r="E396" s="0"/>
+      <c r="F396" s="0"/>
+      <c r="G396" s="0"/>
+      <c r="H396" s="0"/>
+      <c r="I396" s="0"/>
+      <c r="XFC396" s="0"/>
+      <c r="XFD396" s="0"/>
     </row>
     <row r="397" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K397" s="1"/>
+      <c r="A397" s="0"/>
+      <c r="B397" s="0"/>
+      <c r="C397" s="0"/>
+      <c r="D397" s="0"/>
+      <c r="E397" s="0"/>
+      <c r="F397" s="0"/>
+      <c r="G397" s="0"/>
+      <c r="H397" s="0"/>
+      <c r="I397" s="0"/>
+      <c r="XFC397" s="0"/>
+      <c r="XFD397" s="0"/>
     </row>
     <row r="398" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K398" s="1"/>
+      <c r="A398" s="0"/>
+      <c r="B398" s="0"/>
+      <c r="C398" s="0"/>
+      <c r="D398" s="0"/>
+      <c r="E398" s="0"/>
+      <c r="F398" s="0"/>
+      <c r="G398" s="0"/>
+      <c r="H398" s="0"/>
+      <c r="I398" s="0"/>
+      <c r="XFC398" s="0"/>
+      <c r="XFD398" s="0"/>
     </row>
     <row r="399" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K399" s="1"/>
+      <c r="A399" s="0"/>
+      <c r="B399" s="0"/>
+      <c r="C399" s="0"/>
+      <c r="D399" s="0"/>
+      <c r="E399" s="0"/>
+      <c r="F399" s="0"/>
+      <c r="G399" s="0"/>
+      <c r="H399" s="0"/>
+      <c r="I399" s="0"/>
+      <c r="XFC399" s="0"/>
+      <c r="XFD399" s="0"/>
     </row>
     <row r="400" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K400" s="1"/>
+      <c r="A400" s="0"/>
+      <c r="B400" s="0"/>
+      <c r="C400" s="0"/>
+      <c r="D400" s="0"/>
+      <c r="E400" s="0"/>
+      <c r="F400" s="0"/>
+      <c r="G400" s="0"/>
+      <c r="H400" s="0"/>
+      <c r="I400" s="0"/>
+      <c r="XFC400" s="0"/>
+      <c r="XFD400" s="0"/>
     </row>
     <row r="401" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K401" s="1"/>
+      <c r="A401" s="0"/>
+      <c r="B401" s="0"/>
+      <c r="C401" s="0"/>
+      <c r="D401" s="0"/>
+      <c r="E401" s="0"/>
+      <c r="F401" s="0"/>
+      <c r="G401" s="0"/>
+      <c r="H401" s="0"/>
+      <c r="I401" s="0"/>
+      <c r="XFC401" s="0"/>
+      <c r="XFD401" s="0"/>
     </row>
     <row r="402" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K402" s="1"/>
+      <c r="A402" s="0"/>
+      <c r="B402" s="0"/>
+      <c r="C402" s="0"/>
+      <c r="D402" s="0"/>
+      <c r="E402" s="0"/>
+      <c r="F402" s="0"/>
+      <c r="G402" s="0"/>
+      <c r="H402" s="0"/>
+      <c r="I402" s="0"/>
+      <c r="XFC402" s="0"/>
+      <c r="XFD402" s="0"/>
+    </row>
+    <row r="403" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A403" s="0"/>
+      <c r="B403" s="0"/>
+      <c r="C403" s="0"/>
+      <c r="D403" s="0"/>
+      <c r="E403" s="0"/>
+      <c r="F403" s="0"/>
+      <c r="G403" s="0"/>
+      <c r="H403" s="0"/>
+      <c r="I403" s="0"/>
+      <c r="XFC403" s="0"/>
+      <c r="XFD403" s="0"/>
+    </row>
+    <row r="404" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A404" s="0"/>
+      <c r="B404" s="0"/>
+      <c r="C404" s="0"/>
+      <c r="D404" s="0"/>
+      <c r="E404" s="0"/>
+      <c r="F404" s="0"/>
+      <c r="G404" s="0"/>
+      <c r="H404" s="0"/>
+      <c r="I404" s="0"/>
+      <c r="XFC404" s="0"/>
+      <c r="XFD404" s="0"/>
     </row>
     <row r="405" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J405" s="1"/>
+      <c r="A405" s="0"/>
+      <c r="B405" s="0"/>
+      <c r="C405" s="0"/>
+      <c r="D405" s="0"/>
+      <c r="E405" s="0"/>
+      <c r="F405" s="0"/>
+      <c r="G405" s="0"/>
+      <c r="H405" s="0"/>
+      <c r="I405" s="0"/>
+      <c r="XFC405" s="0"/>
+      <c r="XFD405" s="0"/>
+    </row>
+    <row r="406" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A406" s="0"/>
+      <c r="B406" s="0"/>
+      <c r="C406" s="0"/>
+      <c r="D406" s="0"/>
+      <c r="E406" s="0"/>
+      <c r="F406" s="0"/>
+      <c r="G406" s="0"/>
+      <c r="H406" s="0"/>
+      <c r="I406" s="0"/>
+      <c r="XFC406" s="0"/>
+      <c r="XFD406" s="0"/>
     </row>
     <row r="407" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J407" s="1"/>
+      <c r="A407" s="0"/>
+      <c r="B407" s="0"/>
+      <c r="C407" s="0"/>
+      <c r="D407" s="0"/>
+      <c r="E407" s="0"/>
+      <c r="F407" s="0"/>
+      <c r="G407" s="0"/>
+      <c r="H407" s="0"/>
+      <c r="I407" s="0"/>
+      <c r="XFC407" s="0"/>
+      <c r="XFD407" s="0"/>
     </row>
     <row r="408" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J408" s="1"/>
+      <c r="A408" s="0"/>
+      <c r="B408" s="0"/>
+      <c r="C408" s="0"/>
+      <c r="D408" s="0"/>
+      <c r="E408" s="0"/>
+      <c r="F408" s="0"/>
+      <c r="G408" s="0"/>
+      <c r="H408" s="0"/>
+      <c r="I408" s="0"/>
+      <c r="XFC408" s="0"/>
+      <c r="XFD408" s="0"/>
     </row>
     <row r="409" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J409" s="1"/>
+      <c r="A409" s="0"/>
+      <c r="B409" s="0"/>
+      <c r="C409" s="0"/>
+      <c r="D409" s="0"/>
+      <c r="E409" s="0"/>
+      <c r="F409" s="0"/>
+      <c r="G409" s="0"/>
+      <c r="H409" s="0"/>
+      <c r="I409" s="0"/>
+      <c r="XFC409" s="0"/>
+      <c r="XFD409" s="0"/>
     </row>
     <row r="410" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J410" s="1"/>
+      <c r="A410" s="0"/>
+      <c r="B410" s="0"/>
+      <c r="C410" s="0"/>
+      <c r="D410" s="0"/>
+      <c r="E410" s="0"/>
+      <c r="F410" s="0"/>
+      <c r="G410" s="0"/>
+      <c r="H410" s="0"/>
+      <c r="I410" s="0"/>
+      <c r="XFC410" s="0"/>
+      <c r="XFD410" s="0"/>
     </row>
     <row r="411" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J411" s="1"/>
+      <c r="A411" s="0"/>
+      <c r="B411" s="0"/>
+      <c r="C411" s="0"/>
+      <c r="D411" s="0"/>
+      <c r="E411" s="0"/>
+      <c r="F411" s="0"/>
+      <c r="G411" s="0"/>
+      <c r="H411" s="0"/>
+      <c r="I411" s="0"/>
+      <c r="XFC411" s="0"/>
+      <c r="XFD411" s="0"/>
     </row>
     <row r="412" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J412" s="1"/>
+      <c r="A412" s="0"/>
+      <c r="B412" s="0"/>
+      <c r="C412" s="0"/>
+      <c r="D412" s="0"/>
+      <c r="E412" s="0"/>
+      <c r="F412" s="0"/>
+      <c r="G412" s="0"/>
+      <c r="H412" s="0"/>
+      <c r="I412" s="0"/>
+      <c r="XFC412" s="0"/>
+      <c r="XFD412" s="0"/>
     </row>
     <row r="413" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J413" s="1"/>
+      <c r="A413" s="0"/>
+      <c r="B413" s="0"/>
+      <c r="C413" s="0"/>
+      <c r="D413" s="0"/>
+      <c r="E413" s="0"/>
+      <c r="F413" s="0"/>
+      <c r="G413" s="0"/>
+      <c r="H413" s="0"/>
+      <c r="I413" s="0"/>
+      <c r="XFC413" s="0"/>
+      <c r="XFD413" s="0"/>
     </row>
     <row r="414" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J414" s="1"/>
+      <c r="A414" s="0"/>
+      <c r="B414" s="0"/>
+      <c r="C414" s="0"/>
+      <c r="D414" s="0"/>
+      <c r="E414" s="0"/>
+      <c r="F414" s="0"/>
+      <c r="G414" s="0"/>
+      <c r="H414" s="0"/>
+      <c r="I414" s="0"/>
+      <c r="XFC414" s="0"/>
+      <c r="XFD414" s="0"/>
     </row>
     <row r="415" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J415" s="1"/>
+      <c r="A415" s="0"/>
+      <c r="B415" s="0"/>
+      <c r="C415" s="0"/>
+      <c r="D415" s="0"/>
+      <c r="E415" s="0"/>
+      <c r="F415" s="0"/>
+      <c r="G415" s="0"/>
+      <c r="H415" s="0"/>
+      <c r="I415" s="0"/>
+      <c r="XFC415" s="0"/>
+      <c r="XFD415" s="0"/>
+    </row>
+    <row r="416" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A416" s="0"/>
+      <c r="B416" s="0"/>
+      <c r="C416" s="0"/>
+      <c r="D416" s="0"/>
+      <c r="E416" s="0"/>
+      <c r="F416" s="0"/>
+      <c r="G416" s="0"/>
+      <c r="H416" s="0"/>
+      <c r="I416" s="0"/>
+      <c r="XFC416" s="0"/>
+      <c r="XFD416" s="0"/>
+    </row>
+    <row r="417" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A417" s="0"/>
+      <c r="B417" s="0"/>
+      <c r="C417" s="0"/>
+      <c r="D417" s="0"/>
+      <c r="E417" s="0"/>
+      <c r="F417" s="0"/>
+      <c r="G417" s="0"/>
+      <c r="H417" s="0"/>
+      <c r="I417" s="0"/>
+      <c r="XFC417" s="0"/>
+      <c r="XFD417" s="0"/>
     </row>
     <row r="418" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J418" s="1"/>
+      <c r="A418" s="0"/>
+      <c r="B418" s="0"/>
+      <c r="C418" s="0"/>
+      <c r="D418" s="0"/>
+      <c r="E418" s="0"/>
+      <c r="F418" s="0"/>
+      <c r="G418" s="0"/>
+      <c r="H418" s="0"/>
+      <c r="I418" s="0"/>
+      <c r="XFC418" s="0"/>
+      <c r="XFD418" s="0"/>
+    </row>
+    <row r="419" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A419" s="0"/>
+      <c r="B419" s="0"/>
+      <c r="C419" s="0"/>
+      <c r="D419" s="0"/>
+      <c r="E419" s="0"/>
+      <c r="F419" s="0"/>
+      <c r="G419" s="4"/>
+      <c r="H419" s="0"/>
+      <c r="I419" s="0"/>
+      <c r="XFC419" s="0"/>
+      <c r="XFD419" s="0"/>
     </row>
     <row r="420" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K420" s="1"/>
+      <c r="A420" s="0"/>
+      <c r="B420" s="0"/>
+      <c r="C420" s="0"/>
+      <c r="D420" s="0"/>
+      <c r="E420" s="0"/>
+      <c r="F420" s="0"/>
+      <c r="G420" s="0"/>
+      <c r="H420" s="0"/>
+      <c r="I420" s="0"/>
+      <c r="XFC420" s="0"/>
+      <c r="XFD420" s="0"/>
     </row>
     <row r="421" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K421" s="1"/>
+      <c r="A421" s="0"/>
+      <c r="B421" s="0"/>
+      <c r="C421" s="0"/>
+      <c r="D421" s="0"/>
+      <c r="E421" s="0"/>
+      <c r="F421" s="0"/>
+      <c r="G421" s="0"/>
+      <c r="H421" s="0"/>
+      <c r="I421" s="0"/>
+      <c r="XFC421" s="0"/>
+      <c r="XFD421" s="0"/>
     </row>
     <row r="422" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K422" s="1"/>
+      <c r="A422" s="0"/>
+      <c r="B422" s="0"/>
+      <c r="C422" s="0"/>
+      <c r="D422" s="0"/>
+      <c r="E422" s="0"/>
+      <c r="F422" s="0"/>
+      <c r="G422" s="0"/>
+      <c r="H422" s="0"/>
+      <c r="I422" s="0"/>
+      <c r="XFC422" s="0"/>
+      <c r="XFD422" s="0"/>
+    </row>
+    <row r="423" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A423" s="0"/>
+      <c r="B423" s="0"/>
+      <c r="C423" s="0"/>
+      <c r="D423" s="0"/>
+      <c r="E423" s="0"/>
+      <c r="F423" s="0"/>
+      <c r="G423" s="0"/>
+      <c r="H423" s="0"/>
+      <c r="I423" s="0"/>
+      <c r="XFC423" s="0"/>
+      <c r="XFD423" s="0"/>
+    </row>
+    <row r="424" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A424" s="0"/>
+      <c r="B424" s="0"/>
+      <c r="C424" s="0"/>
+      <c r="D424" s="0"/>
+      <c r="E424" s="0"/>
+      <c r="F424" s="0"/>
+      <c r="G424" s="0"/>
+      <c r="H424" s="0"/>
+      <c r="I424" s="0"/>
+      <c r="XFC424" s="0"/>
+      <c r="XFD424" s="0"/>
     </row>
     <row r="425" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K425" s="1"/>
+      <c r="A425" s="0"/>
+      <c r="B425" s="0"/>
+      <c r="C425" s="0"/>
+      <c r="D425" s="0"/>
+      <c r="E425" s="0"/>
+      <c r="F425" s="0"/>
+      <c r="G425" s="0"/>
+      <c r="H425" s="0"/>
+      <c r="I425" s="0"/>
+      <c r="XFC425" s="0"/>
+      <c r="XFD425" s="0"/>
     </row>
     <row r="426" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J426" s="1"/>
-      <c r="M426" s="1"/>
+      <c r="A426" s="0"/>
+      <c r="B426" s="0"/>
+      <c r="C426" s="0"/>
+      <c r="D426" s="0"/>
+      <c r="E426" s="0"/>
+      <c r="F426" s="0"/>
+      <c r="G426" s="0"/>
+      <c r="H426" s="0"/>
+      <c r="I426" s="0"/>
+      <c r="XFC426" s="0"/>
+      <c r="XFD426" s="0"/>
     </row>
     <row r="427" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K427" s="1"/>
+      <c r="A427" s="0"/>
+      <c r="B427" s="0"/>
+      <c r="C427" s="0"/>
+      <c r="D427" s="0"/>
+      <c r="E427" s="0"/>
+      <c r="F427" s="0"/>
+      <c r="G427" s="0"/>
+      <c r="H427" s="0"/>
+      <c r="I427" s="0"/>
+      <c r="XFC427" s="0"/>
+      <c r="XFD427" s="0"/>
+    </row>
+    <row r="428" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A428" s="0"/>
+      <c r="B428" s="0"/>
+      <c r="C428" s="0"/>
+      <c r="D428" s="0"/>
+      <c r="E428" s="0"/>
+      <c r="F428" s="0"/>
+      <c r="G428" s="0"/>
+      <c r="H428" s="0"/>
+      <c r="I428" s="0"/>
+      <c r="XFC428" s="0"/>
+      <c r="XFD428" s="0"/>
     </row>
     <row r="429" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J429" s="1"/>
+      <c r="A429" s="0"/>
+      <c r="B429" s="0"/>
+      <c r="C429" s="0"/>
+      <c r="D429" s="0"/>
+      <c r="E429" s="0"/>
+      <c r="F429" s="0"/>
+      <c r="G429" s="0"/>
+      <c r="H429" s="0"/>
+      <c r="I429" s="0"/>
+      <c r="XFC429" s="0"/>
+      <c r="XFD429" s="0"/>
+    </row>
+    <row r="430" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A430" s="0"/>
+      <c r="B430" s="0"/>
+      <c r="C430" s="0"/>
+      <c r="D430" s="0"/>
+      <c r="E430" s="0"/>
+      <c r="F430" s="0"/>
+      <c r="G430" s="0"/>
+      <c r="H430" s="0"/>
+      <c r="I430" s="0"/>
+      <c r="XFC430" s="0"/>
+      <c r="XFD430" s="0"/>
+    </row>
+    <row r="431" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A431" s="0"/>
+      <c r="B431" s="0"/>
+      <c r="C431" s="0"/>
+      <c r="D431" s="0"/>
+      <c r="E431" s="0"/>
+      <c r="F431" s="0"/>
+      <c r="G431" s="0"/>
+      <c r="H431" s="0"/>
+      <c r="I431" s="0"/>
+      <c r="XFC431" s="0"/>
+      <c r="XFD431" s="0"/>
+    </row>
+    <row r="432" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A432" s="0"/>
+      <c r="B432" s="0"/>
+      <c r="C432" s="0"/>
+      <c r="D432" s="0"/>
+      <c r="E432" s="0"/>
+      <c r="F432" s="0"/>
+      <c r="G432" s="0"/>
+      <c r="H432" s="0"/>
+      <c r="I432" s="0"/>
+      <c r="XFC432" s="0"/>
+      <c r="XFD432" s="0"/>
     </row>
     <row r="433" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K433" s="1"/>
+      <c r="A433" s="0"/>
+      <c r="B433" s="0"/>
+      <c r="C433" s="0"/>
+      <c r="D433" s="0"/>
+      <c r="E433" s="0"/>
+      <c r="F433" s="0"/>
+      <c r="G433" s="0"/>
+      <c r="H433" s="0"/>
+      <c r="I433" s="0"/>
+      <c r="XFC433" s="0"/>
+      <c r="XFD433" s="0"/>
     </row>
     <row r="434" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J434" s="1"/>
+      <c r="A434" s="0"/>
+      <c r="B434" s="0"/>
+      <c r="C434" s="0"/>
+      <c r="D434" s="0"/>
+      <c r="E434" s="0"/>
+      <c r="F434" s="0"/>
+      <c r="G434" s="0"/>
+      <c r="H434" s="0"/>
+      <c r="I434" s="0"/>
+      <c r="XFC434" s="0"/>
+      <c r="XFD434" s="0"/>
     </row>
     <row r="435" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K435" s="1"/>
+      <c r="A435" s="0"/>
+      <c r="B435" s="0"/>
+      <c r="C435" s="0"/>
+      <c r="D435" s="0"/>
+      <c r="E435" s="0"/>
+      <c r="F435" s="0"/>
+      <c r="G435" s="0"/>
+      <c r="H435" s="0"/>
+      <c r="I435" s="0"/>
+      <c r="XFC435" s="0"/>
+      <c r="XFD435" s="0"/>
+    </row>
+    <row r="436" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A436" s="0"/>
+      <c r="B436" s="0"/>
+      <c r="C436" s="0"/>
+      <c r="D436" s="0"/>
+      <c r="E436" s="0"/>
+      <c r="F436" s="0"/>
+      <c r="G436" s="0"/>
+      <c r="H436" s="0"/>
+      <c r="I436" s="0"/>
+      <c r="XFC436" s="0"/>
+      <c r="XFD436" s="0"/>
     </row>
     <row r="437" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K437" s="1"/>
+      <c r="A437" s="0"/>
+      <c r="B437" s="0"/>
+      <c r="C437" s="0"/>
+      <c r="D437" s="0"/>
+      <c r="E437" s="0"/>
+      <c r="F437" s="0"/>
+      <c r="G437" s="0"/>
+      <c r="H437" s="0"/>
+      <c r="I437" s="0"/>
+      <c r="XFC437" s="0"/>
+      <c r="XFD437" s="0"/>
     </row>
     <row r="438" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K438" s="1"/>
+      <c r="A438" s="0"/>
+      <c r="B438" s="0"/>
+      <c r="C438" s="0"/>
+      <c r="D438" s="0"/>
+      <c r="E438" s="0"/>
+      <c r="F438" s="0"/>
+      <c r="G438" s="0"/>
+      <c r="H438" s="0"/>
+      <c r="I438" s="0"/>
+      <c r="XFC438" s="0"/>
+      <c r="XFD438" s="0"/>
     </row>
     <row r="439" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K439" s="1"/>
+      <c r="A439" s="0"/>
+      <c r="B439" s="0"/>
+      <c r="C439" s="0"/>
+      <c r="D439" s="0"/>
+      <c r="E439" s="0"/>
+      <c r="F439" s="0"/>
+      <c r="G439" s="0"/>
+      <c r="H439" s="0"/>
+      <c r="I439" s="0"/>
+      <c r="XFC439" s="0"/>
+      <c r="XFD439" s="0"/>
     </row>
     <row r="440" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K440" s="1"/>
+      <c r="A440" s="0"/>
+      <c r="B440" s="0"/>
+      <c r="C440" s="0"/>
+      <c r="D440" s="0"/>
+      <c r="E440" s="0"/>
+      <c r="F440" s="0"/>
+      <c r="G440" s="0"/>
+      <c r="H440" s="0"/>
+      <c r="I440" s="0"/>
+      <c r="XFC440" s="0"/>
+      <c r="XFD440" s="0"/>
     </row>
     <row r="441" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K441" s="1"/>
+      <c r="A441" s="0"/>
+      <c r="B441" s="0"/>
+      <c r="C441" s="0"/>
+      <c r="D441" s="0"/>
+      <c r="E441" s="0"/>
+      <c r="F441" s="0"/>
+      <c r="G441" s="0"/>
+      <c r="H441" s="0"/>
+      <c r="I441" s="0"/>
+      <c r="XFC441" s="0"/>
+      <c r="XFD441" s="0"/>
     </row>
     <row r="442" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K442" s="1"/>
+      <c r="A442" s="0"/>
+      <c r="B442" s="0"/>
+      <c r="C442" s="0"/>
+      <c r="D442" s="0"/>
+      <c r="E442" s="0"/>
+      <c r="F442" s="0"/>
+      <c r="G442" s="0"/>
+      <c r="H442" s="0"/>
+      <c r="I442" s="0"/>
+      <c r="XFC442" s="0"/>
+      <c r="XFD442" s="0"/>
     </row>
     <row r="443" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K443" s="1"/>
+      <c r="A443" s="0"/>
+      <c r="B443" s="0"/>
+      <c r="C443" s="0"/>
+      <c r="D443" s="0"/>
+      <c r="E443" s="0"/>
+      <c r="F443" s="0"/>
+      <c r="G443" s="0"/>
+      <c r="H443" s="0"/>
+      <c r="I443" s="0"/>
+      <c r="XFC443" s="0"/>
+      <c r="XFD443" s="0"/>
     </row>
     <row r="444" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K444" s="1"/>
+      <c r="A444" s="0"/>
+      <c r="B444" s="0"/>
+      <c r="C444" s="0"/>
+      <c r="D444" s="0"/>
+      <c r="E444" s="0"/>
+      <c r="F444" s="0"/>
+      <c r="G444" s="0"/>
+      <c r="H444" s="0"/>
+      <c r="I444" s="0"/>
+      <c r="XFC444" s="0"/>
+      <c r="XFD444" s="0"/>
     </row>
     <row r="445" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K445" s="1"/>
+      <c r="A445" s="0"/>
+      <c r="B445" s="0"/>
+      <c r="C445" s="0"/>
+      <c r="D445" s="0"/>
+      <c r="E445" s="0"/>
+      <c r="F445" s="0"/>
+      <c r="G445" s="0"/>
+      <c r="H445" s="0"/>
+      <c r="I445" s="0"/>
+      <c r="XFC445" s="0"/>
+      <c r="XFD445" s="0"/>
+    </row>
+    <row r="446" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A446" s="0"/>
+      <c r="B446" s="0"/>
+      <c r="C446" s="0"/>
+      <c r="D446" s="0"/>
+      <c r="E446" s="0"/>
+      <c r="F446" s="0"/>
+      <c r="G446" s="0"/>
+      <c r="H446" s="0"/>
+      <c r="I446" s="0"/>
+      <c r="XFC446" s="0"/>
+      <c r="XFD446" s="0"/>
+    </row>
+    <row r="447" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A447" s="0"/>
+      <c r="B447" s="0"/>
+      <c r="C447" s="0"/>
+      <c r="D447" s="0"/>
+      <c r="E447" s="0"/>
+      <c r="F447" s="0"/>
+      <c r="G447" s="0"/>
+      <c r="H447" s="0"/>
+      <c r="I447" s="0"/>
+      <c r="XFC447" s="0"/>
+      <c r="XFD447" s="0"/>
     </row>
     <row r="448" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J448" s="1"/>
+      <c r="A448" s="0"/>
+      <c r="B448" s="0"/>
+      <c r="C448" s="0"/>
+      <c r="D448" s="0"/>
+      <c r="E448" s="0"/>
+      <c r="F448" s="0"/>
+      <c r="G448" s="0"/>
+      <c r="H448" s="0"/>
+      <c r="I448" s="0"/>
+      <c r="XFC448" s="0"/>
+      <c r="XFD448" s="0"/>
+    </row>
+    <row r="449" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A449" s="0"/>
+      <c r="B449" s="0"/>
+      <c r="C449" s="0"/>
+      <c r="D449" s="0"/>
+      <c r="E449" s="0"/>
+      <c r="F449" s="0"/>
+      <c r="G449" s="0"/>
+      <c r="H449" s="0"/>
+      <c r="I449" s="0"/>
+      <c r="XFC449" s="0"/>
+      <c r="XFD449" s="0"/>
     </row>
     <row r="450" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J450" s="1"/>
+      <c r="A450" s="0"/>
+      <c r="B450" s="0"/>
+      <c r="C450" s="0"/>
+      <c r="D450" s="0"/>
+      <c r="E450" s="0"/>
+      <c r="F450" s="0"/>
+      <c r="G450" s="0"/>
+      <c r="H450" s="0"/>
+      <c r="I450" s="0"/>
+      <c r="XFC450" s="0"/>
+      <c r="XFD450" s="0"/>
     </row>
     <row r="451" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J451" s="1"/>
+      <c r="A451" s="0"/>
+      <c r="B451" s="0"/>
+      <c r="C451" s="0"/>
+      <c r="D451" s="0"/>
+      <c r="E451" s="0"/>
+      <c r="F451" s="0"/>
+      <c r="G451" s="0"/>
+      <c r="H451" s="0"/>
+      <c r="I451" s="0"/>
+      <c r="XFC451" s="0"/>
+      <c r="XFD451" s="0"/>
     </row>
     <row r="452" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J452" s="1"/>
+      <c r="A452" s="0"/>
+      <c r="B452" s="0"/>
+      <c r="C452" s="0"/>
+      <c r="D452" s="0"/>
+      <c r="E452" s="0"/>
+      <c r="F452" s="0"/>
+      <c r="G452" s="0"/>
+      <c r="H452" s="0"/>
+      <c r="I452" s="0"/>
+      <c r="XFC452" s="0"/>
+      <c r="XFD452" s="0"/>
     </row>
     <row r="453" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J453" s="1"/>
+      <c r="A453" s="0"/>
+      <c r="B453" s="0"/>
+      <c r="C453" s="0"/>
+      <c r="D453" s="0"/>
+      <c r="E453" s="0"/>
+      <c r="F453" s="0"/>
+      <c r="G453" s="0"/>
+      <c r="H453" s="0"/>
+      <c r="I453" s="0"/>
+      <c r="XFC453" s="0"/>
+      <c r="XFD453" s="0"/>
     </row>
     <row r="454" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J454" s="1"/>
+      <c r="A454" s="0"/>
+      <c r="B454" s="0"/>
+      <c r="C454" s="0"/>
+      <c r="D454" s="0"/>
+      <c r="E454" s="0"/>
+      <c r="F454" s="0"/>
+      <c r="G454" s="0"/>
+      <c r="H454" s="0"/>
+      <c r="I454" s="0"/>
+      <c r="XFC454" s="0"/>
+      <c r="XFD454" s="0"/>
     </row>
     <row r="455" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J455" s="1"/>
+      <c r="A455" s="0"/>
+      <c r="B455" s="0"/>
+      <c r="C455" s="0"/>
+      <c r="D455" s="0"/>
+      <c r="E455" s="0"/>
+      <c r="F455" s="0"/>
+      <c r="G455" s="0"/>
+      <c r="H455" s="0"/>
+      <c r="I455" s="0"/>
+      <c r="XFC455" s="0"/>
+      <c r="XFD455" s="0"/>
     </row>
     <row r="456" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J456" s="1"/>
+      <c r="A456" s="0"/>
+      <c r="B456" s="0"/>
+      <c r="C456" s="0"/>
+      <c r="D456" s="0"/>
+      <c r="E456" s="0"/>
+      <c r="F456" s="0"/>
+      <c r="G456" s="0"/>
+      <c r="H456" s="0"/>
+      <c r="I456" s="0"/>
+      <c r="XFC456" s="0"/>
+      <c r="XFD456" s="0"/>
     </row>
     <row r="457" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J457" s="1"/>
+      <c r="A457" s="0"/>
+      <c r="B457" s="0"/>
+      <c r="C457" s="0"/>
+      <c r="D457" s="0"/>
+      <c r="E457" s="0"/>
+      <c r="F457" s="0"/>
+      <c r="G457" s="0"/>
+      <c r="H457" s="0"/>
+      <c r="I457" s="0"/>
+      <c r="XFC457" s="0"/>
+      <c r="XFD457" s="0"/>
     </row>
     <row r="458" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J458" s="1"/>
+      <c r="A458" s="0"/>
+      <c r="B458" s="0"/>
+      <c r="C458" s="0"/>
+      <c r="D458" s="0"/>
+      <c r="E458" s="0"/>
+      <c r="F458" s="0"/>
+      <c r="G458" s="0"/>
+      <c r="H458" s="0"/>
+      <c r="I458" s="0"/>
+      <c r="XFC458" s="0"/>
+      <c r="XFD458" s="0"/>
+    </row>
+    <row r="459" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A459" s="0"/>
+      <c r="B459" s="0"/>
+      <c r="C459" s="0"/>
+      <c r="D459" s="0"/>
+      <c r="E459" s="0"/>
+      <c r="F459" s="0"/>
+      <c r="G459" s="0"/>
+      <c r="H459" s="0"/>
+      <c r="I459" s="0"/>
+      <c r="XFC459" s="0"/>
+      <c r="XFD459" s="0"/>
+    </row>
+    <row r="460" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A460" s="0"/>
+      <c r="B460" s="0"/>
+      <c r="C460" s="0"/>
+      <c r="D460" s="0"/>
+      <c r="E460" s="0"/>
+      <c r="F460" s="0"/>
+      <c r="G460" s="0"/>
+      <c r="H460" s="0"/>
+      <c r="I460" s="0"/>
+      <c r="XFC460" s="0"/>
+      <c r="XFD460" s="0"/>
     </row>
     <row r="461" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J461" s="1"/>
+      <c r="A461" s="0"/>
+      <c r="B461" s="0"/>
+      <c r="C461" s="0"/>
+      <c r="D461" s="0"/>
+      <c r="E461" s="0"/>
+      <c r="F461" s="0"/>
+      <c r="G461" s="0"/>
+      <c r="H461" s="0"/>
+      <c r="I461" s="0"/>
+      <c r="XFC461" s="0"/>
+      <c r="XFD461" s="0"/>
+    </row>
+    <row r="462" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A462" s="0"/>
+      <c r="B462" s="0"/>
+      <c r="C462" s="0"/>
+      <c r="D462" s="0"/>
+      <c r="E462" s="0"/>
+      <c r="F462" s="0"/>
+      <c r="G462" s="4"/>
+      <c r="H462" s="0"/>
+      <c r="I462" s="0"/>
+      <c r="XFC462" s="0"/>
+      <c r="XFD462" s="0"/>
     </row>
     <row r="463" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K463" s="1"/>
+      <c r="A463" s="0"/>
+      <c r="B463" s="0"/>
+      <c r="C463" s="0"/>
+      <c r="D463" s="0"/>
+      <c r="E463" s="0"/>
+      <c r="F463" s="0"/>
+      <c r="G463" s="0"/>
+      <c r="H463" s="0"/>
+      <c r="I463" s="0"/>
+      <c r="XFC463" s="0"/>
+      <c r="XFD463" s="0"/>
     </row>
     <row r="464" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K464" s="1"/>
+      <c r="A464" s="0"/>
+      <c r="B464" s="0"/>
+      <c r="C464" s="0"/>
+      <c r="D464" s="0"/>
+      <c r="E464" s="0"/>
+      <c r="F464" s="0"/>
+      <c r="G464" s="0"/>
+      <c r="H464" s="0"/>
+      <c r="I464" s="0"/>
+      <c r="XFC464" s="0"/>
+      <c r="XFD464" s="0"/>
     </row>
     <row r="465" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K465" s="1"/>
+      <c r="A465" s="0"/>
+      <c r="B465" s="0"/>
+      <c r="C465" s="0"/>
+      <c r="D465" s="0"/>
+      <c r="E465" s="0"/>
+      <c r="F465" s="0"/>
+      <c r="G465" s="0"/>
+      <c r="H465" s="0"/>
+      <c r="I465" s="0"/>
+      <c r="XFC465" s="0"/>
+      <c r="XFD465" s="0"/>
+    </row>
+    <row r="466" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A466" s="0"/>
+      <c r="B466" s="0"/>
+      <c r="C466" s="0"/>
+      <c r="D466" s="0"/>
+      <c r="E466" s="0"/>
+      <c r="F466" s="0"/>
+      <c r="G466" s="0"/>
+      <c r="H466" s="0"/>
+      <c r="I466" s="0"/>
+      <c r="XFC466" s="0"/>
+      <c r="XFD466" s="0"/>
+    </row>
+    <row r="467" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A467" s="0"/>
+      <c r="B467" s="0"/>
+      <c r="C467" s="0"/>
+      <c r="D467" s="0"/>
+      <c r="E467" s="0"/>
+      <c r="F467" s="0"/>
+      <c r="G467" s="0"/>
+      <c r="H467" s="0"/>
+      <c r="I467" s="0"/>
+      <c r="XFC467" s="0"/>
+      <c r="XFD467" s="0"/>
     </row>
     <row r="468" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K468" s="1"/>
+      <c r="A468" s="0"/>
+      <c r="B468" s="0"/>
+      <c r="C468" s="0"/>
+      <c r="D468" s="0"/>
+      <c r="E468" s="0"/>
+      <c r="F468" s="0"/>
+      <c r="G468" s="0"/>
+      <c r="H468" s="0"/>
+      <c r="I468" s="0"/>
+      <c r="XFC468" s="0"/>
+      <c r="XFD468" s="0"/>
     </row>
     <row r="469" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J469" s="1"/>
-      <c r="M469" s="1"/>
+      <c r="A469" s="0"/>
+      <c r="B469" s="0"/>
+      <c r="C469" s="0"/>
+      <c r="D469" s="0"/>
+      <c r="E469" s="0"/>
+      <c r="F469" s="0"/>
+      <c r="G469" s="0"/>
+      <c r="H469" s="0"/>
+      <c r="I469" s="0"/>
+      <c r="XFC469" s="0"/>
+      <c r="XFD469" s="0"/>
     </row>
     <row r="470" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K470" s="1"/>
+      <c r="A470" s="0"/>
+      <c r="B470" s="0"/>
+      <c r="C470" s="0"/>
+      <c r="D470" s="0"/>
+      <c r="E470" s="0"/>
+      <c r="F470" s="0"/>
+      <c r="G470" s="0"/>
+      <c r="H470" s="0"/>
+      <c r="I470" s="0"/>
+      <c r="XFC470" s="0"/>
+      <c r="XFD470" s="0"/>
+    </row>
+    <row r="471" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A471" s="0"/>
+      <c r="B471" s="0"/>
+      <c r="C471" s="0"/>
+      <c r="D471" s="0"/>
+      <c r="E471" s="0"/>
+      <c r="F471" s="0"/>
+      <c r="G471" s="0"/>
+      <c r="H471" s="0"/>
+      <c r="I471" s="0"/>
+      <c r="XFC471" s="0"/>
+      <c r="XFD471" s="0"/>
     </row>
     <row r="472" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J472" s="1"/>
+      <c r="A472" s="0"/>
+      <c r="B472" s="0"/>
+      <c r="C472" s="0"/>
+      <c r="D472" s="0"/>
+      <c r="E472" s="0"/>
+      <c r="F472" s="0"/>
+      <c r="G472" s="0"/>
+      <c r="H472" s="0"/>
+      <c r="I472" s="0"/>
+      <c r="XFC472" s="0"/>
+      <c r="XFD472" s="0"/>
+    </row>
+    <row r="473" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A473" s="0"/>
+      <c r="B473" s="0"/>
+      <c r="C473" s="0"/>
+      <c r="D473" s="0"/>
+      <c r="E473" s="0"/>
+      <c r="F473" s="0"/>
+      <c r="G473" s="0"/>
+      <c r="H473" s="0"/>
+      <c r="I473" s="0"/>
+      <c r="XFC473" s="0"/>
+      <c r="XFD473" s="0"/>
+    </row>
+    <row r="474" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A474" s="0"/>
+      <c r="B474" s="0"/>
+      <c r="C474" s="0"/>
+      <c r="D474" s="0"/>
+      <c r="E474" s="0"/>
+      <c r="F474" s="0"/>
+      <c r="G474" s="0"/>
+      <c r="H474" s="0"/>
+      <c r="I474" s="0"/>
+      <c r="XFC474" s="0"/>
+      <c r="XFD474" s="0"/>
+    </row>
+    <row r="475" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A475" s="0"/>
+      <c r="B475" s="0"/>
+      <c r="C475" s="0"/>
+      <c r="D475" s="0"/>
+      <c r="E475" s="0"/>
+      <c r="F475" s="0"/>
+      <c r="G475" s="0"/>
+      <c r="H475" s="0"/>
+      <c r="I475" s="0"/>
+      <c r="XFC475" s="0"/>
+      <c r="XFD475" s="0"/>
     </row>
     <row r="476" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K476" s="1"/>
+      <c r="A476" s="0"/>
+      <c r="B476" s="0"/>
+      <c r="C476" s="0"/>
+      <c r="D476" s="0"/>
+      <c r="E476" s="0"/>
+      <c r="F476" s="0"/>
+      <c r="G476" s="0"/>
+      <c r="H476" s="0"/>
+      <c r="I476" s="0"/>
+      <c r="XFC476" s="0"/>
+      <c r="XFD476" s="0"/>
     </row>
     <row r="477" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J477" s="1"/>
+      <c r="A477" s="0"/>
+      <c r="B477" s="0"/>
+      <c r="C477" s="0"/>
+      <c r="D477" s="0"/>
+      <c r="E477" s="0"/>
+      <c r="F477" s="0"/>
+      <c r="G477" s="0"/>
+      <c r="H477" s="0"/>
+      <c r="I477" s="0"/>
+      <c r="XFC477" s="0"/>
+      <c r="XFD477" s="0"/>
     </row>
     <row r="478" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K478" s="1"/>
+      <c r="A478" s="0"/>
+      <c r="B478" s="0"/>
+      <c r="C478" s="0"/>
+      <c r="D478" s="0"/>
+      <c r="E478" s="0"/>
+      <c r="F478" s="0"/>
+      <c r="G478" s="0"/>
+      <c r="H478" s="0"/>
+      <c r="I478" s="0"/>
+      <c r="XFC478" s="0"/>
+      <c r="XFD478" s="0"/>
+    </row>
+    <row r="479" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A479" s="0"/>
+      <c r="B479" s="0"/>
+      <c r="C479" s="0"/>
+      <c r="D479" s="0"/>
+      <c r="E479" s="0"/>
+      <c r="F479" s="0"/>
+      <c r="G479" s="0"/>
+      <c r="H479" s="0"/>
+      <c r="I479" s="0"/>
+      <c r="XFC479" s="0"/>
+      <c r="XFD479" s="0"/>
     </row>
     <row r="480" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K480" s="1"/>
+      <c r="A480" s="0"/>
+      <c r="B480" s="0"/>
+      <c r="C480" s="0"/>
+      <c r="D480" s="0"/>
+      <c r="E480" s="0"/>
+      <c r="F480" s="0"/>
+      <c r="G480" s="0"/>
+      <c r="H480" s="0"/>
+      <c r="I480" s="0"/>
+      <c r="XFC480" s="0"/>
+      <c r="XFD480" s="0"/>
     </row>
     <row r="481" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K481" s="1"/>
+      <c r="A481" s="0"/>
+      <c r="B481" s="0"/>
+      <c r="C481" s="0"/>
+      <c r="D481" s="0"/>
+      <c r="E481" s="0"/>
+      <c r="F481" s="0"/>
+      <c r="G481" s="0"/>
+      <c r="H481" s="0"/>
+      <c r="I481" s="0"/>
+      <c r="XFC481" s="0"/>
+      <c r="XFD481" s="0"/>
     </row>
     <row r="482" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K482" s="1"/>
+      <c r="A482" s="0"/>
+      <c r="B482" s="0"/>
+      <c r="C482" s="0"/>
+      <c r="D482" s="0"/>
+      <c r="E482" s="0"/>
+      <c r="F482" s="0"/>
+      <c r="G482" s="0"/>
+      <c r="H482" s="0"/>
+      <c r="I482" s="0"/>
+      <c r="XFC482" s="0"/>
+      <c r="XFD482" s="0"/>
     </row>
     <row r="483" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K483" s="1"/>
+      <c r="A483" s="0"/>
+      <c r="B483" s="0"/>
+      <c r="C483" s="0"/>
+      <c r="D483" s="0"/>
+      <c r="E483" s="0"/>
+      <c r="F483" s="0"/>
+      <c r="G483" s="0"/>
+      <c r="H483" s="0"/>
+      <c r="I483" s="0"/>
+      <c r="XFC483" s="0"/>
+      <c r="XFD483" s="0"/>
     </row>
     <row r="484" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K484" s="1"/>
+      <c r="A484" s="0"/>
+      <c r="B484" s="0"/>
+      <c r="C484" s="0"/>
+      <c r="D484" s="0"/>
+      <c r="E484" s="0"/>
+      <c r="F484" s="0"/>
+      <c r="G484" s="0"/>
+      <c r="H484" s="0"/>
+      <c r="I484" s="0"/>
+      <c r="XFC484" s="0"/>
+      <c r="XFD484" s="0"/>
     </row>
     <row r="485" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K485" s="1"/>
+      <c r="A485" s="0"/>
+      <c r="B485" s="0"/>
+      <c r="C485" s="0"/>
+      <c r="D485" s="0"/>
+      <c r="E485" s="0"/>
+      <c r="F485" s="0"/>
+      <c r="G485" s="0"/>
+      <c r="H485" s="0"/>
+      <c r="I485" s="0"/>
+      <c r="XFC485" s="0"/>
+      <c r="XFD485" s="0"/>
     </row>
     <row r="486" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K486" s="1"/>
+      <c r="A486" s="0"/>
+      <c r="B486" s="0"/>
+      <c r="C486" s="0"/>
+      <c r="D486" s="0"/>
+      <c r="E486" s="0"/>
+      <c r="F486" s="0"/>
+      <c r="G486" s="0"/>
+      <c r="H486" s="0"/>
+      <c r="I486" s="0"/>
+      <c r="XFC486" s="0"/>
+      <c r="XFD486" s="0"/>
     </row>
     <row r="487" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K487" s="1"/>
+      <c r="A487" s="0"/>
+      <c r="B487" s="0"/>
+      <c r="C487" s="0"/>
+      <c r="D487" s="0"/>
+      <c r="E487" s="0"/>
+      <c r="F487" s="0"/>
+      <c r="G487" s="0"/>
+      <c r="H487" s="0"/>
+      <c r="I487" s="0"/>
+      <c r="XFC487" s="0"/>
+      <c r="XFD487" s="0"/>
     </row>
     <row r="488" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K488" s="1"/>
+      <c r="A488" s="0"/>
+      <c r="B488" s="0"/>
+      <c r="C488" s="0"/>
+      <c r="D488" s="0"/>
+      <c r="E488" s="0"/>
+      <c r="F488" s="0"/>
+      <c r="G488" s="0"/>
+      <c r="H488" s="0"/>
+      <c r="I488" s="0"/>
+      <c r="XFC488" s="0"/>
+      <c r="XFD488" s="0"/>
+    </row>
+    <row r="489" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A489" s="0"/>
+      <c r="B489" s="0"/>
+      <c r="C489" s="0"/>
+      <c r="D489" s="0"/>
+      <c r="E489" s="0"/>
+      <c r="F489" s="0"/>
+      <c r="G489" s="0"/>
+      <c r="H489" s="0"/>
+      <c r="I489" s="0"/>
+      <c r="XFC489" s="0"/>
+      <c r="XFD489" s="0"/>
+    </row>
+    <row r="490" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A490" s="0"/>
+      <c r="B490" s="0"/>
+      <c r="C490" s="0"/>
+      <c r="D490" s="0"/>
+      <c r="E490" s="0"/>
+      <c r="F490" s="0"/>
+      <c r="G490" s="0"/>
+      <c r="H490" s="0"/>
+      <c r="I490" s="0"/>
+      <c r="XFC490" s="0"/>
+      <c r="XFD490" s="0"/>
     </row>
     <row r="491" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J491" s="1"/>
+      <c r="A491" s="0"/>
+      <c r="B491" s="0"/>
+      <c r="C491" s="0"/>
+      <c r="D491" s="0"/>
+      <c r="E491" s="0"/>
+      <c r="F491" s="0"/>
+      <c r="G491" s="0"/>
+      <c r="H491" s="0"/>
+      <c r="I491" s="0"/>
+      <c r="XFC491" s="0"/>
+      <c r="XFD491" s="0"/>
+    </row>
+    <row r="492" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A492" s="0"/>
+      <c r="B492" s="0"/>
+      <c r="C492" s="0"/>
+      <c r="D492" s="0"/>
+      <c r="E492" s="0"/>
+      <c r="F492" s="0"/>
+      <c r="G492" s="0"/>
+      <c r="H492" s="0"/>
+      <c r="I492" s="0"/>
+      <c r="XFC492" s="0"/>
+      <c r="XFD492" s="0"/>
     </row>
     <row r="493" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J493" s="1"/>
+      <c r="A493" s="0"/>
+      <c r="B493" s="0"/>
+      <c r="C493" s="0"/>
+      <c r="D493" s="0"/>
+      <c r="E493" s="0"/>
+      <c r="F493" s="0"/>
+      <c r="G493" s="0"/>
+      <c r="H493" s="0"/>
+      <c r="I493" s="0"/>
+      <c r="XFC493" s="0"/>
+      <c r="XFD493" s="0"/>
     </row>
     <row r="494" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J494" s="1"/>
+      <c r="A494" s="0"/>
+      <c r="B494" s="0"/>
+      <c r="C494" s="0"/>
+      <c r="D494" s="0"/>
+      <c r="E494" s="0"/>
+      <c r="F494" s="0"/>
+      <c r="G494" s="0"/>
+      <c r="H494" s="0"/>
+      <c r="I494" s="0"/>
+      <c r="XFC494" s="0"/>
+      <c r="XFD494" s="0"/>
     </row>
     <row r="495" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J495" s="1"/>
+      <c r="A495" s="0"/>
+      <c r="B495" s="0"/>
+      <c r="C495" s="0"/>
+      <c r="D495" s="0"/>
+      <c r="E495" s="0"/>
+      <c r="F495" s="0"/>
+      <c r="G495" s="0"/>
+      <c r="H495" s="0"/>
+      <c r="I495" s="0"/>
+      <c r="XFC495" s="0"/>
+      <c r="XFD495" s="0"/>
     </row>
     <row r="496" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J496" s="1"/>
+      <c r="A496" s="0"/>
+      <c r="B496" s="0"/>
+      <c r="C496" s="0"/>
+      <c r="D496" s="0"/>
+      <c r="E496" s="0"/>
+      <c r="F496" s="0"/>
+      <c r="G496" s="0"/>
+      <c r="H496" s="0"/>
+      <c r="I496" s="0"/>
+      <c r="XFC496" s="0"/>
+      <c r="XFD496" s="0"/>
     </row>
     <row r="497" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J497" s="1"/>
+      <c r="A497" s="0"/>
+      <c r="B497" s="0"/>
+      <c r="C497" s="0"/>
+      <c r="D497" s="0"/>
+      <c r="E497" s="0"/>
+      <c r="F497" s="0"/>
+      <c r="G497" s="0"/>
+      <c r="H497" s="0"/>
+      <c r="I497" s="0"/>
+      <c r="XFC497" s="0"/>
+      <c r="XFD497" s="0"/>
     </row>
     <row r="498" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J498" s="1"/>
+      <c r="A498" s="0"/>
+      <c r="B498" s="0"/>
+      <c r="C498" s="0"/>
+      <c r="D498" s="0"/>
+      <c r="E498" s="0"/>
+      <c r="F498" s="0"/>
+      <c r="G498" s="0"/>
+      <c r="H498" s="0"/>
+      <c r="I498" s="0"/>
+      <c r="XFC498" s="0"/>
+      <c r="XFD498" s="0"/>
     </row>
     <row r="499" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J499" s="1"/>
+      <c r="A499" s="0"/>
+      <c r="B499" s="0"/>
+      <c r="C499" s="0"/>
+      <c r="D499" s="0"/>
+      <c r="E499" s="0"/>
+      <c r="F499" s="0"/>
+      <c r="G499" s="0"/>
+      <c r="H499" s="0"/>
+      <c r="I499" s="0"/>
+      <c r="XFC499" s="0"/>
+      <c r="XFD499" s="0"/>
     </row>
     <row r="500" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J500" s="1"/>
+      <c r="A500" s="0"/>
+      <c r="B500" s="0"/>
+      <c r="C500" s="0"/>
+      <c r="D500" s="0"/>
+      <c r="E500" s="0"/>
+      <c r="F500" s="0"/>
+      <c r="G500" s="0"/>
+      <c r="H500" s="0"/>
+      <c r="I500" s="0"/>
+      <c r="XFC500" s="0"/>
+      <c r="XFD500" s="0"/>
     </row>
     <row r="501" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J501" s="1"/>
+      <c r="A501" s="0"/>
+      <c r="B501" s="0"/>
+      <c r="C501" s="0"/>
+      <c r="D501" s="0"/>
+      <c r="E501" s="0"/>
+      <c r="F501" s="0"/>
+      <c r="G501" s="0"/>
+      <c r="H501" s="0"/>
+      <c r="I501" s="0"/>
+      <c r="XFC501" s="0"/>
+      <c r="XFD501" s="0"/>
+    </row>
+    <row r="502" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A502" s="0"/>
+      <c r="B502" s="0"/>
+      <c r="C502" s="0"/>
+      <c r="D502" s="0"/>
+      <c r="E502" s="0"/>
+      <c r="F502" s="0"/>
+      <c r="G502" s="0"/>
+      <c r="H502" s="0"/>
+      <c r="I502" s="0"/>
+      <c r="XFC502" s="0"/>
+      <c r="XFD502" s="0"/>
+    </row>
+    <row r="503" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A503" s="0"/>
+      <c r="B503" s="0"/>
+      <c r="C503" s="0"/>
+      <c r="D503" s="0"/>
+      <c r="E503" s="0"/>
+      <c r="F503" s="0"/>
+      <c r="G503" s="0"/>
+      <c r="H503" s="0"/>
+      <c r="I503" s="0"/>
+      <c r="XFC503" s="0"/>
+      <c r="XFD503" s="0"/>
     </row>
     <row r="504" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J504" s="1"/>
+      <c r="A504" s="0"/>
+      <c r="B504" s="0"/>
+      <c r="C504" s="0"/>
+      <c r="D504" s="0"/>
+      <c r="E504" s="0"/>
+      <c r="F504" s="0"/>
+      <c r="G504" s="0"/>
+      <c r="H504" s="0"/>
+      <c r="I504" s="0"/>
+      <c r="XFC504" s="0"/>
+      <c r="XFD504" s="0"/>
+    </row>
+    <row r="505" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A505" s="0"/>
+      <c r="B505" s="0"/>
+      <c r="C505" s="0"/>
+      <c r="D505" s="0"/>
+      <c r="E505" s="0"/>
+      <c r="F505" s="0"/>
+      <c r="G505" s="4"/>
+      <c r="H505" s="0"/>
+      <c r="I505" s="0"/>
+      <c r="XFC505" s="0"/>
+      <c r="XFD505" s="0"/>
     </row>
     <row r="506" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K506" s="1"/>
+      <c r="A506" s="0"/>
+      <c r="B506" s="0"/>
+      <c r="C506" s="0"/>
+      <c r="D506" s="0"/>
+      <c r="E506" s="0"/>
+      <c r="F506" s="0"/>
+      <c r="G506" s="0"/>
+      <c r="H506" s="0"/>
+      <c r="I506" s="0"/>
+      <c r="XFC506" s="0"/>
+      <c r="XFD506" s="0"/>
     </row>
     <row r="507" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K507" s="1"/>
+      <c r="A507" s="0"/>
+      <c r="B507" s="0"/>
+      <c r="C507" s="0"/>
+      <c r="D507" s="0"/>
+      <c r="E507" s="0"/>
+      <c r="F507" s="0"/>
+      <c r="G507" s="0"/>
+      <c r="H507" s="0"/>
+      <c r="I507" s="0"/>
+      <c r="XFC507" s="0"/>
+      <c r="XFD507" s="0"/>
     </row>
     <row r="508" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K508" s="1"/>
+      <c r="A508" s="0"/>
+      <c r="B508" s="0"/>
+      <c r="C508" s="0"/>
+      <c r="D508" s="0"/>
+      <c r="E508" s="0"/>
+      <c r="F508" s="0"/>
+      <c r="G508" s="0"/>
+      <c r="H508" s="0"/>
+      <c r="I508" s="0"/>
+      <c r="XFC508" s="0"/>
+      <c r="XFD508" s="0"/>
+    </row>
+    <row r="509" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A509" s="0"/>
+      <c r="B509" s="0"/>
+      <c r="C509" s="0"/>
+      <c r="D509" s="0"/>
+      <c r="E509" s="0"/>
+      <c r="F509" s="0"/>
+      <c r="G509" s="0"/>
+      <c r="H509" s="0"/>
+      <c r="I509" s="0"/>
+      <c r="XFC509" s="0"/>
+      <c r="XFD509" s="0"/>
+    </row>
+    <row r="510" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A510" s="0"/>
+      <c r="B510" s="0"/>
+      <c r="C510" s="0"/>
+      <c r="D510" s="0"/>
+      <c r="E510" s="0"/>
+      <c r="F510" s="0"/>
+      <c r="G510" s="0"/>
+      <c r="H510" s="0"/>
+      <c r="I510" s="0"/>
+      <c r="XFC510" s="0"/>
+      <c r="XFD510" s="0"/>
     </row>
     <row r="511" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K511" s="1"/>
+      <c r="A511" s="0"/>
+      <c r="B511" s="0"/>
+      <c r="C511" s="0"/>
+      <c r="D511" s="0"/>
+      <c r="E511" s="0"/>
+      <c r="F511" s="0"/>
+      <c r="G511" s="0"/>
+      <c r="H511" s="0"/>
+      <c r="I511" s="0"/>
+      <c r="XFC511" s="0"/>
+      <c r="XFD511" s="0"/>
     </row>
     <row r="512" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J512" s="1"/>
-      <c r="M512" s="1"/>
+      <c r="A512" s="0"/>
+      <c r="B512" s="0"/>
+      <c r="C512" s="0"/>
+      <c r="D512" s="0"/>
+      <c r="E512" s="0"/>
+      <c r="F512" s="0"/>
+      <c r="G512" s="0"/>
+      <c r="H512" s="0"/>
+      <c r="I512" s="0"/>
+      <c r="XFC512" s="0"/>
+      <c r="XFD512" s="0"/>
     </row>
     <row r="513" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K513" s="1"/>
+      <c r="A513" s="0"/>
+      <c r="B513" s="0"/>
+      <c r="C513" s="0"/>
+      <c r="D513" s="0"/>
+      <c r="E513" s="0"/>
+      <c r="F513" s="0"/>
+      <c r="G513" s="0"/>
+      <c r="H513" s="0"/>
+      <c r="I513" s="0"/>
+      <c r="XFC513" s="0"/>
+      <c r="XFD513" s="0"/>
+    </row>
+    <row r="514" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A514" s="0"/>
+      <c r="B514" s="0"/>
+      <c r="C514" s="0"/>
+      <c r="D514" s="0"/>
+      <c r="E514" s="0"/>
+      <c r="F514" s="0"/>
+      <c r="G514" s="0"/>
+      <c r="H514" s="0"/>
+      <c r="I514" s="0"/>
+      <c r="XFC514" s="0"/>
+      <c r="XFD514" s="0"/>
     </row>
     <row r="515" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J515" s="1"/>
+      <c r="A515" s="0"/>
+      <c r="B515" s="0"/>
+      <c r="C515" s="0"/>
+      <c r="D515" s="0"/>
+      <c r="E515" s="0"/>
+      <c r="F515" s="0"/>
+      <c r="G515" s="0"/>
+      <c r="H515" s="0"/>
+      <c r="I515" s="0"/>
+      <c r="XFC515" s="0"/>
+      <c r="XFD515" s="0"/>
+    </row>
+    <row r="516" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A516" s="0"/>
+      <c r="B516" s="0"/>
+      <c r="C516" s="0"/>
+      <c r="D516" s="0"/>
+      <c r="E516" s="0"/>
+      <c r="F516" s="0"/>
+      <c r="G516" s="0"/>
+      <c r="H516" s="0"/>
+      <c r="I516" s="0"/>
+      <c r="XFC516" s="0"/>
+      <c r="XFD516" s="0"/>
+    </row>
+    <row r="517" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A517" s="0"/>
+      <c r="B517" s="0"/>
+      <c r="C517" s="0"/>
+      <c r="D517" s="0"/>
+      <c r="E517" s="0"/>
+      <c r="F517" s="0"/>
+      <c r="G517" s="0"/>
+      <c r="H517" s="0"/>
+      <c r="I517" s="0"/>
+      <c r="XFC517" s="0"/>
+      <c r="XFD517" s="0"/>
+    </row>
+    <row r="518" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A518" s="0"/>
+      <c r="B518" s="0"/>
+      <c r="C518" s="0"/>
+      <c r="D518" s="0"/>
+      <c r="E518" s="0"/>
+      <c r="F518" s="0"/>
+      <c r="G518" s="0"/>
+      <c r="H518" s="0"/>
+      <c r="I518" s="0"/>
+      <c r="XFC518" s="0"/>
+      <c r="XFD518" s="0"/>
     </row>
     <row r="519" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K519" s="1"/>
+      <c r="A519" s="0"/>
+      <c r="B519" s="0"/>
+      <c r="C519" s="0"/>
+      <c r="D519" s="0"/>
+      <c r="E519" s="0"/>
+      <c r="F519" s="0"/>
+      <c r="G519" s="0"/>
+      <c r="H519" s="0"/>
+      <c r="I519" s="0"/>
+      <c r="XFC519" s="0"/>
+      <c r="XFD519" s="0"/>
     </row>
     <row r="520" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J520" s="1"/>
+      <c r="A520" s="0"/>
+      <c r="B520" s="0"/>
+      <c r="C520" s="0"/>
+      <c r="D520" s="0"/>
+      <c r="E520" s="0"/>
+      <c r="F520" s="0"/>
+      <c r="G520" s="0"/>
+      <c r="H520" s="0"/>
+      <c r="I520" s="0"/>
+      <c r="XFC520" s="0"/>
+      <c r="XFD520" s="0"/>
     </row>
     <row r="521" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K521" s="1"/>
+      <c r="A521" s="0"/>
+      <c r="B521" s="0"/>
+      <c r="C521" s="0"/>
+      <c r="D521" s="0"/>
+      <c r="E521" s="0"/>
+      <c r="F521" s="0"/>
+      <c r="G521" s="0"/>
+      <c r="H521" s="0"/>
+      <c r="I521" s="0"/>
+      <c r="XFC521" s="0"/>
+      <c r="XFD521" s="0"/>
+    </row>
+    <row r="522" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A522" s="0"/>
+      <c r="B522" s="0"/>
+      <c r="C522" s="0"/>
+      <c r="D522" s="0"/>
+      <c r="E522" s="0"/>
+      <c r="F522" s="0"/>
+      <c r="G522" s="0"/>
+      <c r="H522" s="0"/>
+      <c r="I522" s="0"/>
+      <c r="XFC522" s="0"/>
+      <c r="XFD522" s="0"/>
     </row>
     <row r="523" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K523" s="1"/>
+      <c r="A523" s="0"/>
+      <c r="B523" s="0"/>
+      <c r="C523" s="0"/>
+      <c r="D523" s="0"/>
+      <c r="E523" s="0"/>
+      <c r="F523" s="0"/>
+      <c r="G523" s="0"/>
+      <c r="H523" s="0"/>
+      <c r="I523" s="0"/>
+      <c r="XFC523" s="0"/>
+      <c r="XFD523" s="0"/>
     </row>
     <row r="524" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K524" s="1"/>
+      <c r="A524" s="0"/>
+      <c r="B524" s="0"/>
+      <c r="C524" s="0"/>
+      <c r="D524" s="0"/>
+      <c r="E524" s="0"/>
+      <c r="F524" s="0"/>
+      <c r="G524" s="0"/>
+      <c r="H524" s="0"/>
+      <c r="I524" s="0"/>
+      <c r="XFC524" s="0"/>
+      <c r="XFD524" s="0"/>
     </row>
     <row r="525" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K525" s="1"/>
+      <c r="A525" s="0"/>
+      <c r="B525" s="0"/>
+      <c r="C525" s="0"/>
+      <c r="D525" s="0"/>
+      <c r="E525" s="0"/>
+      <c r="F525" s="0"/>
+      <c r="G525" s="0"/>
+      <c r="H525" s="0"/>
+      <c r="I525" s="0"/>
+      <c r="XFC525" s="0"/>
+      <c r="XFD525" s="0"/>
     </row>
     <row r="526" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K526" s="1"/>
+      <c r="A526" s="0"/>
+      <c r="B526" s="0"/>
+      <c r="C526" s="0"/>
+      <c r="D526" s="0"/>
+      <c r="E526" s="0"/>
+      <c r="F526" s="0"/>
+      <c r="G526" s="0"/>
+      <c r="H526" s="0"/>
+      <c r="I526" s="0"/>
+      <c r="XFC526" s="0"/>
+      <c r="XFD526" s="0"/>
     </row>
     <row r="527" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K527" s="1"/>
+      <c r="A527" s="0"/>
+      <c r="B527" s="0"/>
+      <c r="C527" s="0"/>
+      <c r="D527" s="0"/>
+      <c r="E527" s="0"/>
+      <c r="F527" s="0"/>
+      <c r="G527" s="0"/>
+      <c r="H527" s="0"/>
+      <c r="I527" s="0"/>
+      <c r="XFC527" s="0"/>
+      <c r="XFD527" s="0"/>
     </row>
     <row r="528" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K528" s="1"/>
+      <c r="A528" s="0"/>
+      <c r="B528" s="0"/>
+      <c r="C528" s="0"/>
+      <c r="D528" s="0"/>
+      <c r="E528" s="0"/>
+      <c r="F528" s="0"/>
+      <c r="G528" s="0"/>
+      <c r="H528" s="0"/>
+      <c r="I528" s="0"/>
+      <c r="XFC528" s="0"/>
+      <c r="XFD528" s="0"/>
     </row>
     <row r="529" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K529" s="1"/>
+      <c r="A529" s="0"/>
+      <c r="B529" s="0"/>
+      <c r="C529" s="0"/>
+      <c r="D529" s="0"/>
+      <c r="E529" s="0"/>
+      <c r="F529" s="0"/>
+      <c r="G529" s="0"/>
+      <c r="H529" s="0"/>
+      <c r="I529" s="0"/>
+      <c r="XFC529" s="0"/>
+      <c r="XFD529" s="0"/>
     </row>
     <row r="530" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K530" s="1"/>
+      <c r="A530" s="0"/>
+      <c r="B530" s="0"/>
+      <c r="C530" s="0"/>
+      <c r="D530" s="0"/>
+      <c r="E530" s="0"/>
+      <c r="F530" s="0"/>
+      <c r="G530" s="0"/>
+      <c r="H530" s="0"/>
+      <c r="I530" s="0"/>
+      <c r="XFC530" s="0"/>
+      <c r="XFD530" s="0"/>
     </row>
     <row r="531" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K531" s="1"/>
+      <c r="A531" s="0"/>
+      <c r="B531" s="0"/>
+      <c r="C531" s="0"/>
+      <c r="D531" s="0"/>
+      <c r="E531" s="0"/>
+      <c r="F531" s="0"/>
+      <c r="G531" s="0"/>
+      <c r="H531" s="0"/>
+      <c r="I531" s="0"/>
+      <c r="XFC531" s="0"/>
+      <c r="XFD531" s="0"/>
+    </row>
+    <row r="532" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A532" s="0"/>
+      <c r="B532" s="0"/>
+      <c r="C532" s="0"/>
+      <c r="D532" s="0"/>
+      <c r="E532" s="0"/>
+      <c r="F532" s="0"/>
+      <c r="G532" s="0"/>
+      <c r="H532" s="0"/>
+      <c r="I532" s="0"/>
+      <c r="XFC532" s="0"/>
+      <c r="XFD532" s="0"/>
+    </row>
+    <row r="533" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A533" s="0"/>
+      <c r="B533" s="0"/>
+      <c r="C533" s="0"/>
+      <c r="D533" s="0"/>
+      <c r="E533" s="0"/>
+      <c r="F533" s="0"/>
+      <c r="G533" s="0"/>
+      <c r="H533" s="0"/>
+      <c r="I533" s="0"/>
+      <c r="XFC533" s="0"/>
+      <c r="XFD533" s="0"/>
     </row>
     <row r="534" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J534" s="1"/>
+      <c r="A534" s="0"/>
+      <c r="B534" s="0"/>
+      <c r="C534" s="0"/>
+      <c r="D534" s="0"/>
+      <c r="E534" s="0"/>
+      <c r="F534" s="0"/>
+      <c r="G534" s="0"/>
+      <c r="H534" s="0"/>
+      <c r="I534" s="0"/>
+      <c r="XFC534" s="0"/>
+      <c r="XFD534" s="0"/>
+    </row>
+    <row r="535" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A535" s="0"/>
+      <c r="B535" s="0"/>
+      <c r="C535" s="0"/>
+      <c r="D535" s="0"/>
+      <c r="E535" s="0"/>
+      <c r="F535" s="0"/>
+      <c r="G535" s="0"/>
+      <c r="H535" s="0"/>
+      <c r="I535" s="0"/>
+      <c r="XFC535" s="0"/>
+      <c r="XFD535" s="0"/>
     </row>
     <row r="536" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J536" s="1"/>
+      <c r="A536" s="0"/>
+      <c r="B536" s="0"/>
+      <c r="C536" s="0"/>
+      <c r="D536" s="0"/>
+      <c r="E536" s="0"/>
+      <c r="F536" s="0"/>
+      <c r="G536" s="0"/>
+      <c r="H536" s="0"/>
+      <c r="I536" s="0"/>
+      <c r="XFC536" s="0"/>
+      <c r="XFD536" s="0"/>
     </row>
     <row r="537" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J537" s="1"/>
+      <c r="A537" s="0"/>
+      <c r="B537" s="0"/>
+      <c r="C537" s="0"/>
+      <c r="D537" s="0"/>
+      <c r="E537" s="0"/>
+      <c r="F537" s="0"/>
+      <c r="G537" s="0"/>
+      <c r="H537" s="0"/>
+      <c r="I537" s="0"/>
+      <c r="XFC537" s="0"/>
+      <c r="XFD537" s="0"/>
     </row>
     <row r="538" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J538" s="1"/>
+      <c r="A538" s="0"/>
+      <c r="B538" s="0"/>
+      <c r="C538" s="0"/>
+      <c r="D538" s="0"/>
+      <c r="E538" s="0"/>
+      <c r="F538" s="0"/>
+      <c r="G538" s="0"/>
+      <c r="H538" s="0"/>
+      <c r="I538" s="0"/>
+      <c r="XFC538" s="0"/>
+      <c r="XFD538" s="0"/>
     </row>
     <row r="539" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J539" s="1"/>
+      <c r="A539" s="0"/>
+      <c r="B539" s="0"/>
+      <c r="C539" s="0"/>
+      <c r="D539" s="0"/>
+      <c r="E539" s="0"/>
+      <c r="F539" s="0"/>
+      <c r="G539" s="0"/>
+      <c r="H539" s="0"/>
+      <c r="I539" s="0"/>
+      <c r="XFC539" s="0"/>
+      <c r="XFD539" s="0"/>
     </row>
     <row r="540" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J540" s="1"/>
+      <c r="A540" s="0"/>
+      <c r="B540" s="0"/>
+      <c r="C540" s="0"/>
+      <c r="D540" s="0"/>
+      <c r="E540" s="0"/>
+      <c r="F540" s="0"/>
+      <c r="G540" s="0"/>
+      <c r="H540" s="0"/>
+      <c r="I540" s="0"/>
+      <c r="XFC540" s="0"/>
+      <c r="XFD540" s="0"/>
     </row>
     <row r="541" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J541" s="1"/>
+      <c r="A541" s="0"/>
+      <c r="B541" s="0"/>
+      <c r="C541" s="0"/>
+      <c r="D541" s="0"/>
+      <c r="E541" s="0"/>
+      <c r="F541" s="0"/>
+      <c r="G541" s="0"/>
+      <c r="H541" s="0"/>
+      <c r="I541" s="0"/>
+      <c r="XFC541" s="0"/>
+      <c r="XFD541" s="0"/>
     </row>
     <row r="542" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J542" s="1"/>
+      <c r="A542" s="0"/>
+      <c r="B542" s="0"/>
+      <c r="C542" s="0"/>
+      <c r="D542" s="0"/>
+      <c r="E542" s="0"/>
+      <c r="F542" s="0"/>
+      <c r="G542" s="0"/>
+      <c r="H542" s="0"/>
+      <c r="I542" s="0"/>
+      <c r="XFC542" s="0"/>
+      <c r="XFD542" s="0"/>
     </row>
     <row r="543" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J543" s="1"/>
+      <c r="A543" s="0"/>
+      <c r="B543" s="0"/>
+      <c r="C543" s="0"/>
+      <c r="D543" s="0"/>
+      <c r="E543" s="0"/>
+      <c r="F543" s="0"/>
+      <c r="G543" s="0"/>
+      <c r="H543" s="0"/>
+      <c r="I543" s="0"/>
+      <c r="XFC543" s="0"/>
+      <c r="XFD543" s="0"/>
     </row>
     <row r="544" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J544" s="1"/>
+      <c r="A544" s="0"/>
+      <c r="B544" s="0"/>
+      <c r="C544" s="0"/>
+      <c r="D544" s="0"/>
+      <c r="E544" s="0"/>
+      <c r="F544" s="0"/>
+      <c r="G544" s="0"/>
+      <c r="H544" s="0"/>
+      <c r="I544" s="0"/>
+      <c r="XFC544" s="0"/>
+      <c r="XFD544" s="0"/>
+    </row>
+    <row r="545" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A545" s="0"/>
+      <c r="B545" s="0"/>
+      <c r="C545" s="0"/>
+      <c r="D545" s="0"/>
+      <c r="E545" s="0"/>
+      <c r="F545" s="0"/>
+      <c r="G545" s="0"/>
+      <c r="H545" s="0"/>
+      <c r="I545" s="0"/>
+      <c r="XFC545" s="0"/>
+      <c r="XFD545" s="0"/>
+    </row>
+    <row r="546" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A546" s="0"/>
+      <c r="B546" s="0"/>
+      <c r="C546" s="0"/>
+      <c r="D546" s="0"/>
+      <c r="E546" s="0"/>
+      <c r="F546" s="0"/>
+      <c r="G546" s="0"/>
+      <c r="H546" s="0"/>
+      <c r="I546" s="0"/>
+      <c r="XFC546" s="0"/>
+      <c r="XFD546" s="0"/>
     </row>
     <row r="547" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J547" s="1"/>
+      <c r="A547" s="0"/>
+      <c r="B547" s="0"/>
+      <c r="C547" s="0"/>
+      <c r="D547" s="0"/>
+      <c r="E547" s="0"/>
+      <c r="F547" s="0"/>
+      <c r="G547" s="0"/>
+      <c r="H547" s="0"/>
+      <c r="I547" s="0"/>
+      <c r="XFC547" s="0"/>
+      <c r="XFD547" s="0"/>
+    </row>
+    <row r="548" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A548" s="0"/>
+      <c r="B548" s="0"/>
+      <c r="C548" s="0"/>
+      <c r="D548" s="0"/>
+      <c r="E548" s="0"/>
+      <c r="F548" s="0"/>
+      <c r="G548" s="4"/>
+      <c r="H548" s="0"/>
+      <c r="I548" s="0"/>
+      <c r="XFC548" s="0"/>
+      <c r="XFD548" s="0"/>
     </row>
     <row r="549" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K549" s="1"/>
+      <c r="A549" s="0"/>
+      <c r="B549" s="0"/>
+      <c r="C549" s="0"/>
+      <c r="D549" s="0"/>
+      <c r="E549" s="0"/>
+      <c r="F549" s="0"/>
+      <c r="G549" s="0"/>
+      <c r="H549" s="0"/>
+      <c r="I549" s="0"/>
+      <c r="XFC549" s="0"/>
+      <c r="XFD549" s="0"/>
     </row>
     <row r="550" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K550" s="1"/>
+      <c r="A550" s="0"/>
+      <c r="B550" s="0"/>
+      <c r="C550" s="0"/>
+      <c r="D550" s="0"/>
+      <c r="E550" s="0"/>
+      <c r="F550" s="0"/>
+      <c r="G550" s="0"/>
+      <c r="H550" s="0"/>
+      <c r="I550" s="0"/>
+      <c r="XFC550" s="0"/>
+      <c r="XFD550" s="0"/>
     </row>
     <row r="551" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K551" s="1"/>
+      <c r="A551" s="0"/>
+      <c r="B551" s="0"/>
+      <c r="C551" s="0"/>
+      <c r="D551" s="0"/>
+      <c r="E551" s="0"/>
+      <c r="F551" s="0"/>
+      <c r="G551" s="0"/>
+      <c r="H551" s="0"/>
+      <c r="I551" s="0"/>
+      <c r="XFC551" s="0"/>
+      <c r="XFD551" s="0"/>
+    </row>
+    <row r="552" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A552" s="0"/>
+      <c r="B552" s="0"/>
+      <c r="C552" s="0"/>
+      <c r="D552" s="0"/>
+      <c r="E552" s="0"/>
+      <c r="F552" s="0"/>
+      <c r="G552" s="0"/>
+      <c r="H552" s="0"/>
+      <c r="I552" s="0"/>
+      <c r="XFC552" s="0"/>
+      <c r="XFD552" s="0"/>
+    </row>
+    <row r="553" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A553" s="0"/>
+      <c r="B553" s="0"/>
+      <c r="C553" s="0"/>
+      <c r="D553" s="0"/>
+      <c r="E553" s="0"/>
+      <c r="F553" s="0"/>
+      <c r="G553" s="0"/>
+      <c r="H553" s="0"/>
+      <c r="I553" s="0"/>
+      <c r="XFC553" s="0"/>
+      <c r="XFD553" s="0"/>
     </row>
     <row r="554" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K554" s="1"/>
+      <c r="A554" s="0"/>
+      <c r="B554" s="0"/>
+      <c r="C554" s="0"/>
+      <c r="D554" s="0"/>
+      <c r="E554" s="0"/>
+      <c r="F554" s="0"/>
+      <c r="G554" s="0"/>
+      <c r="H554" s="0"/>
+      <c r="I554" s="0"/>
+      <c r="XFC554" s="0"/>
+      <c r="XFD554" s="0"/>
     </row>
     <row r="555" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J555" s="1"/>
-      <c r="M555" s="1"/>
+      <c r="A555" s="0"/>
+      <c r="B555" s="0"/>
+      <c r="C555" s="0"/>
+      <c r="D555" s="0"/>
+      <c r="E555" s="0"/>
+      <c r="F555" s="0"/>
+      <c r="G555" s="0"/>
+      <c r="H555" s="0"/>
+      <c r="I555" s="0"/>
+      <c r="XFC555" s="0"/>
+      <c r="XFD555" s="0"/>
     </row>
     <row r="556" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K556" s="1"/>
+      <c r="A556" s="0"/>
+      <c r="B556" s="0"/>
+      <c r="C556" s="0"/>
+      <c r="D556" s="0"/>
+      <c r="E556" s="0"/>
+      <c r="F556" s="0"/>
+      <c r="G556" s="0"/>
+      <c r="H556" s="0"/>
+      <c r="I556" s="0"/>
+      <c r="XFC556" s="0"/>
+      <c r="XFD556" s="0"/>
+    </row>
+    <row r="557" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A557" s="0"/>
+      <c r="B557" s="0"/>
+      <c r="C557" s="0"/>
+      <c r="D557" s="0"/>
+      <c r="E557" s="0"/>
+      <c r="F557" s="0"/>
+      <c r="G557" s="0"/>
+      <c r="H557" s="0"/>
+      <c r="I557" s="0"/>
+      <c r="XFC557" s="0"/>
+      <c r="XFD557" s="0"/>
     </row>
     <row r="558" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J558" s="1"/>
+      <c r="A558" s="0"/>
+      <c r="B558" s="0"/>
+      <c r="C558" s="0"/>
+      <c r="D558" s="0"/>
+      <c r="E558" s="0"/>
+      <c r="F558" s="0"/>
+      <c r="G558" s="0"/>
+      <c r="H558" s="0"/>
+      <c r="I558" s="0"/>
+      <c r="XFC558" s="0"/>
+      <c r="XFD558" s="0"/>
+    </row>
+    <row r="559" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A559" s="0"/>
+      <c r="B559" s="0"/>
+      <c r="C559" s="0"/>
+      <c r="D559" s="0"/>
+      <c r="E559" s="0"/>
+      <c r="F559" s="0"/>
+      <c r="G559" s="0"/>
+      <c r="H559" s="0"/>
+      <c r="I559" s="0"/>
+      <c r="XFC559" s="0"/>
+      <c r="XFD559" s="0"/>
+    </row>
+    <row r="560" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A560" s="0"/>
+      <c r="B560" s="0"/>
+      <c r="C560" s="0"/>
+      <c r="D560" s="0"/>
+      <c r="E560" s="0"/>
+      <c r="F560" s="0"/>
+      <c r="G560" s="0"/>
+      <c r="H560" s="0"/>
+      <c r="I560" s="0"/>
+      <c r="XFC560" s="0"/>
+      <c r="XFD560" s="0"/>
+    </row>
+    <row r="561" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A561" s="0"/>
+      <c r="B561" s="0"/>
+      <c r="C561" s="0"/>
+      <c r="D561" s="0"/>
+      <c r="E561" s="0"/>
+      <c r="F561" s="0"/>
+      <c r="G561" s="0"/>
+      <c r="H561" s="0"/>
+      <c r="I561" s="0"/>
+      <c r="XFC561" s="0"/>
+      <c r="XFD561" s="0"/>
     </row>
     <row r="562" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K562" s="1"/>
+      <c r="A562" s="0"/>
+      <c r="B562" s="0"/>
+      <c r="C562" s="0"/>
+      <c r="D562" s="0"/>
+      <c r="E562" s="0"/>
+      <c r="F562" s="0"/>
+      <c r="G562" s="0"/>
+      <c r="H562" s="0"/>
+      <c r="I562" s="0"/>
+      <c r="XFC562" s="0"/>
+      <c r="XFD562" s="0"/>
     </row>
     <row r="563" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J563" s="1"/>
+      <c r="A563" s="0"/>
+      <c r="B563" s="0"/>
+      <c r="C563" s="0"/>
+      <c r="D563" s="0"/>
+      <c r="E563" s="0"/>
+      <c r="F563" s="0"/>
+      <c r="G563" s="0"/>
+      <c r="H563" s="0"/>
+      <c r="I563" s="0"/>
+      <c r="XFC563" s="0"/>
+      <c r="XFD563" s="0"/>
     </row>
     <row r="564" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K564" s="1"/>
+      <c r="A564" s="0"/>
+      <c r="B564" s="0"/>
+      <c r="C564" s="0"/>
+      <c r="D564" s="0"/>
+      <c r="E564" s="0"/>
+      <c r="F564" s="0"/>
+      <c r="G564" s="0"/>
+      <c r="H564" s="0"/>
+      <c r="I564" s="0"/>
+      <c r="XFC564" s="0"/>
+      <c r="XFD564" s="0"/>
+    </row>
+    <row r="565" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A565" s="0"/>
+      <c r="B565" s="0"/>
+      <c r="C565" s="0"/>
+      <c r="D565" s="0"/>
+      <c r="E565" s="0"/>
+      <c r="F565" s="0"/>
+      <c r="G565" s="0"/>
+      <c r="H565" s="0"/>
+      <c r="I565" s="0"/>
+      <c r="XFC565" s="0"/>
+      <c r="XFD565" s="0"/>
     </row>
     <row r="566" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K566" s="1"/>
+      <c r="A566" s="0"/>
+      <c r="B566" s="0"/>
+      <c r="C566" s="0"/>
+      <c r="D566" s="0"/>
+      <c r="E566" s="0"/>
+      <c r="F566" s="0"/>
+      <c r="G566" s="0"/>
+      <c r="H566" s="0"/>
+      <c r="I566" s="0"/>
+      <c r="XFC566" s="0"/>
+      <c r="XFD566" s="0"/>
     </row>
     <row r="567" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K567" s="1"/>
+      <c r="A567" s="0"/>
+      <c r="B567" s="0"/>
+      <c r="C567" s="0"/>
+      <c r="D567" s="0"/>
+      <c r="E567" s="0"/>
+      <c r="F567" s="0"/>
+      <c r="G567" s="0"/>
+      <c r="H567" s="0"/>
+      <c r="I567" s="0"/>
+      <c r="XFC567" s="0"/>
+      <c r="XFD567" s="0"/>
     </row>
     <row r="568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K568" s="1"/>
+      <c r="A568" s="0"/>
+      <c r="B568" s="0"/>
+      <c r="C568" s="0"/>
+      <c r="D568" s="0"/>
+      <c r="E568" s="0"/>
+      <c r="F568" s="0"/>
+      <c r="G568" s="0"/>
+      <c r="H568" s="0"/>
+      <c r="I568" s="0"/>
+      <c r="XFC568" s="0"/>
+      <c r="XFD568" s="0"/>
     </row>
     <row r="569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K569" s="1"/>
+      <c r="A569" s="0"/>
+      <c r="B569" s="0"/>
+      <c r="C569" s="0"/>
+      <c r="D569" s="0"/>
+      <c r="E569" s="0"/>
+      <c r="F569" s="0"/>
+      <c r="G569" s="0"/>
+      <c r="H569" s="0"/>
+      <c r="I569" s="0"/>
+      <c r="XFC569" s="0"/>
+      <c r="XFD569" s="0"/>
     </row>
     <row r="570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K570" s="1"/>
+      <c r="A570" s="0"/>
+      <c r="B570" s="0"/>
+      <c r="C570" s="0"/>
+      <c r="D570" s="0"/>
+      <c r="E570" s="0"/>
+      <c r="F570" s="0"/>
+      <c r="G570" s="0"/>
+      <c r="H570" s="0"/>
+      <c r="I570" s="0"/>
+      <c r="XFC570" s="0"/>
+      <c r="XFD570" s="0"/>
     </row>
     <row r="571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K571" s="1"/>
+      <c r="A571" s="0"/>
+      <c r="B571" s="0"/>
+      <c r="C571" s="0"/>
+      <c r="D571" s="0"/>
+      <c r="E571" s="0"/>
+      <c r="F571" s="0"/>
+      <c r="G571" s="4"/>
+      <c r="H571" s="0"/>
+      <c r="I571" s="0"/>
+      <c r="XFC571" s="0"/>
+      <c r="XFD571" s="0"/>
     </row>
     <row r="572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K572" s="1"/>
+      <c r="A572" s="0"/>
+      <c r="B572" s="0"/>
+      <c r="C572" s="0"/>
+      <c r="D572" s="0"/>
+      <c r="E572" s="0"/>
+      <c r="F572" s="0"/>
+      <c r="G572" s="4"/>
+      <c r="H572" s="0"/>
+      <c r="I572" s="0"/>
+      <c r="XFC572" s="0"/>
+      <c r="XFD572" s="0"/>
     </row>
     <row r="573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K573" s="1"/>
+      <c r="A573" s="0"/>
+      <c r="B573" s="0"/>
+      <c r="C573" s="0"/>
+      <c r="D573" s="0"/>
+      <c r="E573" s="0"/>
+      <c r="F573" s="0"/>
+      <c r="G573" s="0"/>
+      <c r="H573" s="0"/>
+      <c r="I573" s="0"/>
+      <c r="XFC573" s="0"/>
+      <c r="XFD573" s="0"/>
     </row>
     <row r="574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K574" s="1"/>
@@ -3918,7 +10104,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D109"/>
+  <dimension ref="A1:D88"/>
   <sheetFormatPr defaultColWidth="13.01171875" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="34.43"/>
@@ -3953,28 +10139,28 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="4"/>
+      <c r="D3" s="5"/>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="4"/>
+      <c r="D4" s="5"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
@@ -4000,73 +10186,74 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
-        <v>23</v>
+      <c r="A9" s="6" t="s">
+        <v>28</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>33</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="D9" s="6"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>37</v>
@@ -4077,7 +10264,7 @@
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>39</v>
@@ -4087,42 +10274,41 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D15" s="5"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="C16" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>48</v>
@@ -4133,7 +10319,7 @@
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>50</v>
@@ -4144,7 +10330,7 @@
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>52</v>
@@ -4155,7 +10341,7 @@
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>54</v>
@@ -4166,7 +10352,7 @@
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>56</v>
@@ -4177,7 +10363,7 @@
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>58</v>
@@ -4188,106 +10374,106 @@
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="C24" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="B25" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="B26" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C26" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="B27" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C27" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="B28" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="B29" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C29" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="B30" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C30" s="1" t="s">
         <v>73</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>75</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="B32" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C32" s="1" t="s">
         <v>77</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>43</v>
+        <v>78</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>79</v>
@@ -4298,7 +10484,7 @@
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>43</v>
+        <v>78</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>81</v>
@@ -4309,7 +10495,7 @@
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>43</v>
+        <v>78</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>83</v>
@@ -4320,43 +10506,43 @@
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>43</v>
+        <v>85</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>43</v>
+        <v>85</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>43</v>
+        <v>85</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>32</v>
+        <v>76</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>33</v>
+        <v>77</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>91</v>
@@ -4364,798 +10550,402 @@
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>92</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B44" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="C44" s="1" t="s">
-        <v>33</v>
+        <v>96</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B48" s="1" t="s">
-        <v>105</v>
-      </c>
       <c r="C48" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
+      </c>
+      <c r="B50" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
+      </c>
+      <c r="B51" s="1" t="n">
+        <v>1</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>109</v>
+        <v>105</v>
+      </c>
+      <c r="B52" s="1" t="n">
+        <v>2</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>110</v>
+        <v>105</v>
+      </c>
+      <c r="B53" s="1" t="n">
+        <v>3</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>112</v>
+        <v>105</v>
+      </c>
+      <c r="B54" s="1" t="n">
+        <v>4</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B55" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="C55" s="1" t="s">
         <v>111</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>117</v>
+        <v>105</v>
+      </c>
+      <c r="B56" s="1" t="n">
+        <v>6</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>119</v>
+        <v>105</v>
+      </c>
+      <c r="B57" s="1" t="n">
+        <v>7</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>121</v>
+        <v>105</v>
+      </c>
+      <c r="B58" s="1" t="n">
+        <v>8</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>123</v>
+        <v>105</v>
+      </c>
+      <c r="B59" s="1" t="n">
+        <v>9</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B60" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="C60" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B60" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>128</v>
+        <v>105</v>
+      </c>
+      <c r="B61" s="1" t="n">
+        <v>11</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="D61" s="6"/>
-    </row>
-    <row r="62" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>130</v>
+        <v>105</v>
+      </c>
+      <c r="B62" s="1" t="n">
+        <v>12</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="D62" s="6"/>
-    </row>
-    <row r="63" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>132</v>
+        <v>105</v>
+      </c>
+      <c r="B63" s="1" t="n">
+        <v>13</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="D63" s="6"/>
-    </row>
-    <row r="64" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>134</v>
+        <v>105</v>
+      </c>
+      <c r="B64" s="1" t="n">
+        <v>14</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="D64" s="6"/>
-    </row>
-    <row r="65" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>136</v>
+        <v>105</v>
+      </c>
+      <c r="B65" s="1" t="n">
+        <v>15</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D65" s="6"/>
+        <v>121</v>
+      </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>139</v>
+        <v>105</v>
+      </c>
+      <c r="B66" s="1" t="n">
+        <v>16</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>141</v>
+        <v>105</v>
+      </c>
+      <c r="B67" s="1" t="n">
+        <v>17</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>142</v>
+        <v>123</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>143</v>
+        <v>105</v>
+      </c>
+      <c r="B68" s="1" t="n">
+        <v>18</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>146</v>
-      </c>
+      <c r="C69" s="7"/>
+      <c r="D69" s="7"/>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>148</v>
-      </c>
+      <c r="C70" s="7"/>
+      <c r="D70" s="7"/>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="B71" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>150</v>
-      </c>
+      <c r="C71" s="7"/>
+      <c r="D71" s="7"/>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="B72" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>151</v>
-      </c>
+      <c r="C72" s="7"/>
+      <c r="D72" s="7"/>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="B73" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>152</v>
-      </c>
+      <c r="C73" s="7"/>
+      <c r="D73" s="7"/>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="B74" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>153</v>
-      </c>
+      <c r="C74" s="7"/>
+      <c r="D74" s="7"/>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="B75" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>154</v>
-      </c>
+      <c r="C75" s="7"/>
+      <c r="D75" s="7"/>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="B76" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>155</v>
-      </c>
+      <c r="C76" s="7"/>
+      <c r="D76" s="7"/>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="B77" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>156</v>
-      </c>
+      <c r="C77" s="7"/>
+      <c r="D77" s="7"/>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="B78" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>157</v>
-      </c>
+      <c r="C78" s="7"/>
+      <c r="D78" s="7"/>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="B79" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>158</v>
-      </c>
+      <c r="C79" s="7"/>
+      <c r="D79" s="7"/>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="B80" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>159</v>
-      </c>
+      <c r="C80" s="7"/>
+      <c r="D80" s="7"/>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="B81" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>160</v>
-      </c>
+      <c r="C81" s="7"/>
+      <c r="D81" s="7"/>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="B82" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>161</v>
-      </c>
+      <c r="C82" s="7"/>
+      <c r="D82" s="7"/>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="B83" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>162</v>
-      </c>
+      <c r="C83" s="7"/>
+      <c r="D83" s="7"/>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="B84" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>163</v>
-      </c>
+      <c r="C84" s="7"/>
+      <c r="D84" s="7"/>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="B85" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>164</v>
-      </c>
+      <c r="C85" s="7"/>
+      <c r="D85" s="7"/>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="B86" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>165</v>
-      </c>
+      <c r="C86" s="7"/>
+      <c r="D86" s="7"/>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="B87" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>166</v>
-      </c>
+      <c r="C87" s="7"/>
+      <c r="D87" s="7"/>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="B88" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="B89" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="B90" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="C90" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="D90" s="7"/>
-    </row>
-    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="B91" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="C91" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="D91" s="7"/>
-    </row>
-    <row r="92" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="B92" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="C92" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="D92" s="7"/>
-    </row>
-    <row r="93" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="B93" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="C93" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="D93" s="7"/>
-    </row>
-    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="B94" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C94" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="D94" s="7"/>
-    </row>
-    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="B95" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="C95" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="D95" s="7"/>
-    </row>
-    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="B96" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="C96" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="D96" s="7"/>
-    </row>
-    <row r="97" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="B97" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="C97" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="D97" s="7"/>
-    </row>
-    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="B98" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="C98" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="D98" s="7"/>
-    </row>
-    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="B99" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C99" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="D99" s="7"/>
-    </row>
-    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="B100" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="C100" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="D100" s="7"/>
-    </row>
-    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="B101" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="C101" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="D101" s="7"/>
-    </row>
-    <row r="102" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="B102" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="C102" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="D102" s="7"/>
-    </row>
-    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="B103" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="C103" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="D103" s="7"/>
-    </row>
-    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="B104" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C104" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="D104" s="7"/>
-    </row>
-    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="B105" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="C105" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="D105" s="7"/>
-    </row>
-    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="B106" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="C106" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D106" s="7"/>
-    </row>
-    <row r="107" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="B107" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="C107" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="D107" s="7"/>
-    </row>
-    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="B108" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="C108" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="D108" s="7"/>
-    </row>
-    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="B109" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C109" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="D109" s="7"/>
+      <c r="C88" s="7"/>
+      <c r="D88" s="7"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -5181,18 +10971,18 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>193</v>
+        <v>125</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>194</v>
+        <v>126</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>195</v>
+        <v>127</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>196</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>
